--- a/testeAcudes.xlsx
+++ b/testeAcudes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guilh\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D654A47-BAE1-4354-9C43-4423F50319C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5CF4A71-0ACD-4889-B293-08C0EBE0B40C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" activeTab="4" xr2:uid="{03030AE7-6658-4B4E-BFD4-202602A2443F}"/>
   </bookViews>
@@ -16,8 +16,9 @@
     <sheet name="cav" sheetId="1" r:id="rId1"/>
     <sheet name="evaporacao" sheetId="2" r:id="rId2"/>
     <sheet name="acudes" sheetId="3" r:id="rId3"/>
-    <sheet name="Acarape do Meio" sheetId="4" r:id="rId4"/>
-    <sheet name="Acaraú Mirim" sheetId="5" r:id="rId5"/>
+    <sheet name="vazoes" sheetId="6" r:id="rId4"/>
+    <sheet name="Acarape do Meio" sheetId="4" r:id="rId5"/>
+    <sheet name="Acaraú Mirim" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -265,7 +266,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="490">
   <si>
     <t>COD</t>
   </si>
@@ -2158,7 +2159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="242">
+  <cellXfs count="243">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2845,6 +2846,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -60364,6 +60366,9510 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AD6CC15-A149-4AF9-8D45-5CE6C1C3ED3D}">
+  <dimension ref="A1:N217"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="242">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s">
+        <v>379</v>
+      </c>
+      <c r="L2">
+        <v>1.2096173116870499E-3</v>
+      </c>
+      <c r="M2">
+        <v>1.2974965140222601E-3</v>
+      </c>
+      <c r="N2">
+        <v>1.0707445340268301E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="242">
+        <v>78</v>
+      </c>
+      <c r="B3" t="s">
+        <v>380</v>
+      </c>
+      <c r="C3">
+        <v>1.59405236529493E-2</v>
+      </c>
+      <c r="D3">
+        <v>9.4438691771907193E-3</v>
+      </c>
+      <c r="E3">
+        <v>0.24228614414308</v>
+      </c>
+      <c r="F3">
+        <v>0.57166096665356403</v>
+      </c>
+      <c r="G3">
+        <v>0.222229313221491</v>
+      </c>
+      <c r="H3">
+        <v>0.109689143518476</v>
+      </c>
+      <c r="I3">
+        <v>5.7800324699421798E-2</v>
+      </c>
+      <c r="J3">
+        <v>9.7573778540179304E-2</v>
+      </c>
+      <c r="K3">
+        <v>3.6756518951740397E-2</v>
+      </c>
+      <c r="L3">
+        <v>1.19129858419681E-2</v>
+      </c>
+      <c r="M3">
+        <v>1.7221561772957202E-2</v>
+      </c>
+      <c r="N3">
+        <v>1.9174326213775499E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="242">
+        <v>78</v>
+      </c>
+      <c r="B4" t="s">
+        <v>381</v>
+      </c>
+      <c r="C4">
+        <v>9.9867181871828803E-2</v>
+      </c>
+      <c r="D4">
+        <v>0.54498934474074301</v>
+      </c>
+      <c r="E4">
+        <v>2.6883836253359399</v>
+      </c>
+      <c r="F4">
+        <v>5.5749290444183703</v>
+      </c>
+      <c r="G4">
+        <v>4.4739621324075003</v>
+      </c>
+      <c r="H4">
+        <v>1.32940540519916</v>
+      </c>
+      <c r="I4">
+        <v>0.23383445482517201</v>
+      </c>
+      <c r="J4">
+        <v>0.33434742804248901</v>
+      </c>
+      <c r="K4">
+        <v>0.16436389699717199</v>
+      </c>
+      <c r="L4">
+        <v>9.9063751894751001E-2</v>
+      </c>
+      <c r="M4">
+        <v>6.15670351208948E-2</v>
+      </c>
+      <c r="N4">
+        <v>5.6552805750309597E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="242">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C5">
+        <v>8.9126259531353905E-2</v>
+      </c>
+      <c r="D5">
+        <v>0.75515652250386101</v>
+      </c>
+      <c r="E5">
+        <v>3.92359154564204</v>
+      </c>
+      <c r="F5">
+        <v>4.4279703962385497</v>
+      </c>
+      <c r="G5">
+        <v>2.5011760890606198</v>
+      </c>
+      <c r="H5">
+        <v>1.8450123342722999</v>
+      </c>
+      <c r="I5">
+        <v>0.65000170094005405</v>
+      </c>
+      <c r="J5">
+        <v>0.3204295122584</v>
+      </c>
+      <c r="K5">
+        <v>0.185799796571228</v>
+      </c>
+      <c r="L5">
+        <v>0.34478573068635499</v>
+      </c>
+      <c r="M5">
+        <v>0.106350202447251</v>
+      </c>
+      <c r="N5">
+        <v>0.39656898519950401</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="242">
+        <v>78</v>
+      </c>
+      <c r="B6" t="s">
+        <v>383</v>
+      </c>
+      <c r="C6">
+        <v>0.58121100841197504</v>
+      </c>
+      <c r="D6">
+        <v>1.1152413655390301</v>
+      </c>
+      <c r="E6">
+        <v>2.1002580113790401</v>
+      </c>
+      <c r="F6">
+        <v>4.4258612342668604</v>
+      </c>
+      <c r="G6">
+        <v>3.1646833520280802</v>
+      </c>
+      <c r="H6">
+        <v>3.7419032161715702</v>
+      </c>
+      <c r="I6">
+        <v>0.82879187237289098</v>
+      </c>
+      <c r="J6">
+        <v>0.81391048862035098</v>
+      </c>
+      <c r="K6">
+        <v>0.129679835616028</v>
+      </c>
+      <c r="L6">
+        <v>0.110514146816002</v>
+      </c>
+      <c r="M6">
+        <v>0.10833044380281701</v>
+      </c>
+      <c r="N6">
+        <v>8.2236283119769896E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="242">
+        <v>78</v>
+      </c>
+      <c r="B7" t="s">
+        <v>384</v>
+      </c>
+      <c r="C7">
+        <v>0.102825458409443</v>
+      </c>
+      <c r="D7">
+        <v>0.10551573674469999</v>
+      </c>
+      <c r="E7">
+        <v>0.108724480659767</v>
+      </c>
+      <c r="F7">
+        <v>0.14951098161476001</v>
+      </c>
+      <c r="G7">
+        <v>9.1972290403366005E-2</v>
+      </c>
+      <c r="H7">
+        <v>7.1536209567438405E-2</v>
+      </c>
+      <c r="I7">
+        <v>3.5264339693460198E-2</v>
+      </c>
+      <c r="J7">
+        <v>3.4737161306178203E-2</v>
+      </c>
+      <c r="K7">
+        <v>3.2217339686446099E-2</v>
+      </c>
+      <c r="L7">
+        <v>2.2895147065785899E-2</v>
+      </c>
+      <c r="M7">
+        <v>1.8836464653602301E-2</v>
+      </c>
+      <c r="N7">
+        <v>2.19959315389875E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="242">
+        <v>78</v>
+      </c>
+      <c r="B8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C8">
+        <v>2.7667753369534899E-2</v>
+      </c>
+      <c r="D8">
+        <v>7.5891269557477201E-2</v>
+      </c>
+      <c r="E8">
+        <v>0.84126152688942302</v>
+      </c>
+      <c r="F8">
+        <v>2.3312756697680999</v>
+      </c>
+      <c r="G8">
+        <v>1.8437496970545</v>
+      </c>
+      <c r="H8">
+        <v>1.82305362263586</v>
+      </c>
+      <c r="I8">
+        <v>4.4465439587795801E-2</v>
+      </c>
+      <c r="J8">
+        <v>4.3129322373750098E-2</v>
+      </c>
+      <c r="K8">
+        <v>4.7324940318107599E-2</v>
+      </c>
+      <c r="L8">
+        <v>5.0630858514414498E-2</v>
+      </c>
+      <c r="M8">
+        <v>0.10042065326892501</v>
+      </c>
+      <c r="N8">
+        <v>0.13209537194709201</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="242">
+        <v>78</v>
+      </c>
+      <c r="B9" t="s">
+        <v>386</v>
+      </c>
+      <c r="C9">
+        <v>0.71762779392593901</v>
+      </c>
+      <c r="D9">
+        <v>3.22862823964073</v>
+      </c>
+      <c r="E9">
+        <v>8.5774401251316696</v>
+      </c>
+      <c r="F9">
+        <v>6.2300603093462898</v>
+      </c>
+      <c r="G9">
+        <v>13.040528449553801</v>
+      </c>
+      <c r="H9">
+        <v>1.8129596001378401</v>
+      </c>
+      <c r="I9">
+        <v>0.31923553257128101</v>
+      </c>
+      <c r="J9">
+        <v>0.226311087603871</v>
+      </c>
+      <c r="K9">
+        <v>0.29679530937621101</v>
+      </c>
+      <c r="L9">
+        <v>0.118370681396452</v>
+      </c>
+      <c r="M9">
+        <v>0.23309067253771701</v>
+      </c>
+      <c r="N9">
+        <v>0.17872806555891901</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="242">
+        <v>78</v>
+      </c>
+      <c r="B10" t="s">
+        <v>387</v>
+      </c>
+      <c r="C10">
+        <v>0.24429338713260601</v>
+      </c>
+      <c r="D10">
+        <v>0.67634065700054202</v>
+      </c>
+      <c r="E10">
+        <v>1.96245079471085</v>
+      </c>
+      <c r="F10">
+        <v>3.1540111027452</v>
+      </c>
+      <c r="G10">
+        <v>3.8918241041446202</v>
+      </c>
+      <c r="H10">
+        <v>1.9147204610483399</v>
+      </c>
+      <c r="I10">
+        <v>0.33646748258218501</v>
+      </c>
+      <c r="J10">
+        <v>0.50636562071350899</v>
+      </c>
+      <c r="K10">
+        <v>0.159322728458791</v>
+      </c>
+      <c r="L10">
+        <v>0.10912297540521</v>
+      </c>
+      <c r="M10">
+        <v>8.6969791287386106E-2</v>
+      </c>
+      <c r="N10">
+        <v>0.24007829870434799</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="242">
+        <v>78</v>
+      </c>
+      <c r="B11" t="s">
+        <v>388</v>
+      </c>
+      <c r="C11">
+        <v>8.2248692345582103E-2</v>
+      </c>
+      <c r="D11">
+        <v>0.130226615538348</v>
+      </c>
+      <c r="E11">
+        <v>0.103104353521815</v>
+      </c>
+      <c r="F11">
+        <v>9.6971259611549995E-2</v>
+      </c>
+      <c r="G11">
+        <v>9.2037039693442194E-2</v>
+      </c>
+      <c r="H11">
+        <v>5.2788916035938702E-2</v>
+      </c>
+      <c r="I11">
+        <v>5.2728727659217503E-2</v>
+      </c>
+      <c r="J11">
+        <v>4.79678701980338E-2</v>
+      </c>
+      <c r="K11">
+        <v>3.5207019586342501E-2</v>
+      </c>
+      <c r="L11">
+        <v>2.4335396066754101E-2</v>
+      </c>
+      <c r="M11">
+        <v>2.0612789885231901E-2</v>
+      </c>
+      <c r="N11">
+        <v>1.7983070572137601E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="242">
+        <v>78</v>
+      </c>
+      <c r="B12" t="s">
+        <v>389</v>
+      </c>
+      <c r="C12">
+        <v>1.6370248735474099E-2</v>
+      </c>
+      <c r="D12">
+        <v>2.09517426767897E-2</v>
+      </c>
+      <c r="E12">
+        <v>0.28169057396085001</v>
+      </c>
+      <c r="F12">
+        <v>1.03259637237393</v>
+      </c>
+      <c r="G12">
+        <v>1.7638357321379099</v>
+      </c>
+      <c r="H12">
+        <v>0.96856803954066895</v>
+      </c>
+      <c r="I12">
+        <v>0.59162257415213404</v>
+      </c>
+      <c r="J12">
+        <v>0.11060395679816699</v>
+      </c>
+      <c r="K12">
+        <v>7.2919240786923398E-2</v>
+      </c>
+      <c r="L12">
+        <v>4.4736338357748102E-2</v>
+      </c>
+      <c r="M12">
+        <v>7.4569917741151806E-2</v>
+      </c>
+      <c r="N12">
+        <v>0.139937002109838</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="242">
+        <v>78</v>
+      </c>
+      <c r="B13" t="s">
+        <v>390</v>
+      </c>
+      <c r="C13">
+        <v>0.15923184749968</v>
+      </c>
+      <c r="D13">
+        <v>0.91797322113219504</v>
+      </c>
+      <c r="E13">
+        <v>6.5043828957305001</v>
+      </c>
+      <c r="F13">
+        <v>6.7133448186812297</v>
+      </c>
+      <c r="G13">
+        <v>8.5507451284587006</v>
+      </c>
+      <c r="H13">
+        <v>1.6208351060328501</v>
+      </c>
+      <c r="I13">
+        <v>2.1183886639094198</v>
+      </c>
+      <c r="J13">
+        <v>0.12648331326248</v>
+      </c>
+      <c r="K13">
+        <v>0.29055410765499601</v>
+      </c>
+      <c r="L13">
+        <v>0.20788464997502801</v>
+      </c>
+      <c r="M13">
+        <v>0.25758101392062799</v>
+      </c>
+      <c r="N13">
+        <v>0.16375192612991701</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="242">
+        <v>78</v>
+      </c>
+      <c r="B14" t="s">
+        <v>391</v>
+      </c>
+      <c r="C14">
+        <v>0.214933719925679</v>
+      </c>
+      <c r="D14">
+        <v>0.253851894559038</v>
+      </c>
+      <c r="E14">
+        <v>0.54262951626314404</v>
+      </c>
+      <c r="F14">
+        <v>2.7190164845249201</v>
+      </c>
+      <c r="G14">
+        <v>4.9531637505384598</v>
+      </c>
+      <c r="H14">
+        <v>2.3563680603023398</v>
+      </c>
+      <c r="I14">
+        <v>1.7022707349284201</v>
+      </c>
+      <c r="J14">
+        <v>0.45884489840036202</v>
+      </c>
+      <c r="K14">
+        <v>0.17494994025975399</v>
+      </c>
+      <c r="L14">
+        <v>9.8596346204985794E-2</v>
+      </c>
+      <c r="M14">
+        <v>0.142574354608657</v>
+      </c>
+      <c r="N14">
+        <v>0.10434662755943599</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="242">
+        <v>78</v>
+      </c>
+      <c r="B15" t="s">
+        <v>392</v>
+      </c>
+      <c r="C15">
+        <v>0.22142913044451601</v>
+      </c>
+      <c r="D15">
+        <v>0.551316028814123</v>
+      </c>
+      <c r="E15">
+        <v>1.24600638856511</v>
+      </c>
+      <c r="F15">
+        <v>3.45359983253487</v>
+      </c>
+      <c r="G15">
+        <v>1.87741983425325</v>
+      </c>
+      <c r="H15">
+        <v>1.0663480176555999</v>
+      </c>
+      <c r="I15">
+        <v>0.83337664523738797</v>
+      </c>
+      <c r="J15">
+        <v>9.2186914073500395E-2</v>
+      </c>
+      <c r="K15">
+        <v>0.109840420805297</v>
+      </c>
+      <c r="L15">
+        <v>9.6002786687285194E-2</v>
+      </c>
+      <c r="M15">
+        <v>8.3310637345427804E-2</v>
+      </c>
+      <c r="N15">
+        <v>6.12569607355311E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="242">
+        <v>78</v>
+      </c>
+      <c r="B16" t="s">
+        <v>393</v>
+      </c>
+      <c r="C16">
+        <v>0.15801553350647299</v>
+      </c>
+      <c r="D16">
+        <v>0.60206860489119995</v>
+      </c>
+      <c r="E16">
+        <v>6.7548708731129699</v>
+      </c>
+      <c r="F16">
+        <v>12.827708129521</v>
+      </c>
+      <c r="G16">
+        <v>9.2949301432336799</v>
+      </c>
+      <c r="H16">
+        <v>4.53362512805744</v>
+      </c>
+      <c r="I16">
+        <v>0.56978695592977602</v>
+      </c>
+      <c r="J16">
+        <v>0.14419521396917701</v>
+      </c>
+      <c r="K16">
+        <v>0.23183310130217899</v>
+      </c>
+      <c r="L16">
+        <v>0.37528894899080101</v>
+      </c>
+      <c r="M16">
+        <v>0.15386963525012501</v>
+      </c>
+      <c r="N16">
+        <v>0.28819522072707698</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="242">
+        <v>78</v>
+      </c>
+      <c r="B17" t="s">
+        <v>394</v>
+      </c>
+      <c r="C17">
+        <v>0.70148577318500804</v>
+      </c>
+      <c r="D17">
+        <v>0.76026809291946496</v>
+      </c>
+      <c r="E17">
+        <v>3.3970201505134301</v>
+      </c>
+      <c r="F17">
+        <v>3.8908115056721</v>
+      </c>
+      <c r="G17">
+        <v>1.8211617855194999</v>
+      </c>
+      <c r="H17">
+        <v>0.34787675583608402</v>
+      </c>
+      <c r="I17">
+        <v>0.199694219237289</v>
+      </c>
+      <c r="J17">
+        <v>0.10280007580672899</v>
+      </c>
+      <c r="K17">
+        <v>0.281783430701527</v>
+      </c>
+      <c r="L17">
+        <v>0.10734729668482</v>
+      </c>
+      <c r="M17">
+        <v>9.5105921284309294E-2</v>
+      </c>
+      <c r="N17">
+        <v>0.10375426536810201</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="242">
+        <v>78</v>
+      </c>
+      <c r="B18" t="s">
+        <v>395</v>
+      </c>
+      <c r="C18">
+        <v>0.13345045401416999</v>
+      </c>
+      <c r="D18">
+        <v>0.37804189554384798</v>
+      </c>
+      <c r="E18">
+        <v>2.6028281617734499</v>
+      </c>
+      <c r="F18">
+        <v>4.9691418004357404</v>
+      </c>
+      <c r="G18">
+        <v>2.90625734445746</v>
+      </c>
+      <c r="H18">
+        <v>0.64033562928200505</v>
+      </c>
+      <c r="I18">
+        <v>0.23834796569040401</v>
+      </c>
+      <c r="J18">
+        <v>8.1251181874117104E-2</v>
+      </c>
+      <c r="K18">
+        <v>7.8739036234126994E-2</v>
+      </c>
+      <c r="L18">
+        <v>8.8191565293558802E-2</v>
+      </c>
+      <c r="M18">
+        <v>7.8001418338578807E-2</v>
+      </c>
+      <c r="N18">
+        <v>6.2284514365327802E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="242">
+        <v>78</v>
+      </c>
+      <c r="B19" t="s">
+        <v>396</v>
+      </c>
+      <c r="C19">
+        <v>9.08013869642499E-2</v>
+      </c>
+      <c r="D19">
+        <v>0.15064955138978001</v>
+      </c>
+      <c r="E19">
+        <v>0.36337331334164702</v>
+      </c>
+      <c r="F19">
+        <v>3.49419812121962</v>
+      </c>
+      <c r="G19">
+        <v>2.9908933283404502</v>
+      </c>
+      <c r="H19">
+        <v>0.83433812988557199</v>
+      </c>
+      <c r="I19">
+        <v>0.64590643484437604</v>
+      </c>
+      <c r="J19">
+        <v>7.5508007750334893E-2</v>
+      </c>
+      <c r="K19">
+        <v>6.9713779211725405E-2</v>
+      </c>
+      <c r="L19">
+        <v>7.2667168385608993E-2</v>
+      </c>
+      <c r="M19">
+        <v>7.21740612888538E-2</v>
+      </c>
+      <c r="N19">
+        <v>6.2067741475159199E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="242">
+        <v>78</v>
+      </c>
+      <c r="B20" t="s">
+        <v>397</v>
+      </c>
+      <c r="C20">
+        <v>9.7637207953383598E-2</v>
+      </c>
+      <c r="D20">
+        <v>6.9415493762251104E-2</v>
+      </c>
+      <c r="E20">
+        <v>0.29852263476642399</v>
+      </c>
+      <c r="F20">
+        <v>0.90088499948337397</v>
+      </c>
+      <c r="G20">
+        <v>0.57888680718832897</v>
+      </c>
+      <c r="H20">
+        <v>0.31876870644596</v>
+      </c>
+      <c r="I20">
+        <v>7.6527168547645005E-2</v>
+      </c>
+      <c r="J20">
+        <v>3.6708888932518703E-2</v>
+      </c>
+      <c r="K20">
+        <v>5.3097453467121997E-2</v>
+      </c>
+      <c r="L20">
+        <v>5.8205512548208202E-2</v>
+      </c>
+      <c r="M20">
+        <v>3.1422419625702899E-2</v>
+      </c>
+      <c r="N20">
+        <v>3.1527907962260703E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="242">
+        <v>78</v>
+      </c>
+      <c r="B21" t="s">
+        <v>398</v>
+      </c>
+      <c r="C21">
+        <v>4.5682863095877102E-2</v>
+      </c>
+      <c r="D21">
+        <v>0.295697378606946</v>
+      </c>
+      <c r="E21">
+        <v>2.7844222143908901</v>
+      </c>
+      <c r="F21">
+        <v>4.5226613988577702</v>
+      </c>
+      <c r="G21">
+        <v>3.1360672507059801</v>
+      </c>
+      <c r="H21">
+        <v>0.94665087230829104</v>
+      </c>
+      <c r="I21">
+        <v>0.394794319367681</v>
+      </c>
+      <c r="J21">
+        <v>0.15576804926497101</v>
+      </c>
+      <c r="K21">
+        <v>0.122329920398339</v>
+      </c>
+      <c r="L21">
+        <v>0.111941301355789</v>
+      </c>
+      <c r="M21">
+        <v>7.7830028071219803E-2</v>
+      </c>
+      <c r="N21">
+        <v>0.103415588212826</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="242">
+        <v>78</v>
+      </c>
+      <c r="B22" t="s">
+        <v>399</v>
+      </c>
+      <c r="C22">
+        <v>0.15938734798701901</v>
+      </c>
+      <c r="D22">
+        <v>0.12853507810306899</v>
+      </c>
+      <c r="E22">
+        <v>0.276179859945346</v>
+      </c>
+      <c r="F22">
+        <v>0.79277982331420005</v>
+      </c>
+      <c r="G22">
+        <v>0.46724368114982601</v>
+      </c>
+      <c r="H22">
+        <v>0.77635576353895497</v>
+      </c>
+      <c r="I22">
+        <v>0.17546179790576899</v>
+      </c>
+      <c r="J22">
+        <v>7.2970035432071104E-2</v>
+      </c>
+      <c r="K22">
+        <v>4.80844751394865E-2</v>
+      </c>
+      <c r="L22">
+        <v>7.5729393314247204E-2</v>
+      </c>
+      <c r="M22">
+        <v>4.0689024866414E-2</v>
+      </c>
+      <c r="N22">
+        <v>5.3401102033746303E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="242">
+        <v>78</v>
+      </c>
+      <c r="B23" t="s">
+        <v>400</v>
+      </c>
+      <c r="C23">
+        <v>7.5649424770260196E-2</v>
+      </c>
+      <c r="D23">
+        <v>0.41786576015910398</v>
+      </c>
+      <c r="E23">
+        <v>0.61258836899133895</v>
+      </c>
+      <c r="F23">
+        <v>1.9883905634561201</v>
+      </c>
+      <c r="G23">
+        <v>0.534479843382481</v>
+      </c>
+      <c r="H23">
+        <v>0.38867481547840199</v>
+      </c>
+      <c r="I23">
+        <v>8.1378757403173907E-2</v>
+      </c>
+      <c r="J23">
+        <v>5.4224365288011799E-2</v>
+      </c>
+      <c r="K23">
+        <v>4.5707306123927802E-2</v>
+      </c>
+      <c r="L23">
+        <v>3.7764232557962102E-2</v>
+      </c>
+      <c r="M23">
+        <v>3.2570356065854102E-2</v>
+      </c>
+      <c r="N23">
+        <v>3.0429959739100999E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="242">
+        <v>78</v>
+      </c>
+      <c r="B24" t="s">
+        <v>401</v>
+      </c>
+      <c r="C24">
+        <v>5.15120673544869E-2</v>
+      </c>
+      <c r="D24">
+        <v>7.4345296829854496E-2</v>
+      </c>
+      <c r="E24">
+        <v>0.102463883691779</v>
+      </c>
+      <c r="F24">
+        <v>6.8794272485361505E-2</v>
+      </c>
+      <c r="G24">
+        <v>4.5108944009152899E-2</v>
+      </c>
+      <c r="H24">
+        <v>5.75142724214378E-2</v>
+      </c>
+      <c r="I24">
+        <v>2.9889160199140199E-2</v>
+      </c>
+      <c r="J24">
+        <v>1.4654461529923699E-2</v>
+      </c>
+      <c r="K24">
+        <v>2.122409081331E-2</v>
+      </c>
+      <c r="L24">
+        <v>1.15260639788098E-2</v>
+      </c>
+      <c r="M24">
+        <v>9.5622568692562502E-3</v>
+      </c>
+      <c r="N24">
+        <v>8.5894093412844895E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="242">
+        <v>78</v>
+      </c>
+      <c r="B25" t="s">
+        <v>402</v>
+      </c>
+      <c r="C25">
+        <v>2.1745331340848901E-2</v>
+      </c>
+      <c r="D25">
+        <v>3.11141362458126E-2</v>
+      </c>
+      <c r="E25">
+        <v>9.2245515564642597E-2</v>
+      </c>
+      <c r="F25">
+        <v>0.78561539791105395</v>
+      </c>
+      <c r="G25">
+        <v>0.28432945117601799</v>
+      </c>
+      <c r="H25">
+        <v>6.0567354785331699E-2</v>
+      </c>
+      <c r="I25">
+        <v>4.2928252536849502E-2</v>
+      </c>
+      <c r="J25">
+        <v>1.6477281753901701E-2</v>
+      </c>
+      <c r="K25">
+        <v>1.60374805524994E-2</v>
+      </c>
+      <c r="L25">
+        <v>1.4790455100104599E-2</v>
+      </c>
+      <c r="M25">
+        <v>1.35495087487986E-2</v>
+      </c>
+      <c r="N25">
+        <v>1.57083996186578E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="242">
+        <v>78</v>
+      </c>
+      <c r="B26" t="s">
+        <v>403</v>
+      </c>
+      <c r="C26">
+        <v>2.8072795598690602E-2</v>
+      </c>
+      <c r="D26">
+        <v>0.116749992195674</v>
+      </c>
+      <c r="E26">
+        <v>1.00823860797734</v>
+      </c>
+      <c r="F26">
+        <v>2.0872617399879401</v>
+      </c>
+      <c r="G26">
+        <v>3.66968479991557</v>
+      </c>
+      <c r="H26">
+        <v>0.71515902523410402</v>
+      </c>
+      <c r="I26">
+        <v>3.5785769341712501E-2</v>
+      </c>
+      <c r="J26">
+        <v>4.93519911429606E-2</v>
+      </c>
+      <c r="K26">
+        <v>5.4045045943716903E-2</v>
+      </c>
+      <c r="L26">
+        <v>4.06364474673881E-2</v>
+      </c>
+      <c r="M26">
+        <v>5.1759269605576398E-2</v>
+      </c>
+      <c r="N26">
+        <v>8.8342198974702496E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="242">
+        <v>78</v>
+      </c>
+      <c r="B27" t="s">
+        <v>404</v>
+      </c>
+      <c r="C27">
+        <v>0.10064420022575001</v>
+      </c>
+      <c r="D27">
+        <v>0.307547031805467</v>
+      </c>
+      <c r="E27">
+        <v>0.84642633369619003</v>
+      </c>
+      <c r="F27">
+        <v>3.4416804577095799</v>
+      </c>
+      <c r="G27">
+        <v>3.0011137460652901</v>
+      </c>
+      <c r="H27">
+        <v>1.72077075128541</v>
+      </c>
+      <c r="I27">
+        <v>0.40449730073011397</v>
+      </c>
+      <c r="J27">
+        <v>0.112214120711199</v>
+      </c>
+      <c r="K27">
+        <v>7.7035111085968097E-2</v>
+      </c>
+      <c r="L27">
+        <v>7.2325096159615701E-2</v>
+      </c>
+      <c r="M27">
+        <v>5.5814737400509302E-2</v>
+      </c>
+      <c r="N27">
+        <v>5.5625803717058803E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="242">
+        <v>78</v>
+      </c>
+      <c r="B28" t="s">
+        <v>405</v>
+      </c>
+      <c r="C28">
+        <v>7.3124494747050697E-2</v>
+      </c>
+      <c r="D28">
+        <v>0.36435501901154899</v>
+      </c>
+      <c r="E28">
+        <v>0.294234823490997</v>
+      </c>
+      <c r="F28">
+        <v>0.84120590312854304</v>
+      </c>
+      <c r="G28">
+        <v>1.6759462101971401</v>
+      </c>
+      <c r="H28">
+        <v>1.28411552988894</v>
+      </c>
+      <c r="I28">
+        <v>0.17531422408216199</v>
+      </c>
+      <c r="J28">
+        <v>5.6165647424153399E-2</v>
+      </c>
+      <c r="K28">
+        <v>6.9353412246889096E-2</v>
+      </c>
+      <c r="L28">
+        <v>5.4442537700265303E-2</v>
+      </c>
+      <c r="M28">
+        <v>4.4842313722694302E-2</v>
+      </c>
+      <c r="N28">
+        <v>3.91215099376407E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="242">
+        <v>78</v>
+      </c>
+      <c r="B29" t="s">
+        <v>406</v>
+      </c>
+      <c r="C29">
+        <v>3.2142404304793697E-2</v>
+      </c>
+      <c r="D29">
+        <v>0.120580670701676</v>
+      </c>
+      <c r="E29">
+        <v>0.20678155508674201</v>
+      </c>
+      <c r="F29">
+        <v>0.87480170670045498</v>
+      </c>
+      <c r="G29">
+        <v>1.3336717407897301</v>
+      </c>
+      <c r="H29">
+        <v>0.93320934261599697</v>
+      </c>
+      <c r="I29">
+        <v>0.30062763587671998</v>
+      </c>
+      <c r="J29">
+        <v>9.2984088120644501E-2</v>
+      </c>
+      <c r="K29">
+        <v>9.5989126511510703E-2</v>
+      </c>
+      <c r="L29">
+        <v>6.2864694528541501E-2</v>
+      </c>
+      <c r="M29">
+        <v>5.3044872627633598E-2</v>
+      </c>
+      <c r="N29">
+        <v>4.4095309203895899E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="242">
+        <v>78</v>
+      </c>
+      <c r="B30" t="s">
+        <v>407</v>
+      </c>
+      <c r="C30">
+        <v>7.4637121693144903E-2</v>
+      </c>
+      <c r="D30">
+        <v>8.0179577303209404E-2</v>
+      </c>
+      <c r="E30">
+        <v>0.60987858441485698</v>
+      </c>
+      <c r="F30">
+        <v>2.9524449311545098</v>
+      </c>
+      <c r="G30">
+        <v>2.5853258266073298</v>
+      </c>
+      <c r="H30">
+        <v>0.47048491809273801</v>
+      </c>
+      <c r="I30">
+        <v>0.10641260865727099</v>
+      </c>
+      <c r="J30">
+        <v>0.13257818962821699</v>
+      </c>
+      <c r="K30">
+        <v>7.0862990895886102E-2</v>
+      </c>
+      <c r="L30">
+        <v>5.5740700482016799E-2</v>
+      </c>
+      <c r="M30">
+        <v>5.4844557167800498E-2</v>
+      </c>
+      <c r="N30">
+        <v>6.8149901955512807E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="242">
+        <v>78</v>
+      </c>
+      <c r="B31" t="s">
+        <v>408</v>
+      </c>
+      <c r="C31">
+        <v>0.101044193282778</v>
+      </c>
+      <c r="D31">
+        <v>1.03768990704428</v>
+      </c>
+      <c r="E31">
+        <v>4.2278325648336699</v>
+      </c>
+      <c r="F31">
+        <v>2.21499136315107</v>
+      </c>
+      <c r="G31">
+        <v>1.4846604486569099</v>
+      </c>
+      <c r="H31">
+        <v>0.66359834478378699</v>
+      </c>
+      <c r="I31">
+        <v>0.49100862055831002</v>
+      </c>
+      <c r="J31">
+        <v>0.424591603006022</v>
+      </c>
+      <c r="K31">
+        <v>0.256865077328368</v>
+      </c>
+      <c r="L31">
+        <v>0.31048790343195298</v>
+      </c>
+      <c r="M31">
+        <v>0.17239039230696199</v>
+      </c>
+      <c r="N31">
+        <v>9.5633381375252902E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="242">
+        <v>78</v>
+      </c>
+      <c r="B32" t="s">
+        <v>409</v>
+      </c>
+      <c r="C32">
+        <v>0.39575528622164002</v>
+      </c>
+      <c r="D32">
+        <v>0.43170020360641398</v>
+      </c>
+      <c r="E32">
+        <v>2.4071672737827901</v>
+      </c>
+      <c r="F32">
+        <v>12.1521298298958</v>
+      </c>
+      <c r="G32">
+        <v>7.5030252460387299</v>
+      </c>
+      <c r="H32">
+        <v>4.75889866353877</v>
+      </c>
+      <c r="I32">
+        <v>2.5751380978009299</v>
+      </c>
+      <c r="J32">
+        <v>0.46315378652712502</v>
+      </c>
+      <c r="K32">
+        <v>0.285369624221399</v>
+      </c>
+      <c r="L32">
+        <v>0.24447031142100101</v>
+      </c>
+      <c r="M32">
+        <v>0.113328901068453</v>
+      </c>
+      <c r="N32">
+        <v>0.150037737866454</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="242">
+        <v>78</v>
+      </c>
+      <c r="B33" t="s">
+        <v>410</v>
+      </c>
+      <c r="C33">
+        <v>0.13270621597732901</v>
+      </c>
+      <c r="D33">
+        <v>0.22966911712483301</v>
+      </c>
+      <c r="E33">
+        <v>0.68504583055562396</v>
+      </c>
+      <c r="F33">
+        <v>2.4078784882360198</v>
+      </c>
+      <c r="G33">
+        <v>1.3054926930523401</v>
+      </c>
+      <c r="H33">
+        <v>0.42192743201107102</v>
+      </c>
+      <c r="I33">
+        <v>0.195834677692484</v>
+      </c>
+      <c r="J33">
+        <v>0.103486839387473</v>
+      </c>
+      <c r="K33">
+        <v>8.6496956038609296E-2</v>
+      </c>
+      <c r="L33">
+        <v>8.1572864502875403E-2</v>
+      </c>
+      <c r="M33">
+        <v>8.0034359704688099E-2</v>
+      </c>
+      <c r="N33">
+        <v>8.8068995241660897E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="242">
+        <v>78</v>
+      </c>
+      <c r="B34" t="s">
+        <v>411</v>
+      </c>
+      <c r="C34">
+        <v>6.3585231984579604E-2</v>
+      </c>
+      <c r="D34">
+        <v>0.16585973075134799</v>
+      </c>
+      <c r="E34">
+        <v>0.60500285831979494</v>
+      </c>
+      <c r="F34">
+        <v>1.22962966437445</v>
+      </c>
+      <c r="G34">
+        <v>1.3393321852475699</v>
+      </c>
+      <c r="H34">
+        <v>0.286619061077374</v>
+      </c>
+      <c r="I34">
+        <v>0.127551789068996</v>
+      </c>
+      <c r="J34">
+        <v>6.8203934842272496E-2</v>
+      </c>
+      <c r="K34">
+        <v>4.65132225378692E-2</v>
+      </c>
+      <c r="L34">
+        <v>6.0003022176277003E-2</v>
+      </c>
+      <c r="M34">
+        <v>3.7827357337903697E-2</v>
+      </c>
+      <c r="N34">
+        <v>5.4192173973870002E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="242">
+        <v>78</v>
+      </c>
+      <c r="B35" t="s">
+        <v>412</v>
+      </c>
+      <c r="C35">
+        <v>6.4596337050784797E-2</v>
+      </c>
+      <c r="D35">
+        <v>8.0009803286589104E-2</v>
+      </c>
+      <c r="E35">
+        <v>0.135240107898807</v>
+      </c>
+      <c r="F35">
+        <v>0.22667061163196001</v>
+      </c>
+      <c r="G35">
+        <v>0.11299885359734101</v>
+      </c>
+      <c r="H35">
+        <v>5.9402161079846499E-2</v>
+      </c>
+      <c r="I35">
+        <v>6.5902497780156194E-2</v>
+      </c>
+      <c r="J35">
+        <v>2.8519111112894398E-2</v>
+      </c>
+      <c r="K35">
+        <v>1.8683987955418799E-2</v>
+      </c>
+      <c r="L35">
+        <v>1.68015855164231E-2</v>
+      </c>
+      <c r="M35">
+        <v>2.1705357086557801E-2</v>
+      </c>
+      <c r="N35">
+        <v>2.1145301594404399E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="242">
+        <v>78</v>
+      </c>
+      <c r="B36" t="s">
+        <v>413</v>
+      </c>
+      <c r="C36">
+        <v>2.7159722838024401E-2</v>
+      </c>
+      <c r="D36">
+        <v>1.9077901283711399E-2</v>
+      </c>
+      <c r="E36">
+        <v>9.6899681734207196E-2</v>
+      </c>
+      <c r="F36">
+        <v>0.34311589308430002</v>
+      </c>
+      <c r="G36">
+        <v>1.5662074134694799</v>
+      </c>
+      <c r="H36">
+        <v>0.36834863252418298</v>
+      </c>
+      <c r="I36">
+        <v>0.30248625851823202</v>
+      </c>
+      <c r="J36">
+        <v>3.0376850089355801E-2</v>
+      </c>
+      <c r="K36">
+        <v>3.5130435171711702E-2</v>
+      </c>
+      <c r="L36">
+        <v>4.7581799167548899E-2</v>
+      </c>
+      <c r="M36">
+        <v>2.5521315124071201E-2</v>
+      </c>
+      <c r="N36">
+        <v>5.6847899677831201E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="242">
+        <v>78</v>
+      </c>
+      <c r="B37" t="s">
+        <v>414</v>
+      </c>
+      <c r="C37">
+        <v>9.7925132249164396E-2</v>
+      </c>
+      <c r="D37">
+        <v>1.04204253736579</v>
+      </c>
+      <c r="E37">
+        <v>3.2795908947955899</v>
+      </c>
+      <c r="F37">
+        <v>5.8043977566903298</v>
+      </c>
+      <c r="G37">
+        <v>5.9020583984646002</v>
+      </c>
+      <c r="H37">
+        <v>5.0170673272297197</v>
+      </c>
+      <c r="I37">
+        <v>0.85212723530937695</v>
+      </c>
+      <c r="J37">
+        <v>0.46442397523232098</v>
+      </c>
+      <c r="K37">
+        <v>0.18976436181328901</v>
+      </c>
+      <c r="L37">
+        <v>0.275106010185387</v>
+      </c>
+      <c r="M37">
+        <v>0.22303793525351101</v>
+      </c>
+      <c r="N37">
+        <v>0.20690721021915001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="242">
+        <v>78</v>
+      </c>
+      <c r="B38" t="s">
+        <v>415</v>
+      </c>
+      <c r="C38">
+        <v>1.58409811333643</v>
+      </c>
+      <c r="D38">
+        <v>1.9414011468179799</v>
+      </c>
+      <c r="E38">
+        <v>3.9195296568344902</v>
+      </c>
+      <c r="F38">
+        <v>4.6891937065798404</v>
+      </c>
+      <c r="G38">
+        <v>1.30312639843455</v>
+      </c>
+      <c r="H38">
+        <v>0.97839134529830196</v>
+      </c>
+      <c r="I38">
+        <v>0.18029271283140799</v>
+      </c>
+      <c r="J38">
+        <v>0.12548791756955699</v>
+      </c>
+      <c r="K38">
+        <v>0.12196408393946</v>
+      </c>
+      <c r="L38">
+        <v>8.8602096722034299E-2</v>
+      </c>
+      <c r="M38">
+        <v>7.8733285100921799E-2</v>
+      </c>
+      <c r="N38">
+        <v>0.123782669090264</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" s="242">
+        <v>78</v>
+      </c>
+      <c r="B39" t="s">
+        <v>416</v>
+      </c>
+      <c r="C39">
+        <v>7.4321500347936997E-2</v>
+      </c>
+      <c r="D39">
+        <v>0.101963376074</v>
+      </c>
+      <c r="E39">
+        <v>0.158521040921868</v>
+      </c>
+      <c r="F39">
+        <v>0.173149776711707</v>
+      </c>
+      <c r="G39">
+        <v>0.14553591736180799</v>
+      </c>
+      <c r="H39">
+        <v>6.03382475257805E-2</v>
+      </c>
+      <c r="I39">
+        <v>4.2114629165286702E-2</v>
+      </c>
+      <c r="J39">
+        <v>2.7184942781383802E-2</v>
+      </c>
+      <c r="K39">
+        <v>2.5212873075026999E-2</v>
+      </c>
+      <c r="L39">
+        <v>2.1224178471791699E-2</v>
+      </c>
+      <c r="M39">
+        <v>2.8261503868156401E-2</v>
+      </c>
+      <c r="N39">
+        <v>2.0092186801708201E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" s="242">
+        <v>78</v>
+      </c>
+      <c r="B40" t="s">
+        <v>417</v>
+      </c>
+      <c r="C40">
+        <v>2.1489869843353802E-2</v>
+      </c>
+      <c r="D40">
+        <v>2.0231554995935701E-2</v>
+      </c>
+      <c r="E40">
+        <v>7.1451606147341806E-2</v>
+      </c>
+      <c r="F40">
+        <v>6.98351447100162E-2</v>
+      </c>
+      <c r="G40">
+        <v>9.9183692290073594E-2</v>
+      </c>
+      <c r="H40">
+        <v>6.8280744073894506E-2</v>
+      </c>
+      <c r="I40">
+        <v>3.1742893139513298E-2</v>
+      </c>
+      <c r="J40">
+        <v>1.13509818790694E-2</v>
+      </c>
+      <c r="K40">
+        <v>1.01596278585428E-2</v>
+      </c>
+      <c r="L40">
+        <v>9.45183853124309E-3</v>
+      </c>
+      <c r="M40">
+        <v>7.8120836608810904E-3</v>
+      </c>
+      <c r="N40">
+        <v>7.2488341411896398E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41" s="242">
+        <v>78</v>
+      </c>
+      <c r="B41" t="s">
+        <v>418</v>
+      </c>
+      <c r="C41">
+        <v>7.2062365068604802E-3</v>
+      </c>
+      <c r="D41">
+        <v>1.9862781480841901E-2</v>
+      </c>
+      <c r="E41">
+        <v>0.16431908271468401</v>
+      </c>
+      <c r="F41">
+        <v>0.99488646559498295</v>
+      </c>
+      <c r="G41">
+        <v>3.1907483712407001</v>
+      </c>
+      <c r="H41">
+        <v>0.79837312436571894</v>
+      </c>
+      <c r="I41">
+        <v>0.14973469512641599</v>
+      </c>
+      <c r="J41">
+        <v>9.3820159980696094E-2</v>
+      </c>
+      <c r="K41">
+        <v>3.4713874209450699E-2</v>
+      </c>
+      <c r="L41">
+        <v>3.0884887469653802E-2</v>
+      </c>
+      <c r="M41">
+        <v>5.9921869033445201E-2</v>
+      </c>
+      <c r="N41">
+        <v>2.7580948632739102E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42" s="242">
+        <v>78</v>
+      </c>
+      <c r="B42" t="s">
+        <v>419</v>
+      </c>
+      <c r="C42">
+        <v>4.7835506606552301E-2</v>
+      </c>
+      <c r="D42">
+        <v>9.7674966979977698E-2</v>
+      </c>
+      <c r="E42">
+        <v>0.66292974517034697</v>
+      </c>
+      <c r="F42">
+        <v>5.6753904911634896</v>
+      </c>
+      <c r="G42">
+        <v>2.9300258827225698</v>
+      </c>
+      <c r="H42">
+        <v>0.15456668510781299</v>
+      </c>
+      <c r="I42">
+        <v>0.13573686157930401</v>
+      </c>
+      <c r="J42">
+        <v>5.5298444995634098E-2</v>
+      </c>
+      <c r="K42">
+        <v>5.5955738109474101E-2</v>
+      </c>
+      <c r="L42">
+        <v>6.1923059418348803E-2</v>
+      </c>
+      <c r="M42">
+        <v>5.0330358985890403E-2</v>
+      </c>
+      <c r="N42">
+        <v>4.9013591295297802E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43" s="242">
+        <v>78</v>
+      </c>
+      <c r="B43" t="s">
+        <v>420</v>
+      </c>
+      <c r="C43">
+        <v>5.6744985976451098E-2</v>
+      </c>
+      <c r="D43">
+        <v>4.3983172775383599E-2</v>
+      </c>
+      <c r="E43">
+        <v>5.39227267093755E-2</v>
+      </c>
+      <c r="F43">
+        <v>0.17687590016965599</v>
+      </c>
+      <c r="G43">
+        <v>0.13364143761589001</v>
+      </c>
+      <c r="H43">
+        <v>0.39902776476872598</v>
+      </c>
+      <c r="I43">
+        <v>4.1406782997389903E-2</v>
+      </c>
+      <c r="J43">
+        <v>2.0296321883852199E-2</v>
+      </c>
+      <c r="K43">
+        <v>2.03244836034948E-2</v>
+      </c>
+      <c r="L43">
+        <v>2.7129395769227099E-2</v>
+      </c>
+      <c r="M43">
+        <v>2.3032338377534801E-2</v>
+      </c>
+      <c r="N43">
+        <v>3.8493675650209898E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" s="242">
+        <v>78</v>
+      </c>
+      <c r="B44" t="s">
+        <v>421</v>
+      </c>
+      <c r="C44">
+        <v>3.7834529960498103E-2</v>
+      </c>
+      <c r="D44">
+        <v>4.1444843629438399E-2</v>
+      </c>
+      <c r="E44">
+        <v>0.19574547676170401</v>
+      </c>
+      <c r="F44">
+        <v>0.66536287638890101</v>
+      </c>
+      <c r="G44">
+        <v>0.62755615161822298</v>
+      </c>
+      <c r="H44">
+        <v>0.12448245871185</v>
+      </c>
+      <c r="I44">
+        <v>2.6703802541307199E-2</v>
+      </c>
+      <c r="J44">
+        <v>2.7809076444485801E-2</v>
+      </c>
+      <c r="K44">
+        <v>2.25253227661203E-2</v>
+      </c>
+      <c r="L44">
+        <v>2.00078962444705E-2</v>
+      </c>
+      <c r="M44">
+        <v>1.8066575722210501E-2</v>
+      </c>
+      <c r="N44">
+        <v>2.26786902735647E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45" s="242">
+        <v>78</v>
+      </c>
+      <c r="B45" t="s">
+        <v>422</v>
+      </c>
+      <c r="C45">
+        <v>1.76085596779261E-2</v>
+      </c>
+      <c r="D45">
+        <v>2.1964473233935598E-2</v>
+      </c>
+      <c r="E45">
+        <v>6.05869162776684E-2</v>
+      </c>
+      <c r="F45">
+        <v>0.19475577077591999</v>
+      </c>
+      <c r="G45">
+        <v>0.17714045700723199</v>
+      </c>
+      <c r="H45">
+        <v>0.18152701900127099</v>
+      </c>
+      <c r="I45">
+        <v>4.0057965164001202E-2</v>
+      </c>
+      <c r="J45">
+        <v>1.90036175123868E-2</v>
+      </c>
+      <c r="K45">
+        <v>1.51312655365523E-2</v>
+      </c>
+      <c r="L45">
+        <v>1.2053820500427999E-2</v>
+      </c>
+      <c r="M45">
+        <v>1.13741511299848E-2</v>
+      </c>
+      <c r="N45">
+        <v>9.7305606372879092E-3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46" s="242">
+        <v>78</v>
+      </c>
+      <c r="B46" t="s">
+        <v>423</v>
+      </c>
+      <c r="C46">
+        <v>1.21560118067949E-2</v>
+      </c>
+      <c r="D46">
+        <v>3.3919187562584698E-2</v>
+      </c>
+      <c r="E46">
+        <v>8.7074293495603403E-2</v>
+      </c>
+      <c r="F46">
+        <v>0.104727317167739</v>
+      </c>
+      <c r="G46">
+        <v>0.33055307808986201</v>
+      </c>
+      <c r="H46">
+        <v>8.6804130342439806E-2</v>
+      </c>
+      <c r="I46">
+        <v>2.7309328240080401E-2</v>
+      </c>
+      <c r="J46">
+        <v>1.41212053011409E-2</v>
+      </c>
+      <c r="K46">
+        <v>1.07768692010998E-2</v>
+      </c>
+      <c r="L46">
+        <v>1.00652991372552E-2</v>
+      </c>
+      <c r="M46">
+        <v>1.0141885397706401E-2</v>
+      </c>
+      <c r="N46">
+        <v>8.9934267556953992E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" s="242">
+        <v>78</v>
+      </c>
+      <c r="B47" t="s">
+        <v>424</v>
+      </c>
+      <c r="C47">
+        <v>1.9468787371344099E-2</v>
+      </c>
+      <c r="D47">
+        <v>2.5967094342236499E-2</v>
+      </c>
+      <c r="E47">
+        <v>8.4806799349849596E-2</v>
+      </c>
+      <c r="F47">
+        <v>0.46118655135154801</v>
+      </c>
+      <c r="G47">
+        <v>0.89999653084467401</v>
+      </c>
+      <c r="H47">
+        <v>0.14986031318504101</v>
+      </c>
+      <c r="I47">
+        <v>3.6140243611546698E-2</v>
+      </c>
+      <c r="J47">
+        <v>3.05716866545752E-2</v>
+      </c>
+      <c r="K47">
+        <v>1.7407457394688498E-2</v>
+      </c>
+      <c r="L47">
+        <v>2.8889543602096401E-2</v>
+      </c>
+      <c r="M47">
+        <v>1.6640438351316601E-2</v>
+      </c>
+      <c r="N47">
+        <v>3.0828160221393099E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" s="242">
+        <v>78</v>
+      </c>
+      <c r="B48" t="s">
+        <v>425</v>
+      </c>
+      <c r="C48">
+        <v>1.80384931326346E-2</v>
+      </c>
+      <c r="D48">
+        <v>9.3514774152272898E-2</v>
+      </c>
+      <c r="E48">
+        <v>0.30933401014540601</v>
+      </c>
+      <c r="F48">
+        <v>1.1139751550320101</v>
+      </c>
+      <c r="G48">
+        <v>0.38107012311292998</v>
+      </c>
+      <c r="H48">
+        <v>0.16478768912299299</v>
+      </c>
+      <c r="I48">
+        <v>0.100273295323297</v>
+      </c>
+      <c r="J48">
+        <v>9.6372220855391502E-2</v>
+      </c>
+      <c r="K48">
+        <v>2.92464706516628E-2</v>
+      </c>
+      <c r="L48">
+        <v>2.4592068290253299E-2</v>
+      </c>
+      <c r="M48">
+        <v>2.0171087008254401E-2</v>
+      </c>
+      <c r="N48">
+        <v>2.5066270492301999E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49" s="242">
+        <v>78</v>
+      </c>
+      <c r="B49" t="s">
+        <v>426</v>
+      </c>
+      <c r="C49">
+        <v>5.3119329681082003E-2</v>
+      </c>
+      <c r="D49">
+        <v>2.2386374736574899E-2</v>
+      </c>
+      <c r="E49">
+        <v>0.31139258136423997</v>
+      </c>
+      <c r="F49">
+        <v>2.0290453399307</v>
+      </c>
+      <c r="G49">
+        <v>0.73081887139313295</v>
+      </c>
+      <c r="H49">
+        <v>0.204081498120816</v>
+      </c>
+      <c r="I49">
+        <v>5.8928876646161601E-2</v>
+      </c>
+      <c r="J49">
+        <v>3.06833984227474E-2</v>
+      </c>
+      <c r="K49">
+        <v>3.5366336186105102E-2</v>
+      </c>
+      <c r="L49">
+        <v>2.79171503938738E-2</v>
+      </c>
+      <c r="M49">
+        <v>2.5014239027914401E-2</v>
+      </c>
+      <c r="N49">
+        <v>2.7998979660039999E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50" s="242">
+        <v>78</v>
+      </c>
+      <c r="B50" t="s">
+        <v>427</v>
+      </c>
+      <c r="C50">
+        <v>2.4348557607784101E-2</v>
+      </c>
+      <c r="D50">
+        <v>2.52213736495745E-2</v>
+      </c>
+      <c r="E50">
+        <v>3.4071541767393403E-2</v>
+      </c>
+      <c r="F50">
+        <v>3.0451586535849898E-2</v>
+      </c>
+      <c r="G50">
+        <v>7.8335130658322205E-2</v>
+      </c>
+      <c r="H50">
+        <v>2.6540878327035701E-2</v>
+      </c>
+      <c r="I50">
+        <v>3.4344755028727698E-2</v>
+      </c>
+      <c r="J50">
+        <v>9.5643686273697397E-3</v>
+      </c>
+      <c r="K50">
+        <v>8.3211631312687107E-3</v>
+      </c>
+      <c r="L50">
+        <v>7.2530743749245497E-3</v>
+      </c>
+      <c r="M50">
+        <v>6.6900952156447504E-3</v>
+      </c>
+      <c r="N50">
+        <v>7.2490285129727999E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A51" s="242">
+        <v>78</v>
+      </c>
+      <c r="B51" t="s">
+        <v>428</v>
+      </c>
+      <c r="C51">
+        <v>2.1167361109834599E-2</v>
+      </c>
+      <c r="D51">
+        <v>6.4097357717601694E-2</v>
+      </c>
+      <c r="E51">
+        <v>0.37960122845538402</v>
+      </c>
+      <c r="F51">
+        <v>0.58136278954435705</v>
+      </c>
+      <c r="G51">
+        <v>0.98580872011250498</v>
+      </c>
+      <c r="H51">
+        <v>0.47178675799775699</v>
+      </c>
+      <c r="I51">
+        <v>0.107889248058752</v>
+      </c>
+      <c r="J51">
+        <v>4.6247461533352199E-2</v>
+      </c>
+      <c r="K51">
+        <v>2.1308913389343799E-2</v>
+      </c>
+      <c r="L51">
+        <v>1.98203444698653E-2</v>
+      </c>
+      <c r="M51">
+        <v>1.9920320466938E-2</v>
+      </c>
+      <c r="N51">
+        <v>1.7328220238339801E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A52" s="242">
+        <v>78</v>
+      </c>
+      <c r="B52" t="s">
+        <v>429</v>
+      </c>
+      <c r="C52">
+        <v>1.8095308336139398E-2</v>
+      </c>
+      <c r="D52">
+        <v>1.8131364566605801E-2</v>
+      </c>
+      <c r="E52">
+        <v>0.23586203643732701</v>
+      </c>
+      <c r="F52">
+        <v>0.75305733834689104</v>
+      </c>
+      <c r="G52">
+        <v>0.299105552760075</v>
+      </c>
+      <c r="H52">
+        <v>0.20656347394576499</v>
+      </c>
+      <c r="I52">
+        <v>9.6271660868584505E-2</v>
+      </c>
+      <c r="J52">
+        <v>3.26533731456667E-2</v>
+      </c>
+      <c r="K52">
+        <v>1.9715998044754199E-2</v>
+      </c>
+      <c r="L52">
+        <v>1.96063848274893E-2</v>
+      </c>
+      <c r="M52">
+        <v>1.69646243651662E-2</v>
+      </c>
+      <c r="N52">
+        <v>2.0805197021378601E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A53" s="242">
+        <v>78</v>
+      </c>
+      <c r="B53" t="s">
+        <v>430</v>
+      </c>
+      <c r="C53">
+        <v>4.7752277422178899E-2</v>
+      </c>
+      <c r="D53">
+        <v>0.30448616269210599</v>
+      </c>
+      <c r="E53">
+        <v>1.6008432330603399</v>
+      </c>
+      <c r="F53">
+        <v>3.6720143468898701</v>
+      </c>
+      <c r="G53">
+        <v>2.1563560463274598</v>
+      </c>
+      <c r="H53">
+        <v>0.97997085254666305</v>
+      </c>
+      <c r="I53">
+        <v>0.37605031829409002</v>
+      </c>
+      <c r="J53">
+        <v>8.1908236547066707E-2</v>
+      </c>
+      <c r="K53">
+        <v>5.92967942645269E-2</v>
+      </c>
+      <c r="L53">
+        <v>6.37131031492425E-2</v>
+      </c>
+      <c r="M53">
+        <v>4.8587248048306601E-2</v>
+      </c>
+      <c r="N53">
+        <v>6.5609758561570697E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A54" s="242">
+        <v>78</v>
+      </c>
+      <c r="B54" t="s">
+        <v>431</v>
+      </c>
+      <c r="C54">
+        <v>0.10049456902272901</v>
+      </c>
+      <c r="D54">
+        <v>0.169184027493999</v>
+      </c>
+      <c r="E54">
+        <v>1.30315563406132</v>
+      </c>
+      <c r="F54">
+        <v>3.0728809789281302</v>
+      </c>
+      <c r="G54">
+        <v>2.0064024255887798</v>
+      </c>
+      <c r="H54">
+        <v>0.51532848472571302</v>
+      </c>
+      <c r="I54">
+        <v>0.24582738439075999</v>
+      </c>
+      <c r="J54">
+        <v>8.9602120859270204E-2</v>
+      </c>
+      <c r="K54">
+        <v>0.10283351102048301</v>
+      </c>
+      <c r="L54">
+        <v>5.8708812698693102E-2</v>
+      </c>
+      <c r="M54">
+        <v>9.5805467705057601E-2</v>
+      </c>
+      <c r="N54">
+        <v>9.7173227119144404E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A55" s="242">
+        <v>78</v>
+      </c>
+      <c r="B55" t="s">
+        <v>432</v>
+      </c>
+      <c r="C55">
+        <v>0.27099307969545799</v>
+      </c>
+      <c r="D55">
+        <v>0.45088441243266603</v>
+      </c>
+      <c r="E55">
+        <v>2.9111054601301798</v>
+      </c>
+      <c r="F55">
+        <v>3.4647632366283898</v>
+      </c>
+      <c r="G55">
+        <v>1.2294722844280701</v>
+      </c>
+      <c r="H55">
+        <v>0.23852955086618599</v>
+      </c>
+      <c r="I55">
+        <v>0.11374775167852599</v>
+      </c>
+      <c r="J55">
+        <v>8.2703716488141704E-2</v>
+      </c>
+      <c r="K55">
+        <v>6.1418918543978802E-2</v>
+      </c>
+      <c r="L55">
+        <v>5.6230696060890803E-2</v>
+      </c>
+      <c r="M55">
+        <v>0.10929891131342601</v>
+      </c>
+      <c r="N55">
+        <v>0.20178157354809501</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A56" s="242">
+        <v>78</v>
+      </c>
+      <c r="B56" t="s">
+        <v>433</v>
+      </c>
+      <c r="C56">
+        <v>0.77759276974789304</v>
+      </c>
+      <c r="D56">
+        <v>4.24795324564605</v>
+      </c>
+      <c r="E56">
+        <v>7.4886735561092399</v>
+      </c>
+      <c r="F56">
+        <v>13.235099649123301</v>
+      </c>
+      <c r="G56">
+        <v>6.8159741915246199</v>
+      </c>
+      <c r="H56">
+        <v>1.6715507208357501</v>
+      </c>
+      <c r="I56">
+        <v>1.2591173837238301</v>
+      </c>
+      <c r="J56">
+        <v>0.50275774630563996</v>
+      </c>
+      <c r="K56">
+        <v>0.50647982402723102</v>
+      </c>
+      <c r="L56">
+        <v>0.16059705720364301</v>
+      </c>
+      <c r="M56">
+        <v>0.121321277673304</v>
+      </c>
+      <c r="N56">
+        <v>0.12787174799752299</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A57" s="242">
+        <v>78</v>
+      </c>
+      <c r="B57" t="s">
+        <v>434</v>
+      </c>
+      <c r="C57">
+        <v>0.21398652886272501</v>
+      </c>
+      <c r="D57">
+        <v>0.153947921862613</v>
+      </c>
+      <c r="E57">
+        <v>0.456631808695591</v>
+      </c>
+      <c r="F57">
+        <v>2.6004570202663202</v>
+      </c>
+      <c r="G57">
+        <v>3.3824047878485901</v>
+      </c>
+      <c r="H57">
+        <v>3.9666684543225101</v>
+      </c>
+      <c r="I57">
+        <v>0.98574974091598599</v>
+      </c>
+      <c r="J57">
+        <v>0.12832429151136099</v>
+      </c>
+      <c r="K57">
+        <v>0.13262467153500801</v>
+      </c>
+      <c r="L57">
+        <v>0.14197634646187199</v>
+      </c>
+      <c r="M57">
+        <v>7.9155389901167203E-2</v>
+      </c>
+      <c r="N57">
+        <v>9.1888295349324897E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A58" s="242">
+        <v>78</v>
+      </c>
+      <c r="B58" t="s">
+        <v>435</v>
+      </c>
+      <c r="C58">
+        <v>7.1380747927769106E-2</v>
+      </c>
+      <c r="D58">
+        <v>0.17204529633709301</v>
+      </c>
+      <c r="E58">
+        <v>0.199031132301869</v>
+      </c>
+      <c r="F58">
+        <v>0.47683628333443401</v>
+      </c>
+      <c r="G58">
+        <v>0.610860348189049</v>
+      </c>
+      <c r="H58">
+        <v>0.303471293449048</v>
+      </c>
+      <c r="I58">
+        <v>0.28981051372504801</v>
+      </c>
+      <c r="J58">
+        <v>7.7940908675009801E-2</v>
+      </c>
+      <c r="K58">
+        <v>7.30912248916189E-2</v>
+      </c>
+      <c r="L58">
+        <v>3.9858577020535003E-2</v>
+      </c>
+      <c r="M58">
+        <v>4.59257315853333E-2</v>
+      </c>
+      <c r="N58">
+        <v>3.9900711024302801E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A59" s="242">
+        <v>78</v>
+      </c>
+      <c r="B59" t="s">
+        <v>436</v>
+      </c>
+      <c r="C59">
+        <v>4.3576184047698703E-2</v>
+      </c>
+      <c r="D59">
+        <v>0.34974652547065899</v>
+      </c>
+      <c r="E59">
+        <v>1.3126351704247201</v>
+      </c>
+      <c r="F59">
+        <v>4.6164930198382104</v>
+      </c>
+      <c r="G59">
+        <v>5.0550726442120304</v>
+      </c>
+      <c r="H59">
+        <v>1.4133266043761501</v>
+      </c>
+      <c r="I59">
+        <v>0.52838601213254699</v>
+      </c>
+      <c r="J59">
+        <v>0.22267337910044199</v>
+      </c>
+      <c r="K59">
+        <v>8.7232602031738396E-2</v>
+      </c>
+      <c r="L59">
+        <v>7.5699038088030093E-2</v>
+      </c>
+      <c r="M59">
+        <v>6.4064706579255407E-2</v>
+      </c>
+      <c r="N59">
+        <v>7.4428180348725406E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A60" s="242">
+        <v>78</v>
+      </c>
+      <c r="B60" t="s">
+        <v>437</v>
+      </c>
+      <c r="C60">
+        <v>0.118099173469667</v>
+      </c>
+      <c r="D60">
+        <v>0.12887913930358599</v>
+      </c>
+      <c r="E60">
+        <v>0.67586247677580502</v>
+      </c>
+      <c r="F60">
+        <v>1.46828060294194</v>
+      </c>
+      <c r="G60">
+        <v>3.6560504588327798</v>
+      </c>
+      <c r="H60">
+        <v>0.49433923586078699</v>
+      </c>
+      <c r="I60">
+        <v>0.58657476362420202</v>
+      </c>
+      <c r="J60">
+        <v>9.1858536729153201E-2</v>
+      </c>
+      <c r="K60">
+        <v>5.7400345153260597E-2</v>
+      </c>
+      <c r="L60">
+        <v>7.3140419016843705E-2</v>
+      </c>
+      <c r="M60">
+        <v>5.5060077585221703E-2</v>
+      </c>
+      <c r="N60">
+        <v>9.6400997024740795E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A61" s="242">
+        <v>78</v>
+      </c>
+      <c r="B61" t="s">
+        <v>438</v>
+      </c>
+      <c r="C61">
+        <v>8.7818865954976497E-2</v>
+      </c>
+      <c r="D61">
+        <v>0.122791753151172</v>
+      </c>
+      <c r="E61">
+        <v>0.67365999677743005</v>
+      </c>
+      <c r="F61">
+        <v>3.7067722027508601</v>
+      </c>
+      <c r="G61">
+        <v>2.5762913173836099</v>
+      </c>
+      <c r="H61">
+        <v>2.0173243845270599</v>
+      </c>
+      <c r="I61">
+        <v>2.7943617259687401</v>
+      </c>
+      <c r="J61">
+        <v>0.426729002910961</v>
+      </c>
+      <c r="K61">
+        <v>0.12037873481127601</v>
+      </c>
+      <c r="L61">
+        <v>0.12910165678063101</v>
+      </c>
+      <c r="M61">
+        <v>7.5340873842615702E-2</v>
+      </c>
+      <c r="N61">
+        <v>0.109646810867364</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A62" s="242">
+        <v>78</v>
+      </c>
+      <c r="B62" t="s">
+        <v>439</v>
+      </c>
+      <c r="C62">
+        <v>0.22194988676704899</v>
+      </c>
+      <c r="D62">
+        <v>0.13575417731004699</v>
+      </c>
+      <c r="E62">
+        <v>0.60644666937208003</v>
+      </c>
+      <c r="F62">
+        <v>1.86530748319814</v>
+      </c>
+      <c r="G62">
+        <v>0.90087345696963805</v>
+      </c>
+      <c r="H62">
+        <v>0.50060402163016104</v>
+      </c>
+      <c r="I62">
+        <v>0.223935547282891</v>
+      </c>
+      <c r="J62">
+        <v>0.12150690438891899</v>
+      </c>
+      <c r="K62">
+        <v>5.60554412060357E-2</v>
+      </c>
+      <c r="L62">
+        <v>5.3852691392248603E-2</v>
+      </c>
+      <c r="M62">
+        <v>7.1406651726806103E-2</v>
+      </c>
+      <c r="N62">
+        <v>6.0510279413919503E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A63" s="242">
+        <v>78</v>
+      </c>
+      <c r="B63" t="s">
+        <v>440</v>
+      </c>
+      <c r="C63">
+        <v>0.123516505359266</v>
+      </c>
+      <c r="D63">
+        <v>0.14904157497536799</v>
+      </c>
+      <c r="E63">
+        <v>0.66463621019381203</v>
+      </c>
+      <c r="F63">
+        <v>1.5322472458707901</v>
+      </c>
+      <c r="G63">
+        <v>2.9358349642117001</v>
+      </c>
+      <c r="H63">
+        <v>1.86375807653406</v>
+      </c>
+      <c r="I63">
+        <v>1.82398771733377</v>
+      </c>
+      <c r="J63">
+        <v>0.23460453473977699</v>
+      </c>
+      <c r="K63">
+        <v>0.108952609745114</v>
+      </c>
+      <c r="L63">
+        <v>0.21848868239864599</v>
+      </c>
+      <c r="M63">
+        <v>0.109051055485722</v>
+      </c>
+      <c r="N63">
+        <v>0.118833273626751</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A64" s="242">
+        <v>78</v>
+      </c>
+      <c r="B64" t="s">
+        <v>441</v>
+      </c>
+      <c r="C64">
+        <v>0.115819901977427</v>
+      </c>
+      <c r="D64">
+        <v>0.15853819317047599</v>
+      </c>
+      <c r="E64">
+        <v>0.36340707598599897</v>
+      </c>
+      <c r="F64">
+        <v>0.48173506572528302</v>
+      </c>
+      <c r="G64">
+        <v>0.90163680297905702</v>
+      </c>
+      <c r="H64">
+        <v>0.73070947988220902</v>
+      </c>
+      <c r="I64">
+        <v>0.56645263037531002</v>
+      </c>
+      <c r="J64">
+        <v>0.26127250738937902</v>
+      </c>
+      <c r="K64">
+        <v>5.1536607864898699E-2</v>
+      </c>
+      <c r="L64">
+        <v>6.5142517681728004E-2</v>
+      </c>
+      <c r="M64">
+        <v>4.5226985393565997E-2</v>
+      </c>
+      <c r="N64">
+        <v>9.0568792941725901E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A65" s="242">
+        <v>78</v>
+      </c>
+      <c r="B65" t="s">
+        <v>442</v>
+      </c>
+      <c r="C65">
+        <v>0.15398966214121801</v>
+      </c>
+      <c r="D65">
+        <v>0.495553857760342</v>
+      </c>
+      <c r="E65">
+        <v>1.62216695381061</v>
+      </c>
+      <c r="F65">
+        <v>4.7793925879207197</v>
+      </c>
+      <c r="G65">
+        <v>4.2199918929020903</v>
+      </c>
+      <c r="H65">
+        <v>3.74263233958342</v>
+      </c>
+      <c r="I65">
+        <v>1.4534525824662099</v>
+      </c>
+      <c r="J65">
+        <v>0.23543204005056001</v>
+      </c>
+      <c r="K65">
+        <v>0.23212682081914099</v>
+      </c>
+      <c r="L65">
+        <v>0.12983802470745301</v>
+      </c>
+      <c r="M65">
+        <v>0.108835620456582</v>
+      </c>
+      <c r="N65">
+        <v>0.12663703545528299</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A66" s="242">
+        <v>78</v>
+      </c>
+      <c r="B66" t="s">
+        <v>443</v>
+      </c>
+      <c r="C66">
+        <v>0.94525377973783198</v>
+      </c>
+      <c r="D66">
+        <v>1.5384009699677801</v>
+      </c>
+      <c r="E66">
+        <v>6.5127559819072101</v>
+      </c>
+      <c r="F66">
+        <v>16.8710514624279</v>
+      </c>
+      <c r="G66">
+        <v>9.2259020781652392</v>
+      </c>
+      <c r="H66">
+        <v>2.6453040923547602</v>
+      </c>
+      <c r="I66">
+        <v>0.65776561421117197</v>
+      </c>
+      <c r="J66">
+        <v>0.29009316314009498</v>
+      </c>
+      <c r="K66">
+        <v>0.40843143307074598</v>
+      </c>
+      <c r="L66">
+        <v>0.17354101140827</v>
+      </c>
+      <c r="M66">
+        <v>0.13417266624616001</v>
+      </c>
+      <c r="N66">
+        <v>0.26212922486870999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A67" s="242">
+        <v>78</v>
+      </c>
+      <c r="B67" t="s">
+        <v>444</v>
+      </c>
+      <c r="C67">
+        <v>0.23998192616512401</v>
+      </c>
+      <c r="D67">
+        <v>0.50605297178546704</v>
+      </c>
+      <c r="E67">
+        <v>1.9653494542650201</v>
+      </c>
+      <c r="F67">
+        <v>2.5932660084413901</v>
+      </c>
+      <c r="G67">
+        <v>4.3300902002697903</v>
+      </c>
+      <c r="H67">
+        <v>2.5873158186449001</v>
+      </c>
+      <c r="I67">
+        <v>1.3888530379025701</v>
+      </c>
+      <c r="J67">
+        <v>0.31403382086682702</v>
+      </c>
+      <c r="K67">
+        <v>0.25463748913346401</v>
+      </c>
+      <c r="L67">
+        <v>0.147273413373913</v>
+      </c>
+      <c r="M67">
+        <v>0.120356308988085</v>
+      </c>
+      <c r="N67">
+        <v>0.32938227008458998</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A68" s="242">
+        <v>78</v>
+      </c>
+      <c r="B68" t="s">
+        <v>445</v>
+      </c>
+      <c r="C68">
+        <v>0.20885559341691101</v>
+      </c>
+      <c r="D68">
+        <v>0.62869534705736196</v>
+      </c>
+      <c r="E68">
+        <v>2.2368699324863099</v>
+      </c>
+      <c r="F68">
+        <v>3.9459142993065699</v>
+      </c>
+      <c r="G68">
+        <v>0.84293653598031104</v>
+      </c>
+      <c r="H68">
+        <v>0.554473931903116</v>
+      </c>
+      <c r="I68">
+        <v>0.130859065878002</v>
+      </c>
+      <c r="J68">
+        <v>0.17674560084152399</v>
+      </c>
+      <c r="K68">
+        <v>8.3355222167560306E-2</v>
+      </c>
+      <c r="L68">
+        <v>0.153087599412803</v>
+      </c>
+      <c r="M68">
+        <v>9.4148306351743705E-2</v>
+      </c>
+      <c r="N68">
+        <v>6.1517464696260099E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69" s="242">
+        <v>78</v>
+      </c>
+      <c r="B69" t="s">
+        <v>446</v>
+      </c>
+      <c r="C69">
+        <v>0.27588050763571398</v>
+      </c>
+      <c r="D69">
+        <v>0.49256002462415299</v>
+      </c>
+      <c r="E69">
+        <v>2.5561870365869002</v>
+      </c>
+      <c r="F69">
+        <v>4.0094175501745797</v>
+      </c>
+      <c r="G69">
+        <v>3.3931530931315099</v>
+      </c>
+      <c r="H69">
+        <v>4.2321201518791396</v>
+      </c>
+      <c r="I69">
+        <v>2.4033495600153598</v>
+      </c>
+      <c r="J69">
+        <v>0.25742837119828299</v>
+      </c>
+      <c r="K69">
+        <v>0.113016444913259</v>
+      </c>
+      <c r="L69">
+        <v>0.12797401160126601</v>
+      </c>
+      <c r="M69">
+        <v>9.9322427004293196E-2</v>
+      </c>
+      <c r="N69">
+        <v>0.109513051008973</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A70" s="242">
+        <v>78</v>
+      </c>
+      <c r="B70" t="s">
+        <v>447</v>
+      </c>
+      <c r="C70">
+        <v>0.102581381944597</v>
+      </c>
+      <c r="D70">
+        <v>0.31714416057678302</v>
+      </c>
+      <c r="E70">
+        <v>0.62122295069938205</v>
+      </c>
+      <c r="F70">
+        <v>1.4282882941533399</v>
+      </c>
+      <c r="G70">
+        <v>3.16490013940001</v>
+      </c>
+      <c r="H70">
+        <v>0.72224074812274996</v>
+      </c>
+      <c r="I70">
+        <v>0.540360014434072</v>
+      </c>
+      <c r="J70">
+        <v>0.141239002485988</v>
+      </c>
+      <c r="K70">
+        <v>0.114629808326279</v>
+      </c>
+      <c r="L70">
+        <v>0.124105500035643</v>
+      </c>
+      <c r="M70">
+        <v>8.1535439097244394E-2</v>
+      </c>
+      <c r="N70">
+        <v>7.8574777614326102E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A71" s="242">
+        <v>78</v>
+      </c>
+      <c r="B71" t="s">
+        <v>448</v>
+      </c>
+      <c r="C71">
+        <v>0.127462129467978</v>
+      </c>
+      <c r="D71">
+        <v>0.23330228073003301</v>
+      </c>
+      <c r="E71">
+        <v>0.45338916896775999</v>
+      </c>
+      <c r="F71">
+        <v>0.975663755668704</v>
+      </c>
+      <c r="G71">
+        <v>1.1767837751369301</v>
+      </c>
+      <c r="H71">
+        <v>0.49579616077042099</v>
+      </c>
+      <c r="I71">
+        <v>0.109213765774216</v>
+      </c>
+      <c r="J71">
+        <v>0.12544853307693801</v>
+      </c>
+      <c r="K71">
+        <v>0.14889449279835801</v>
+      </c>
+      <c r="L71">
+        <v>4.7222084593742802E-2</v>
+      </c>
+      <c r="M71">
+        <v>4.9896397845708998E-2</v>
+      </c>
+      <c r="N71">
+        <v>3.4167092384933602E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A72" s="242">
+        <v>78</v>
+      </c>
+      <c r="B72" t="s">
+        <v>449</v>
+      </c>
+      <c r="C72">
+        <v>8.8388190769932207E-2</v>
+      </c>
+      <c r="D72">
+        <v>0.80384828958765697</v>
+      </c>
+      <c r="E72">
+        <v>1.9772293444568001</v>
+      </c>
+      <c r="F72">
+        <v>0.991793373997366</v>
+      </c>
+      <c r="G72">
+        <v>0.48956975826068799</v>
+      </c>
+      <c r="H72">
+        <v>0.47143621959172599</v>
+      </c>
+      <c r="I72">
+        <v>8.1959637252463802E-2</v>
+      </c>
+      <c r="J72">
+        <v>5.7682140702381798E-2</v>
+      </c>
+      <c r="K72">
+        <v>7.78881606826827E-2</v>
+      </c>
+      <c r="L72">
+        <v>6.7769458421885004E-2</v>
+      </c>
+      <c r="M72">
+        <v>4.2687004780538503E-2</v>
+      </c>
+      <c r="N72">
+        <v>5.3583223144303402E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A73" s="242">
+        <v>78</v>
+      </c>
+      <c r="B73" t="s">
+        <v>450</v>
+      </c>
+      <c r="C73">
+        <v>5.61842171034607E-2</v>
+      </c>
+      <c r="D73">
+        <v>4.9659672298297902E-2</v>
+      </c>
+      <c r="E73">
+        <v>0.44905407424218102</v>
+      </c>
+      <c r="F73">
+        <v>0.54521747236323004</v>
+      </c>
+      <c r="G73">
+        <v>0.484519406586983</v>
+      </c>
+      <c r="H73">
+        <v>0.16486749269821999</v>
+      </c>
+      <c r="I73">
+        <v>2.7030414697030498E-2</v>
+      </c>
+      <c r="J73">
+        <v>2.76500476340222E-2</v>
+      </c>
+      <c r="K73">
+        <v>2.6270218928672501E-2</v>
+      </c>
+      <c r="L73">
+        <v>2.4325953196800601E-2</v>
+      </c>
+      <c r="M73">
+        <v>2.3588175106094501E-2</v>
+      </c>
+      <c r="N73">
+        <v>4.0804803414338002E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A74" s="242">
+        <v>78</v>
+      </c>
+      <c r="B74" t="s">
+        <v>451</v>
+      </c>
+      <c r="C74">
+        <v>6.1793429019901001E-2</v>
+      </c>
+      <c r="D74">
+        <v>7.4771522635261406E-2</v>
+      </c>
+      <c r="E74">
+        <v>0.42592762381148103</v>
+      </c>
+      <c r="F74">
+        <v>0.86174687401556804</v>
+      </c>
+      <c r="G74">
+        <v>1.45636315342987</v>
+      </c>
+      <c r="H74">
+        <v>0.50220498099716104</v>
+      </c>
+      <c r="I74">
+        <v>0.24041955379499899</v>
+      </c>
+      <c r="J74">
+        <v>0.11698465302592299</v>
+      </c>
+      <c r="K74">
+        <v>6.4405965672373805E-2</v>
+      </c>
+      <c r="L74">
+        <v>4.9127624722865797E-2</v>
+      </c>
+      <c r="M74">
+        <v>4.3505684935068699E-2</v>
+      </c>
+      <c r="N74">
+        <v>3.84090171678819E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A75" s="242">
+        <v>78</v>
+      </c>
+      <c r="B75" t="s">
+        <v>452</v>
+      </c>
+      <c r="C75">
+        <v>2.9523168361807801E-2</v>
+      </c>
+      <c r="D75">
+        <v>0.128377773815225</v>
+      </c>
+      <c r="E75">
+        <v>0.20804405880893001</v>
+      </c>
+      <c r="F75">
+        <v>0.228531260806491</v>
+      </c>
+      <c r="G75">
+        <v>0.19546203628682199</v>
+      </c>
+      <c r="H75">
+        <v>4.4072724876541097E-2</v>
+      </c>
+      <c r="I75">
+        <v>2.6456984426647401E-2</v>
+      </c>
+      <c r="J75">
+        <v>2.5740028724226999E-2</v>
+      </c>
+      <c r="K75">
+        <v>2.1195391930718101E-2</v>
+      </c>
+      <c r="L75">
+        <v>1.99848656228056E-2</v>
+      </c>
+      <c r="M75">
+        <v>1.38832289558231E-2</v>
+      </c>
+      <c r="N75">
+        <v>1.3267177114591199E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A76" s="242">
+        <v>78</v>
+      </c>
+      <c r="B76" t="s">
+        <v>453</v>
+      </c>
+      <c r="C76">
+        <v>1.79076892414076E-2</v>
+      </c>
+      <c r="D76">
+        <v>4.50734341306194E-2</v>
+      </c>
+      <c r="E76">
+        <v>0.282830902646445</v>
+      </c>
+      <c r="F76">
+        <v>1.1428017573604701</v>
+      </c>
+      <c r="G76">
+        <v>4.0654597720216197</v>
+      </c>
+      <c r="H76">
+        <v>2.2039231647371702</v>
+      </c>
+      <c r="I76">
+        <v>1.2133646444664901</v>
+      </c>
+      <c r="J76">
+        <v>0.36055583821667198</v>
+      </c>
+      <c r="K76">
+        <v>0.225308895392025</v>
+      </c>
+      <c r="L76">
+        <v>0.13877459381128199</v>
+      </c>
+      <c r="M76">
+        <v>6.5954490178279798E-2</v>
+      </c>
+      <c r="N76">
+        <v>7.7563476141919205E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A77" s="242">
+        <v>78</v>
+      </c>
+      <c r="B77" t="s">
+        <v>454</v>
+      </c>
+      <c r="C77">
+        <v>0.36733514795991901</v>
+      </c>
+      <c r="D77">
+        <v>1.5481097031247699</v>
+      </c>
+      <c r="E77">
+        <v>8.2808648548837507</v>
+      </c>
+      <c r="F77">
+        <v>9.8140445498952307</v>
+      </c>
+      <c r="G77">
+        <v>7.4399204484591097</v>
+      </c>
+      <c r="H77">
+        <v>6.1575135975613096</v>
+      </c>
+      <c r="I77">
+        <v>3.47125626732841</v>
+      </c>
+      <c r="J77">
+        <v>0.67998591660611296</v>
+      </c>
+      <c r="K77">
+        <v>0.27576593861090998</v>
+      </c>
+      <c r="L77">
+        <v>0.14626976488240701</v>
+      </c>
+      <c r="M77">
+        <v>0.147970584099786</v>
+      </c>
+      <c r="N77">
+        <v>0.38210491944488401</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A78" s="242">
+        <v>78</v>
+      </c>
+      <c r="B78" t="s">
+        <v>455</v>
+      </c>
+      <c r="C78">
+        <v>0.38381768619804801</v>
+      </c>
+      <c r="D78">
+        <v>1.2103053397847601</v>
+      </c>
+      <c r="E78">
+        <v>7.8740107898098604</v>
+      </c>
+      <c r="F78">
+        <v>12.5937054175009</v>
+      </c>
+      <c r="G78">
+        <v>4.4268704870463802</v>
+      </c>
+      <c r="H78">
+        <v>3.6945744105488099</v>
+      </c>
+      <c r="I78">
+        <v>0.831628822572413</v>
+      </c>
+      <c r="J78">
+        <v>0.46275984958182098</v>
+      </c>
+      <c r="K78">
+        <v>0.23104406917376599</v>
+      </c>
+      <c r="L78">
+        <v>0.23461150127661201</v>
+      </c>
+      <c r="M78">
+        <v>0.26886452476172001</v>
+      </c>
+      <c r="N78">
+        <v>0.24031049187916001</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A79" s="242">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>456</v>
+      </c>
+      <c r="C79">
+        <v>0.219757963523278</v>
+      </c>
+      <c r="D79">
+        <v>0.33434686746366798</v>
+      </c>
+      <c r="E79">
+        <v>1.4766911281667401</v>
+      </c>
+      <c r="F79">
+        <v>1.9992647295983299</v>
+      </c>
+      <c r="G79">
+        <v>0.68202010862415896</v>
+      </c>
+      <c r="H79">
+        <v>3.5041713184427299</v>
+      </c>
+      <c r="I79">
+        <v>0.41687558397181701</v>
+      </c>
+      <c r="J79">
+        <v>0.107385051693691</v>
+      </c>
+      <c r="K79">
+        <v>0.11739175480683001</v>
+      </c>
+      <c r="L79">
+        <v>8.8583658700123205E-2</v>
+      </c>
+      <c r="M79">
+        <v>9.9056720225807304E-2</v>
+      </c>
+      <c r="N79">
+        <v>6.2064962849041803E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A80" s="242">
+        <v>78</v>
+      </c>
+      <c r="B80" t="s">
+        <v>457</v>
+      </c>
+      <c r="C80">
+        <v>0.23446061690570599</v>
+      </c>
+      <c r="D80">
+        <v>0.28263693610076601</v>
+      </c>
+      <c r="E80">
+        <v>0.74919948039245798</v>
+      </c>
+      <c r="F80">
+        <v>5.1076842760025301</v>
+      </c>
+      <c r="G80">
+        <v>5.3719188900807504</v>
+      </c>
+      <c r="H80">
+        <v>2.1199057677209399</v>
+      </c>
+      <c r="I80">
+        <v>1.0361578664047599</v>
+      </c>
+      <c r="J80">
+        <v>0.107711811460483</v>
+      </c>
+      <c r="K80">
+        <v>0.18570725057972201</v>
+      </c>
+      <c r="L80">
+        <v>0.115784032167575</v>
+      </c>
+      <c r="M80">
+        <v>0.125208900757354</v>
+      </c>
+      <c r="N80">
+        <v>0.24006203487556901</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A81" s="242">
+        <v>78</v>
+      </c>
+      <c r="B81" t="s">
+        <v>458</v>
+      </c>
+      <c r="C81">
+        <v>0.30358714963993899</v>
+      </c>
+      <c r="D81">
+        <v>0.23096668443503099</v>
+      </c>
+      <c r="E81">
+        <v>0.66800653537858101</v>
+      </c>
+      <c r="F81">
+        <v>4.3209515188229997</v>
+      </c>
+      <c r="G81">
+        <v>4.9966532151628602</v>
+      </c>
+      <c r="H81">
+        <v>4.3180240400785603</v>
+      </c>
+      <c r="I81">
+        <v>3.3812635807243101</v>
+      </c>
+      <c r="J81">
+        <v>0.31074206792519099</v>
+      </c>
+      <c r="K81">
+        <v>0.216191370846888</v>
+      </c>
+      <c r="L81">
+        <v>0.14580704815124099</v>
+      </c>
+      <c r="M81">
+        <v>0.12781824501932401</v>
+      </c>
+      <c r="N81">
+        <v>0.39546946567803398</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A82" s="242">
+        <v>78</v>
+      </c>
+      <c r="B82" t="s">
+        <v>459</v>
+      </c>
+      <c r="C82">
+        <v>0.127906153861439</v>
+      </c>
+      <c r="D82">
+        <v>0.226384384984126</v>
+      </c>
+      <c r="E82">
+        <v>0.28632172419928498</v>
+      </c>
+      <c r="F82">
+        <v>0.87088334944503398</v>
+      </c>
+      <c r="G82">
+        <v>0.81211888638945096</v>
+      </c>
+      <c r="H82">
+        <v>0.39371320265035897</v>
+      </c>
+      <c r="I82">
+        <v>0.41704883946913202</v>
+      </c>
+      <c r="J82">
+        <v>9.9955329916723498E-2</v>
+      </c>
+      <c r="K82">
+        <v>0.119294319133764</v>
+      </c>
+      <c r="L82">
+        <v>5.5966106533312202E-2</v>
+      </c>
+      <c r="M82">
+        <v>5.4259295434598502E-2</v>
+      </c>
+      <c r="N82">
+        <v>4.6930099353010499E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A83" s="242">
+        <v>78</v>
+      </c>
+      <c r="B83" t="s">
+        <v>460</v>
+      </c>
+      <c r="C83">
+        <v>8.3645232150712207E-2</v>
+      </c>
+      <c r="D83">
+        <v>0.14469469214317801</v>
+      </c>
+      <c r="E83">
+        <v>0.91037218076759696</v>
+      </c>
+      <c r="F83">
+        <v>2.1661154865583199</v>
+      </c>
+      <c r="G83">
+        <v>2.89020631416179</v>
+      </c>
+      <c r="H83">
+        <v>0.998765288132899</v>
+      </c>
+      <c r="I83">
+        <v>0.19561980252091901</v>
+      </c>
+      <c r="J83">
+        <v>8.5141278604625795E-2</v>
+      </c>
+      <c r="K83">
+        <v>6.1951314687808699E-2</v>
+      </c>
+      <c r="L83">
+        <v>8.04599779004921E-2</v>
+      </c>
+      <c r="M83">
+        <v>4.84250275509851E-2</v>
+      </c>
+      <c r="N83">
+        <v>4.3940774282526601E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A84" s="242">
+        <v>78</v>
+      </c>
+      <c r="B84" t="s">
+        <v>461</v>
+      </c>
+      <c r="C84">
+        <v>0.103307742296461</v>
+      </c>
+      <c r="D84">
+        <v>0.43599752570392902</v>
+      </c>
+      <c r="E84">
+        <v>0.87743532768163501</v>
+      </c>
+      <c r="F84">
+        <v>1.38074422519718</v>
+      </c>
+      <c r="G84">
+        <v>0.51100968961444504</v>
+      </c>
+      <c r="H84">
+        <v>0.53243748663392498</v>
+      </c>
+      <c r="I84">
+        <v>8.7981023675801295E-2</v>
+      </c>
+      <c r="J84">
+        <v>6.5919462798755199E-2</v>
+      </c>
+      <c r="K84">
+        <v>5.0702938874431801E-2</v>
+      </c>
+      <c r="L84">
+        <v>5.4009959963210903E-2</v>
+      </c>
+      <c r="M84">
+        <v>4.5305814304138402E-2</v>
+      </c>
+      <c r="N84">
+        <v>2.9815097282109598E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A85" s="242">
+        <v>78</v>
+      </c>
+      <c r="B85" t="s">
+        <v>462</v>
+      </c>
+      <c r="C85">
+        <v>4.0417994778904003E-2</v>
+      </c>
+      <c r="D85">
+        <v>3.5167586540118999E-2</v>
+      </c>
+      <c r="E85">
+        <v>8.2497664337670307E-2</v>
+      </c>
+      <c r="F85">
+        <v>8.0574976757174996E-2</v>
+      </c>
+      <c r="G85">
+        <v>4.79748955902701E-2</v>
+      </c>
+      <c r="H85">
+        <v>3.4249509920876803E-2</v>
+      </c>
+      <c r="I85">
+        <v>6.1802790170964898E-2</v>
+      </c>
+      <c r="J85">
+        <v>2.1171736287794101E-2</v>
+      </c>
+      <c r="K85">
+        <v>1.41508513807593E-2</v>
+      </c>
+      <c r="L85">
+        <v>1.5908362625667201E-2</v>
+      </c>
+      <c r="M85">
+        <v>1.08090527104894E-2</v>
+      </c>
+      <c r="N85">
+        <v>1.1863338799203199E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A86" s="242">
+        <v>78</v>
+      </c>
+      <c r="B86" t="s">
+        <v>463</v>
+      </c>
+      <c r="C86">
+        <v>3.0412217556172901E-2</v>
+      </c>
+      <c r="D86">
+        <v>9.5260923223463398E-2</v>
+      </c>
+      <c r="E86">
+        <v>0.54338606013639001</v>
+      </c>
+      <c r="F86">
+        <v>3.14047920525624</v>
+      </c>
+      <c r="G86">
+        <v>6.4368819391906396</v>
+      </c>
+      <c r="H86">
+        <v>6.0260059052042498</v>
+      </c>
+      <c r="I86">
+        <v>0.86757817902625101</v>
+      </c>
+      <c r="J86">
+        <v>7.5821325669459205E-2</v>
+      </c>
+      <c r="K86">
+        <v>8.9812925431514798E-2</v>
+      </c>
+      <c r="L86">
+        <v>7.5277507354119103E-2</v>
+      </c>
+      <c r="M86">
+        <v>8.8034741884951195E-2</v>
+      </c>
+      <c r="N86">
+        <v>0.22302899743548801</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A87" s="242">
+        <v>78</v>
+      </c>
+      <c r="B87" t="s">
+        <v>464</v>
+      </c>
+      <c r="C87">
+        <v>0.320901110879528</v>
+      </c>
+      <c r="D87">
+        <v>0.63789905459834095</v>
+      </c>
+      <c r="E87">
+        <v>1.0367254219994599</v>
+      </c>
+      <c r="F87">
+        <v>7.2234691427179403</v>
+      </c>
+      <c r="G87">
+        <v>7.4070665577736898</v>
+      </c>
+      <c r="H87">
+        <v>1.8690749642764499</v>
+      </c>
+      <c r="I87">
+        <v>1.3570426504064901</v>
+      </c>
+      <c r="J87">
+        <v>0.102925350348019</v>
+      </c>
+      <c r="K87">
+        <v>0.103009942680357</v>
+      </c>
+      <c r="L87">
+        <v>0.1090493848098</v>
+      </c>
+      <c r="M87">
+        <v>0.12698222561733899</v>
+      </c>
+      <c r="N87">
+        <v>8.6337031657839305E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A88" s="242">
+        <v>78</v>
+      </c>
+      <c r="B88" t="s">
+        <v>465</v>
+      </c>
+      <c r="C88">
+        <v>0.37732988915910298</v>
+      </c>
+      <c r="D88">
+        <v>0.51095969669100405</v>
+      </c>
+      <c r="E88">
+        <v>3.24174191452986</v>
+      </c>
+      <c r="F88">
+        <v>8.3465316573056896</v>
+      </c>
+      <c r="G88">
+        <v>2.7313058433805901</v>
+      </c>
+      <c r="H88">
+        <v>0.32569634692829003</v>
+      </c>
+      <c r="I88">
+        <v>0.20640435606454099</v>
+      </c>
+      <c r="J88">
+        <v>0.222218415004035</v>
+      </c>
+      <c r="K88">
+        <v>0.124043565017708</v>
+      </c>
+      <c r="L88">
+        <v>0.12725565136035399</v>
+      </c>
+      <c r="M88">
+        <v>0.126283012945622</v>
+      </c>
+      <c r="N88">
+        <v>8.2535823466477795E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A89" s="242">
+        <v>78</v>
+      </c>
+      <c r="B89" t="s">
+        <v>466</v>
+      </c>
+      <c r="C89">
+        <v>0.113134570995215</v>
+      </c>
+      <c r="D89">
+        <v>0.13332528048224301</v>
+      </c>
+      <c r="E89">
+        <v>0.19103244290566601</v>
+      </c>
+      <c r="F89">
+        <v>0.54576466318271799</v>
+      </c>
+      <c r="G89">
+        <v>0.61098530571805498</v>
+      </c>
+      <c r="H89">
+        <v>4.6589113529540399E-2</v>
+      </c>
+      <c r="I89">
+        <v>6.4525115037526795E-2</v>
+      </c>
+      <c r="J89">
+        <v>4.0634810148025703E-2</v>
+      </c>
+      <c r="K89">
+        <v>3.4049396054169602E-2</v>
+      </c>
+      <c r="L89">
+        <v>3.2115688243160502E-2</v>
+      </c>
+      <c r="M89">
+        <v>2.9616418200234799E-2</v>
+      </c>
+      <c r="N89">
+        <v>4.3305050442205298E-2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A90" s="242">
+        <v>78</v>
+      </c>
+      <c r="B90" t="s">
+        <v>467</v>
+      </c>
+      <c r="C90">
+        <v>0.16556346759946</v>
+      </c>
+      <c r="D90">
+        <v>8.5129504196859204E-2</v>
+      </c>
+      <c r="E90">
+        <v>0.26504555582554001</v>
+      </c>
+      <c r="F90">
+        <v>0.41720612789249201</v>
+      </c>
+      <c r="G90">
+        <v>0.164680661317847</v>
+      </c>
+      <c r="H90">
+        <v>6.0599198274008399E-2</v>
+      </c>
+      <c r="I90">
+        <v>5.3012333041965697E-2</v>
+      </c>
+      <c r="J90">
+        <v>5.7576856273599597E-2</v>
+      </c>
+      <c r="K90">
+        <v>2.0744402621926301E-2</v>
+      </c>
+      <c r="L90">
+        <v>2.3495245551046502E-2</v>
+      </c>
+      <c r="M90">
+        <v>1.8856352586779899E-2</v>
+      </c>
+      <c r="N90">
+        <v>2.07316783315745E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A91" s="242">
+        <v>78</v>
+      </c>
+      <c r="B91" t="s">
+        <v>468</v>
+      </c>
+      <c r="C91">
+        <v>3.28330399315893E-2</v>
+      </c>
+      <c r="D91">
+        <v>6.5211727210326101E-2</v>
+      </c>
+      <c r="E91">
+        <v>0.272906369080258</v>
+      </c>
+      <c r="F91">
+        <v>0.74010049323305904</v>
+      </c>
+      <c r="G91">
+        <v>1.9682593520776901</v>
+      </c>
+      <c r="H91">
+        <v>0.79412278733976804</v>
+      </c>
+      <c r="I91">
+        <v>0.122335002246311</v>
+      </c>
+      <c r="J91">
+        <v>3.0196774236676702E-2</v>
+      </c>
+      <c r="K91">
+        <v>5.9317056807331701E-2</v>
+      </c>
+      <c r="L91">
+        <v>3.0654404239557301E-2</v>
+      </c>
+      <c r="M91">
+        <v>3.6476714559781999E-2</v>
+      </c>
+      <c r="N91">
+        <v>6.0717326367064797E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A92" s="242">
+        <v>78</v>
+      </c>
+      <c r="B92" t="s">
+        <v>469</v>
+      </c>
+      <c r="C92">
+        <v>0.30780965248602798</v>
+      </c>
+      <c r="D92">
+        <v>0.46307902037384202</v>
+      </c>
+      <c r="E92">
+        <v>2.1242958415205502</v>
+      </c>
+      <c r="F92">
+        <v>8.0209517905307699</v>
+      </c>
+      <c r="G92">
+        <v>2.53203923268735</v>
+      </c>
+      <c r="H92">
+        <v>1.5133029743783699</v>
+      </c>
+      <c r="I92">
+        <v>1.92255389394883</v>
+      </c>
+      <c r="J92">
+        <v>1.20108327790835</v>
+      </c>
+      <c r="K92">
+        <v>0.46179027643795201</v>
+      </c>
+      <c r="L92">
+        <v>8.3766751499485897E-2</v>
+      </c>
+      <c r="M92">
+        <v>9.9541093835351604E-2</v>
+      </c>
+      <c r="N92">
+        <v>0.102847453074889</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A93" s="242">
+        <v>78</v>
+      </c>
+      <c r="B93" t="s">
+        <v>470</v>
+      </c>
+      <c r="C93">
+        <v>0.25913474130099901</v>
+      </c>
+      <c r="D93">
+        <v>0.25223161093332203</v>
+      </c>
+      <c r="E93">
+        <v>0.77529482861611299</v>
+      </c>
+      <c r="F93">
+        <v>6.38747617647675</v>
+      </c>
+      <c r="G93">
+        <v>1.2051475646675101</v>
+      </c>
+      <c r="H93">
+        <v>1.5968563408708101</v>
+      </c>
+      <c r="I93">
+        <v>0.28544753744634799</v>
+      </c>
+      <c r="J93">
+        <v>8.6825728524503598E-2</v>
+      </c>
+      <c r="K93">
+        <v>8.4526437729306306E-2</v>
+      </c>
+      <c r="L93">
+        <v>7.5685032465586999E-2</v>
+      </c>
+      <c r="M93">
+        <v>7.3123992288340406E-2</v>
+      </c>
+      <c r="N93">
+        <v>7.0797793686934396E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A94" s="242">
+        <v>78</v>
+      </c>
+      <c r="B94" t="s">
+        <v>471</v>
+      </c>
+      <c r="C94">
+        <v>0.54705603026447802</v>
+      </c>
+      <c r="D94">
+        <v>0.30368788327731799</v>
+      </c>
+      <c r="E94">
+        <v>1.5530532862240001</v>
+      </c>
+      <c r="F94">
+        <v>6.6769927086582896</v>
+      </c>
+      <c r="G94">
+        <v>4.1978780092162502</v>
+      </c>
+      <c r="H94">
+        <v>2.0726896469737599</v>
+      </c>
+      <c r="I94">
+        <v>0.89962506179718504</v>
+      </c>
+      <c r="J94">
+        <v>0.14071644619505599</v>
+      </c>
+      <c r="K94">
+        <v>0.112897722110598</v>
+      </c>
+      <c r="L94">
+        <v>9.4715160718355104E-2</v>
+      </c>
+      <c r="M94">
+        <v>0.110492880650118</v>
+      </c>
+      <c r="N94">
+        <v>9.7336402893272903E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A95" s="242">
+        <v>78</v>
+      </c>
+      <c r="B95" t="s">
+        <v>472</v>
+      </c>
+      <c r="C95">
+        <v>0.26053446824353399</v>
+      </c>
+      <c r="D95">
+        <v>0.657320274743594</v>
+      </c>
+      <c r="E95">
+        <v>2.5716964272591598</v>
+      </c>
+      <c r="F95">
+        <v>6.1515057627291299</v>
+      </c>
+      <c r="G95">
+        <v>3.25860319250428</v>
+      </c>
+      <c r="H95">
+        <v>2.2820900742322801</v>
+      </c>
+      <c r="I95">
+        <v>0.26296672149588102</v>
+      </c>
+      <c r="J95">
+        <v>0.25358975646214299</v>
+      </c>
+      <c r="K95">
+        <v>9.5655656808473793E-2</v>
+      </c>
+      <c r="L95">
+        <v>8.5875778565627101E-2</v>
+      </c>
+      <c r="M95">
+        <v>9.0894532938020606E-2</v>
+      </c>
+      <c r="N95">
+        <v>0.11671224018842299</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A96" s="242">
+        <v>78</v>
+      </c>
+      <c r="B96" t="s">
+        <v>473</v>
+      </c>
+      <c r="C96">
+        <v>1.1510106205661901</v>
+      </c>
+      <c r="D96">
+        <v>3.4053438013488799</v>
+      </c>
+      <c r="E96">
+        <v>3.3963430696202099</v>
+      </c>
+      <c r="F96">
+        <v>1.8410999758264199</v>
+      </c>
+      <c r="G96">
+        <v>0.70489470857627001</v>
+      </c>
+      <c r="H96">
+        <v>2.3473433017202101</v>
+      </c>
+      <c r="I96">
+        <v>0.81119677042628202</v>
+      </c>
+      <c r="J96">
+        <v>0.16279245810644799</v>
+      </c>
+      <c r="K96">
+        <v>0.110782970242155</v>
+      </c>
+      <c r="L96">
+        <v>8.8891351277898906E-2</v>
+      </c>
+      <c r="M96">
+        <v>7.3518632466596207E-2</v>
+      </c>
+      <c r="N96">
+        <v>6.8547510729386196E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A97" s="242">
+        <v>78</v>
+      </c>
+      <c r="B97" t="s">
+        <v>474</v>
+      </c>
+      <c r="C97">
+        <v>7.0217658881473494E-2</v>
+      </c>
+      <c r="D97">
+        <v>9.4427838238215794E-2</v>
+      </c>
+      <c r="E97">
+        <v>0.17014052422131401</v>
+      </c>
+      <c r="F97">
+        <v>0.53553369791096905</v>
+      </c>
+      <c r="G97">
+        <v>2.0624187669408198</v>
+      </c>
+      <c r="H97">
+        <v>1.7372992760955701</v>
+      </c>
+      <c r="I97">
+        <v>0.20833817748755001</v>
+      </c>
+      <c r="J97">
+        <v>5.1240477632314797E-2</v>
+      </c>
+      <c r="K97">
+        <v>5.8320779360633498E-2</v>
+      </c>
+      <c r="L97">
+        <v>4.8263122401177298E-2</v>
+      </c>
+      <c r="M97">
+        <v>4.2011751879073599E-2</v>
+      </c>
+      <c r="N97">
+        <v>4.6516676887449197E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A98" s="242">
+        <v>78</v>
+      </c>
+      <c r="B98" t="s">
+        <v>475</v>
+      </c>
+      <c r="C98">
+        <v>4.6243517031036997E-2</v>
+      </c>
+      <c r="D98">
+        <v>8.6232941772421301E-2</v>
+      </c>
+      <c r="E98">
+        <v>0.31292135356088602</v>
+      </c>
+      <c r="F98">
+        <v>1.5826403766158199</v>
+      </c>
+      <c r="G98">
+        <v>3.1096513775183698</v>
+      </c>
+      <c r="H98">
+        <v>1.6935745068477399</v>
+      </c>
+      <c r="I98">
+        <v>0.27916188974739298</v>
+      </c>
+      <c r="J98">
+        <v>0.168224827757538</v>
+      </c>
+      <c r="K98">
+        <v>7.4191346887253901E-2</v>
+      </c>
+      <c r="L98">
+        <v>4.91115686772969E-2</v>
+      </c>
+      <c r="M98">
+        <v>5.3577051038016701E-2</v>
+      </c>
+      <c r="N98">
+        <v>5.1004970611300701E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A99" s="242">
+        <v>78</v>
+      </c>
+      <c r="B99" t="s">
+        <v>476</v>
+      </c>
+      <c r="C99">
+        <v>8.1459576913667398E-2</v>
+      </c>
+      <c r="D99">
+        <v>0.224164129720761</v>
+      </c>
+      <c r="E99">
+        <v>0.57220374247883699</v>
+      </c>
+      <c r="F99">
+        <v>2.18070868194514</v>
+      </c>
+      <c r="G99">
+        <v>1.11185713121864</v>
+      </c>
+      <c r="H99">
+        <v>1.1269246081963</v>
+      </c>
+      <c r="I99">
+        <v>0.21232249167478801</v>
+      </c>
+      <c r="J99">
+        <v>7.2031751391244195E-2</v>
+      </c>
+      <c r="K99">
+        <v>4.9170714796432501E-2</v>
+      </c>
+      <c r="L99">
+        <v>4.6098001310737199E-2</v>
+      </c>
+      <c r="M99">
+        <v>4.5169569213399E-2</v>
+      </c>
+      <c r="N99">
+        <v>6.1601582137891901E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A100" s="242">
+        <v>78</v>
+      </c>
+      <c r="B100" t="s">
+        <v>477</v>
+      </c>
+      <c r="C100">
+        <v>0.113606415697315</v>
+      </c>
+      <c r="D100">
+        <v>7.2408228464959007E-2</v>
+      </c>
+      <c r="E100">
+        <v>0.42721341377829802</v>
+      </c>
+      <c r="F100">
+        <v>2.3583082406351199</v>
+      </c>
+      <c r="G100">
+        <v>1.5971702503974801</v>
+      </c>
+      <c r="H100">
+        <v>0.73362368573297898</v>
+      </c>
+      <c r="I100">
+        <v>0.30659466532614699</v>
+      </c>
+      <c r="J100">
+        <v>0.18074290785751801</v>
+      </c>
+      <c r="K100">
+        <v>4.8483862633557397E-2</v>
+      </c>
+      <c r="L100">
+        <v>4.4490496401612303E-2</v>
+      </c>
+      <c r="M100">
+        <v>4.2815585246212401E-2</v>
+      </c>
+      <c r="N100">
+        <v>4.6178820330166202E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A101" s="242">
+        <v>78</v>
+      </c>
+      <c r="B101" t="s">
+        <v>478</v>
+      </c>
+      <c r="C101">
+        <v>0.100094528800866</v>
+      </c>
+      <c r="D101">
+        <v>0.246993153742667</v>
+      </c>
+      <c r="E101">
+        <v>1.64436678941005</v>
+      </c>
+      <c r="F101">
+        <v>8.3580897371446898</v>
+      </c>
+      <c r="G101">
+        <v>9.1065951737463102</v>
+      </c>
+      <c r="H101">
+        <v>3.1957058907936702</v>
+      </c>
+      <c r="I101">
+        <v>2.4578364983747298</v>
+      </c>
+      <c r="J101">
+        <v>0.42580003814939199</v>
+      </c>
+      <c r="K101">
+        <v>0.11405272741615299</v>
+      </c>
+      <c r="L101">
+        <v>0.106844060865377</v>
+      </c>
+      <c r="M101">
+        <v>0.10398348691218701</v>
+      </c>
+      <c r="N101">
+        <v>9.1897004220202694E-2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A102" s="242">
+        <v>78</v>
+      </c>
+      <c r="B102" t="s">
+        <v>479</v>
+      </c>
+      <c r="C102">
+        <v>0.183571244930475</v>
+      </c>
+      <c r="D102">
+        <v>0.109215444908919</v>
+      </c>
+      <c r="E102">
+        <v>0.18361521880242199</v>
+      </c>
+      <c r="F102">
+        <v>0.53386262202353696</v>
+      </c>
+      <c r="G102">
+        <v>0.200244423362577</v>
+      </c>
+      <c r="H102">
+        <v>0.13287745781837801</v>
+      </c>
+      <c r="I102">
+        <v>6.2587571376030299E-2</v>
+      </c>
+      <c r="J102">
+        <v>3.9489209424544702E-2</v>
+      </c>
+      <c r="K102">
+        <v>3.60304778389497E-2</v>
+      </c>
+      <c r="L102">
+        <v>3.33449664126809E-2</v>
+      </c>
+      <c r="M102">
+        <v>2.90029204575247E-2</v>
+      </c>
+      <c r="N102">
+        <v>4.4397294042015097E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A103" s="242">
+        <v>78</v>
+      </c>
+      <c r="B103" t="s">
+        <v>480</v>
+      </c>
+      <c r="C103">
+        <v>0.234599501870075</v>
+      </c>
+      <c r="D103">
+        <v>0.45665751666031601</v>
+      </c>
+      <c r="E103">
+        <v>1.3446258750103399</v>
+      </c>
+      <c r="F103">
+        <v>3.3765739901436702</v>
+      </c>
+      <c r="G103">
+        <v>2.6377182085202202</v>
+      </c>
+      <c r="H103">
+        <v>0.88907379213015802</v>
+      </c>
+      <c r="I103">
+        <v>1.3149870994600299</v>
+      </c>
+      <c r="J103">
+        <v>0.16172507938047501</v>
+      </c>
+      <c r="K103">
+        <v>6.9298345868743894E-2</v>
+      </c>
+      <c r="L103">
+        <v>0.22048346911941999</v>
+      </c>
+      <c r="M103">
+        <v>0.120768819068719</v>
+      </c>
+      <c r="N103">
+        <v>5.6664859647994302E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A104" s="242">
+        <v>78</v>
+      </c>
+      <c r="B104" t="s">
+        <v>481</v>
+      </c>
+      <c r="C104">
+        <v>0.10218374854393</v>
+      </c>
+      <c r="D104">
+        <v>0.45153534891976899</v>
+      </c>
+      <c r="E104">
+        <v>0.54198321885425205</v>
+      </c>
+      <c r="F104">
+        <v>0.56117457856312603</v>
+      </c>
+      <c r="G104">
+        <v>0.183988753077095</v>
+      </c>
+      <c r="H104">
+        <v>0.226864842748217</v>
+      </c>
+      <c r="I104">
+        <v>4.5111643819221302E-2</v>
+      </c>
+      <c r="J104">
+        <v>3.6144425136378701E-2</v>
+      </c>
+      <c r="K104">
+        <v>3.3550973011852503E-2</v>
+      </c>
+      <c r="L104">
+        <v>3.3156870910319103E-2</v>
+      </c>
+      <c r="M104">
+        <v>2.9552498502574999E-2</v>
+      </c>
+      <c r="N104">
+        <v>2.5555483239977E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A105" s="242">
+        <v>78</v>
+      </c>
+      <c r="B105" t="s">
+        <v>482</v>
+      </c>
+      <c r="C105">
+        <v>3.4886527336751197E-2</v>
+      </c>
+      <c r="D105">
+        <v>5.0622047231571897E-2</v>
+      </c>
+      <c r="E105">
+        <v>6.9806798827844505E-2</v>
+      </c>
+      <c r="F105">
+        <v>0.19275535840275801</v>
+      </c>
+      <c r="G105">
+        <v>0.31273624621735802</v>
+      </c>
+      <c r="H105">
+        <v>0.28296062319713799</v>
+      </c>
+      <c r="I105">
+        <v>0.24367968372378199</v>
+      </c>
+      <c r="J105">
+        <v>2.5860447593654801E-2</v>
+      </c>
+      <c r="K105">
+        <v>2.0918251230911299E-2</v>
+      </c>
+      <c r="L105">
+        <v>1.9310382969117301E-2</v>
+      </c>
+      <c r="M105">
+        <v>2.4107900518688299E-2</v>
+      </c>
+      <c r="N105">
+        <v>2.2499122493821799E-2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A106" s="242">
+        <v>78</v>
+      </c>
+      <c r="B106" t="s">
+        <v>483</v>
+      </c>
+      <c r="C106">
+        <v>4.7688336157882899E-2</v>
+      </c>
+      <c r="D106">
+        <v>4.5796646002648003E-2</v>
+      </c>
+      <c r="E106">
+        <v>0.29166333429253699</v>
+      </c>
+      <c r="F106">
+        <v>0.60225859748742205</v>
+      </c>
+      <c r="G106">
+        <v>0.73088980316245</v>
+      </c>
+      <c r="H106">
+        <v>0.15857212649600499</v>
+      </c>
+      <c r="I106">
+        <v>5.7023371638977298E-2</v>
+      </c>
+      <c r="J106">
+        <v>2.1142403762408401E-2</v>
+      </c>
+      <c r="K106">
+        <v>3.1256170495344598E-2</v>
+      </c>
+      <c r="L106">
+        <v>2.5161285038597402E-2</v>
+      </c>
+      <c r="M106">
+        <v>2.2911647096099001E-2</v>
+      </c>
+      <c r="N106">
+        <v>1.81879721156194E-2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A107" s="242">
+        <v>78</v>
+      </c>
+      <c r="B107" t="s">
+        <v>484</v>
+      </c>
+      <c r="C107">
+        <v>3.3915588166744198E-2</v>
+      </c>
+      <c r="D107">
+        <v>6.6414569889110806E-2</v>
+      </c>
+      <c r="E107">
+        <v>0.288379837299157</v>
+      </c>
+      <c r="F107">
+        <v>0.53387094784113698</v>
+      </c>
+      <c r="G107">
+        <v>0.30854166212908901</v>
+      </c>
+      <c r="H107">
+        <v>0.321859403221192</v>
+      </c>
+      <c r="I107">
+        <v>0.84128898530954399</v>
+      </c>
+      <c r="J107">
+        <v>2.68785544742191E-2</v>
+      </c>
+      <c r="K107">
+        <v>3.5806886533898602E-2</v>
+      </c>
+      <c r="L107">
+        <v>2.4065978086000001E-2</v>
+      </c>
+      <c r="M107">
+        <v>2.1929833340612399E-2</v>
+      </c>
+      <c r="N107">
+        <v>3.8989606408070199E-2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A108" s="242">
+        <v>78</v>
+      </c>
+      <c r="B108" t="s">
+        <v>485</v>
+      </c>
+      <c r="C108">
+        <v>0.15351690078101901</v>
+      </c>
+      <c r="D108">
+        <v>0.125148102843676</v>
+      </c>
+      <c r="E108">
+        <v>0.284192120123683</v>
+      </c>
+      <c r="F108">
+        <v>0.740437740073146</v>
+      </c>
+      <c r="G108">
+        <v>0.44391914751818101</v>
+      </c>
+      <c r="H108">
+        <v>0.284398144236509</v>
+      </c>
+      <c r="I108">
+        <v>2.93334070086772E-2</v>
+      </c>
+      <c r="J108">
+        <v>2.6885946044332299E-2</v>
+      </c>
+      <c r="K108">
+        <v>2.8382284703168802E-2</v>
+      </c>
+      <c r="L108">
+        <v>2.4022792289284001E-2</v>
+      </c>
+      <c r="M108">
+        <v>2.59966127571097E-2</v>
+      </c>
+      <c r="N108">
+        <v>4.1251350344151901E-2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A109" s="242">
+        <v>78</v>
+      </c>
+      <c r="B109" t="s">
+        <v>486</v>
+      </c>
+      <c r="C109">
+        <v>5.4386587415762598E-2</v>
+      </c>
+      <c r="D109">
+        <v>0.13263895450647301</v>
+      </c>
+      <c r="E109">
+        <v>0.92831991717914497</v>
+      </c>
+      <c r="F109">
+        <v>1.5898653734913499</v>
+      </c>
+      <c r="G109">
+        <v>1.7227540028577799</v>
+      </c>
+      <c r="H109">
+        <v>0.59742179954751196</v>
+      </c>
+      <c r="I109">
+        <v>0.50346135790232305</v>
+      </c>
+      <c r="J109">
+        <v>8.4284495881963101E-2</v>
+      </c>
+      <c r="K109">
+        <v>3.8956794289619699E-2</v>
+      </c>
+      <c r="L109">
+        <v>6.0167650117849698E-2</v>
+      </c>
+      <c r="M109">
+        <v>3.7956168001554401E-2</v>
+      </c>
+      <c r="N109">
+        <v>7.21261991982248E-2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A110" s="200">
+        <v>1</v>
+      </c>
+      <c r="B110" t="s">
+        <v>379</v>
+      </c>
+      <c r="L110">
+        <v>1.9087913224138599E-3</v>
+      </c>
+      <c r="M110">
+        <v>1.5295460117919499E-3</v>
+      </c>
+      <c r="N110">
+        <v>2.1730637357995099E-2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A111" s="200">
+        <v>1</v>
+      </c>
+      <c r="B111" t="s">
+        <v>380</v>
+      </c>
+      <c r="C111">
+        <v>3.95486570531485E-2</v>
+      </c>
+      <c r="D111">
+        <v>5.2929046477555398E-2</v>
+      </c>
+      <c r="E111">
+        <v>1.1654963077205001</v>
+      </c>
+      <c r="F111">
+        <v>1.4064563426405099</v>
+      </c>
+      <c r="G111">
+        <v>0.66450890157605902</v>
+      </c>
+      <c r="H111">
+        <v>0.71306554564381397</v>
+      </c>
+      <c r="I111">
+        <v>0.181259456473952</v>
+      </c>
+      <c r="J111">
+        <v>7.7867967311887804E-2</v>
+      </c>
+      <c r="K111">
+        <v>3.2863231137851903E-2</v>
+      </c>
+      <c r="L111">
+        <v>1.31393263963019E-3</v>
+      </c>
+      <c r="M111">
+        <v>1.1662765038478701E-3</v>
+      </c>
+      <c r="N111">
+        <v>2.7225239201083801E-2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A112" s="200">
+        <v>1</v>
+      </c>
+      <c r="B112" t="s">
+        <v>381</v>
+      </c>
+      <c r="C112">
+        <v>0.100423243412242</v>
+      </c>
+      <c r="D112">
+        <v>0.57350378701141502</v>
+      </c>
+      <c r="E112">
+        <v>2.4475211400616801</v>
+      </c>
+      <c r="F112">
+        <v>2.40199099141407</v>
+      </c>
+      <c r="G112">
+        <v>8.1700637117813706</v>
+      </c>
+      <c r="H112">
+        <v>2.7647955828863702</v>
+      </c>
+      <c r="I112">
+        <v>0.17446071213175199</v>
+      </c>
+      <c r="J112">
+        <v>0.25418830259911301</v>
+      </c>
+      <c r="K112">
+        <v>3.6763763078739999E-2</v>
+      </c>
+      <c r="L112">
+        <v>2.2548415157102601E-3</v>
+      </c>
+      <c r="M112">
+        <v>5.5978749614200799E-3</v>
+      </c>
+      <c r="N112">
+        <v>7.1054047150750201E-3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A113" s="200">
+        <v>1</v>
+      </c>
+      <c r="B113" t="s">
+        <v>382</v>
+      </c>
+      <c r="C113">
+        <v>3.9291914750133002E-2</v>
+      </c>
+      <c r="D113">
+        <v>0.94924995178338401</v>
+      </c>
+      <c r="E113">
+        <v>9.6428079907290893</v>
+      </c>
+      <c r="F113">
+        <v>19.807332420589798</v>
+      </c>
+      <c r="G113">
+        <v>17.917846529556201</v>
+      </c>
+      <c r="H113">
+        <v>6.3544350709584201</v>
+      </c>
+      <c r="I113">
+        <v>1.9573580481175099</v>
+      </c>
+      <c r="J113">
+        <v>0.34278375779982201</v>
+      </c>
+      <c r="K113">
+        <v>1.4537407624595501E-2</v>
+      </c>
+      <c r="L113">
+        <v>0.17531324795066</v>
+      </c>
+      <c r="M113">
+        <v>2.12419919284547E-2</v>
+      </c>
+      <c r="N113">
+        <v>0.13219585142599899</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A114" s="200">
+        <v>1</v>
+      </c>
+      <c r="B114" t="s">
+        <v>383</v>
+      </c>
+      <c r="C114">
+        <v>0.72368704899442904</v>
+      </c>
+      <c r="D114">
+        <v>2.8473805830141199</v>
+      </c>
+      <c r="E114">
+        <v>5.4739243628585799</v>
+      </c>
+      <c r="F114">
+        <v>7.7063710509184897</v>
+      </c>
+      <c r="G114">
+        <v>2.73378675403114</v>
+      </c>
+      <c r="H114">
+        <v>2.3792314325967299</v>
+      </c>
+      <c r="I114">
+        <v>0.30518953066045601</v>
+      </c>
+      <c r="J114">
+        <v>0.34003917257385902</v>
+      </c>
+      <c r="K114">
+        <v>1.99834427990472E-2</v>
+      </c>
+      <c r="L114">
+        <v>5.9758332006801199E-3</v>
+      </c>
+      <c r="M114">
+        <v>2.6934299697030902E-3</v>
+      </c>
+      <c r="N114">
+        <v>1.23676797173034E-3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A115" s="200">
+        <v>1</v>
+      </c>
+      <c r="B115" t="s">
+        <v>384</v>
+      </c>
+      <c r="C115">
+        <v>9.2687508920063708E-3</v>
+      </c>
+      <c r="D115">
+        <v>1.0744854143394499E-2</v>
+      </c>
+      <c r="E115">
+        <v>5.4876177284533999E-2</v>
+      </c>
+      <c r="F115">
+        <v>0.21560666248152799</v>
+      </c>
+      <c r="G115">
+        <v>8.7299019432877503E-2</v>
+      </c>
+      <c r="H115">
+        <v>2.1014499551378501E-2</v>
+      </c>
+      <c r="I115">
+        <v>3.73041326682899E-4</v>
+      </c>
+      <c r="J115">
+        <v>2.9977373449715399E-3</v>
+      </c>
+      <c r="K115">
+        <v>1.9290140661774801E-4</v>
+      </c>
+      <c r="L115">
+        <v>4.2850178693352797E-5</v>
+      </c>
+      <c r="M115">
+        <v>2.8038176587273299E-6</v>
+      </c>
+      <c r="N115">
+        <v>3.02357978195691E-3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A116" s="200">
+        <v>1</v>
+      </c>
+      <c r="B116" t="s">
+        <v>385</v>
+      </c>
+      <c r="C116">
+        <v>2.5081043197083399E-2</v>
+      </c>
+      <c r="D116">
+        <v>0.16026900228025701</v>
+      </c>
+      <c r="E116">
+        <v>2.47016289497564</v>
+      </c>
+      <c r="F116">
+        <v>11.6641830740109</v>
+      </c>
+      <c r="G116">
+        <v>6.4421296984210796</v>
+      </c>
+      <c r="H116">
+        <v>3.7127937629889201</v>
+      </c>
+      <c r="I116">
+        <v>0.12597000095813901</v>
+      </c>
+      <c r="J116">
+        <v>3.7837739950039902E-4</v>
+      </c>
+      <c r="K116">
+        <v>1.7940480550831001E-3</v>
+      </c>
+      <c r="L116">
+        <v>1.17528255728252E-2</v>
+      </c>
+      <c r="M116">
+        <v>7.2000699902397297E-2</v>
+      </c>
+      <c r="N116">
+        <v>9.8000638455978506E-2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A117" s="200">
+        <v>1</v>
+      </c>
+      <c r="B117" t="s">
+        <v>386</v>
+      </c>
+      <c r="C117">
+        <v>1.01636822551163</v>
+      </c>
+      <c r="D117">
+        <v>5.1243276444933201</v>
+      </c>
+      <c r="E117">
+        <v>21.2755474020409</v>
+      </c>
+      <c r="F117">
+        <v>20.090111224245899</v>
+      </c>
+      <c r="G117">
+        <v>35.28350266468</v>
+      </c>
+      <c r="H117">
+        <v>7.3036374577845198</v>
+      </c>
+      <c r="I117">
+        <v>1.1108923023928801</v>
+      </c>
+      <c r="J117">
+        <v>7.7124388848731204E-3</v>
+      </c>
+      <c r="K117">
+        <v>0.14297616116751599</v>
+      </c>
+      <c r="L117">
+        <v>1.0098595653373101E-2</v>
+      </c>
+      <c r="M117">
+        <v>0.20946810876447</v>
+      </c>
+      <c r="N117">
+        <v>0.20490259561761801</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A118" s="200">
+        <v>1</v>
+      </c>
+      <c r="B118" t="s">
+        <v>387</v>
+      </c>
+      <c r="C118">
+        <v>0.54839526566369501</v>
+      </c>
+      <c r="D118">
+        <v>1.55876354027938</v>
+      </c>
+      <c r="E118">
+        <v>11.7243507578241</v>
+      </c>
+      <c r="F118">
+        <v>19.736840361973702</v>
+      </c>
+      <c r="G118">
+        <v>23.266813080348602</v>
+      </c>
+      <c r="H118">
+        <v>7.3123398819495398</v>
+      </c>
+      <c r="I118">
+        <v>0.91179886422021705</v>
+      </c>
+      <c r="J118">
+        <v>0.48956798653318501</v>
+      </c>
+      <c r="K118">
+        <v>3.8209921276230102E-2</v>
+      </c>
+      <c r="L118">
+        <v>1.7838271077321902E-2</v>
+      </c>
+      <c r="M118">
+        <v>5.5446500957832502E-3</v>
+      </c>
+      <c r="N118">
+        <v>7.8276777045684295E-2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A119" s="200">
+        <v>1</v>
+      </c>
+      <c r="B119" t="s">
+        <v>388</v>
+      </c>
+      <c r="C119">
+        <v>4.0179195518100203E-2</v>
+      </c>
+      <c r="D119">
+        <v>9.0577128436209103E-2</v>
+      </c>
+      <c r="E119">
+        <v>7.1225292044943406E-2</v>
+      </c>
+      <c r="F119">
+        <v>4.4498116722508897E-2</v>
+      </c>
+      <c r="G119">
+        <v>4.5528261412151598E-2</v>
+      </c>
+      <c r="H119">
+        <v>6.0401075591699103E-3</v>
+      </c>
+      <c r="I119">
+        <v>5.8676252658011498E-3</v>
+      </c>
+      <c r="J119">
+        <v>2.6626177398807898E-3</v>
+      </c>
+      <c r="K119">
+        <v>1.3655407545226899E-4</v>
+      </c>
+      <c r="L119">
+        <v>1.6991935493786099E-4</v>
+      </c>
+      <c r="M119">
+        <v>1.70526236094766E-4</v>
+      </c>
+      <c r="N119">
+        <v>1.2239552430986101E-4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A120" s="200">
+        <v>1</v>
+      </c>
+      <c r="B120" t="s">
+        <v>389</v>
+      </c>
+      <c r="C120">
+        <v>3.3784323217890598E-4</v>
+      </c>
+      <c r="D120">
+        <v>4.9896655585893604E-3</v>
+      </c>
+      <c r="E120">
+        <v>1.4851617179161301</v>
+      </c>
+      <c r="F120">
+        <v>9.8489061067307908</v>
+      </c>
+      <c r="G120">
+        <v>7.8134760435143198</v>
+      </c>
+      <c r="H120">
+        <v>1.6349057102351401</v>
+      </c>
+      <c r="I120">
+        <v>0.53373779217210204</v>
+      </c>
+      <c r="J120">
+        <v>0.17549738446127899</v>
+      </c>
+      <c r="K120">
+        <v>1.8052370181697301E-2</v>
+      </c>
+      <c r="L120">
+        <v>1.9036896832220498E-2</v>
+      </c>
+      <c r="M120">
+        <v>6.4406159871575799E-3</v>
+      </c>
+      <c r="N120">
+        <v>9.6873124849949796E-2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A121" s="200">
+        <v>1</v>
+      </c>
+      <c r="B121" t="s">
+        <v>390</v>
+      </c>
+      <c r="C121">
+        <v>0.14330109679689301</v>
+      </c>
+      <c r="D121">
+        <v>2.1706722657344999</v>
+      </c>
+      <c r="E121">
+        <v>19.4907854779497</v>
+      </c>
+      <c r="F121">
+        <v>24.443959592119601</v>
+      </c>
+      <c r="G121">
+        <v>43.535591692106898</v>
+      </c>
+      <c r="H121">
+        <v>1.5313794461915899</v>
+      </c>
+      <c r="I121">
+        <v>3.60339758628586</v>
+      </c>
+      <c r="J121">
+        <v>2.2920856399159601E-2</v>
+      </c>
+      <c r="K121">
+        <v>0.244422069105378</v>
+      </c>
+      <c r="L121">
+        <v>6.9562656303165202E-2</v>
+      </c>
+      <c r="M121">
+        <v>9.4132777736881196E-2</v>
+      </c>
+      <c r="N121">
+        <v>3.8261757598718797E-2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A122" s="200">
+        <v>1</v>
+      </c>
+      <c r="B122" t="s">
+        <v>391</v>
+      </c>
+      <c r="C122">
+        <v>6.3972774849089906E-2</v>
+      </c>
+      <c r="D122">
+        <v>0.26562477907271498</v>
+      </c>
+      <c r="E122">
+        <v>2.4662616357067302</v>
+      </c>
+      <c r="F122">
+        <v>13.320263833483899</v>
+      </c>
+      <c r="G122">
+        <v>8.2775369392768194</v>
+      </c>
+      <c r="H122">
+        <v>2.3949958442214201</v>
+      </c>
+      <c r="I122">
+        <v>0.83362954548326496</v>
+      </c>
+      <c r="J122">
+        <v>0.24155973759148699</v>
+      </c>
+      <c r="K122">
+        <v>2.3346734902703101E-2</v>
+      </c>
+      <c r="L122">
+        <v>9.6418200330523392E-3</v>
+      </c>
+      <c r="M122">
+        <v>0.17819979188552601</v>
+      </c>
+      <c r="N122">
+        <v>6.5502214064388697E-3</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A123" s="200">
+        <v>1</v>
+      </c>
+      <c r="B123" t="s">
+        <v>392</v>
+      </c>
+      <c r="C123">
+        <v>0.157876492059317</v>
+      </c>
+      <c r="D123">
+        <v>3.5987739708106701</v>
+      </c>
+      <c r="E123">
+        <v>6.3883240223863904</v>
+      </c>
+      <c r="F123">
+        <v>16.218358240335402</v>
+      </c>
+      <c r="G123">
+        <v>7.47896270197365</v>
+      </c>
+      <c r="H123">
+        <v>5.0136615845077204</v>
+      </c>
+      <c r="I123">
+        <v>0.86559099627603697</v>
+      </c>
+      <c r="J123">
+        <v>4.8667418213127499E-2</v>
+      </c>
+      <c r="K123">
+        <v>6.6179276427831696E-3</v>
+      </c>
+      <c r="L123">
+        <v>9.2936248852387403E-3</v>
+      </c>
+      <c r="M123">
+        <v>7.4393019545694302E-4</v>
+      </c>
+      <c r="N123">
+        <v>5.6557076686372101E-4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A124" s="200">
+        <v>1</v>
+      </c>
+      <c r="B124" t="s">
+        <v>393</v>
+      </c>
+      <c r="C124">
+        <v>0.21463436601041899</v>
+      </c>
+      <c r="D124">
+        <v>1.9222868657577401</v>
+      </c>
+      <c r="E124">
+        <v>29.149136927855299</v>
+      </c>
+      <c r="F124">
+        <v>59.811808486287298</v>
+      </c>
+      <c r="G124">
+        <v>31.7826183360397</v>
+      </c>
+      <c r="H124">
+        <v>9.2446397526475295</v>
+      </c>
+      <c r="I124">
+        <v>0.18868822021103401</v>
+      </c>
+      <c r="J124">
+        <v>3.0840665239194601E-2</v>
+      </c>
+      <c r="K124">
+        <v>5.0926498300651699E-2</v>
+      </c>
+      <c r="L124">
+        <v>0.15975277254605499</v>
+      </c>
+      <c r="M124">
+        <v>2.3560376230064701E-2</v>
+      </c>
+      <c r="N124">
+        <v>0.17458714765052299</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A125" s="200">
+        <v>1</v>
+      </c>
+      <c r="B125" t="s">
+        <v>394</v>
+      </c>
+      <c r="C125">
+        <v>0.68739284940099399</v>
+      </c>
+      <c r="D125">
+        <v>1.2198202997191701</v>
+      </c>
+      <c r="E125">
+        <v>8.5885349047580899</v>
+      </c>
+      <c r="F125">
+        <v>19.418636448234899</v>
+      </c>
+      <c r="G125">
+        <v>8.0395754447562702</v>
+      </c>
+      <c r="H125">
+        <v>1.6638098676336199</v>
+      </c>
+      <c r="I125">
+        <v>0.64204557061194101</v>
+      </c>
+      <c r="J125">
+        <v>6.9498658375126504E-2</v>
+      </c>
+      <c r="K125">
+        <v>0.14801082689280201</v>
+      </c>
+      <c r="L125">
+        <v>2.6736306309977299E-2</v>
+      </c>
+      <c r="M125">
+        <v>1.0853729601058701E-2</v>
+      </c>
+      <c r="N125">
+        <v>1.2303296427977299E-2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A126" s="200">
+        <v>1</v>
+      </c>
+      <c r="B126" t="s">
+        <v>395</v>
+      </c>
+      <c r="C126">
+        <v>0.14170064343635799</v>
+      </c>
+      <c r="D126">
+        <v>1.03433227460398</v>
+      </c>
+      <c r="E126">
+        <v>6.1523617767951704</v>
+      </c>
+      <c r="F126">
+        <v>23.434118775599401</v>
+      </c>
+      <c r="G126">
+        <v>12.663705134333201</v>
+      </c>
+      <c r="H126">
+        <v>3.7472592058152498</v>
+      </c>
+      <c r="I126">
+        <v>0.65937033036744697</v>
+      </c>
+      <c r="J126">
+        <v>9.0368025549831003E-4</v>
+      </c>
+      <c r="K126">
+        <v>7.7058750930407503E-4</v>
+      </c>
+      <c r="L126">
+        <v>3.1320805054272998E-4</v>
+      </c>
+      <c r="M126">
+        <v>1.89348929474694E-2</v>
+      </c>
+      <c r="N126">
+        <v>9.7726171036952407E-3</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A127" s="200">
+        <v>1</v>
+      </c>
+      <c r="B127" t="s">
+        <v>396</v>
+      </c>
+      <c r="C127">
+        <v>5.5680480274157403E-2</v>
+      </c>
+      <c r="D127">
+        <v>0.53233988033372304</v>
+      </c>
+      <c r="E127">
+        <v>5.0644563271953498</v>
+      </c>
+      <c r="F127">
+        <v>20.900464152148999</v>
+      </c>
+      <c r="G127">
+        <v>9.8686287927225393</v>
+      </c>
+      <c r="H127">
+        <v>4.2674396554367</v>
+      </c>
+      <c r="I127">
+        <v>0.721421551668322</v>
+      </c>
+      <c r="J127">
+        <v>5.60944045247278E-3</v>
+      </c>
+      <c r="K127">
+        <v>1.1130410400238299E-3</v>
+      </c>
+      <c r="L127">
+        <v>7.7243216028610598E-4</v>
+      </c>
+      <c r="M127">
+        <v>3.5521784849032798E-4</v>
+      </c>
+      <c r="N127">
+        <v>1.03097952333349E-2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A128" s="200">
+        <v>1</v>
+      </c>
+      <c r="B128" t="s">
+        <v>397</v>
+      </c>
+      <c r="C128">
+        <v>9.4251397921059799E-2</v>
+      </c>
+      <c r="D128">
+        <v>0.16865771716333</v>
+      </c>
+      <c r="E128">
+        <v>1.9602933602305701</v>
+      </c>
+      <c r="F128">
+        <v>10.848069043548699</v>
+      </c>
+      <c r="G128">
+        <v>2.8194965790337001</v>
+      </c>
+      <c r="H128">
+        <v>1.2506147530004801</v>
+      </c>
+      <c r="I128">
+        <v>0.15619285426511101</v>
+      </c>
+      <c r="J128">
+        <v>5.4536709013073799E-4</v>
+      </c>
+      <c r="K128">
+        <v>7.1729140681281195E-4</v>
+      </c>
+      <c r="L128">
+        <v>4.76507930863186E-4</v>
+      </c>
+      <c r="M128">
+        <v>2.3702608828332701E-4</v>
+      </c>
+      <c r="N128">
+        <v>4.4397375452058701E-3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A129" s="200">
+        <v>1</v>
+      </c>
+      <c r="B129" t="s">
+        <v>398</v>
+      </c>
+      <c r="C129">
+        <v>7.2611904293656895E-2</v>
+      </c>
+      <c r="D129">
+        <v>1.21784445430115</v>
+      </c>
+      <c r="E129">
+        <v>11.1253134877858</v>
+      </c>
+      <c r="F129">
+        <v>24.945201914430299</v>
+      </c>
+      <c r="G129">
+        <v>8.0088108108362004</v>
+      </c>
+      <c r="H129">
+        <v>4.5637960359410599</v>
+      </c>
+      <c r="I129">
+        <v>0.43591666438562898</v>
+      </c>
+      <c r="J129">
+        <v>1.29361779753216E-2</v>
+      </c>
+      <c r="K129">
+        <v>5.5230119148210403E-2</v>
+      </c>
+      <c r="L129">
+        <v>5.6455357000186099E-2</v>
+      </c>
+      <c r="M129">
+        <v>1.7996751056706999E-2</v>
+      </c>
+      <c r="N129">
+        <v>6.7152710573910798E-2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A130" s="200">
+        <v>1</v>
+      </c>
+      <c r="B130" t="s">
+        <v>399</v>
+      </c>
+      <c r="C130">
+        <v>0.27099496846766102</v>
+      </c>
+      <c r="D130">
+        <v>1.93739069355115</v>
+      </c>
+      <c r="E130">
+        <v>8.4786345439714506</v>
+      </c>
+      <c r="F130">
+        <v>13.9925402149045</v>
+      </c>
+      <c r="G130">
+        <v>1.8002685016829401</v>
+      </c>
+      <c r="H130">
+        <v>3.4360943945484701</v>
+      </c>
+      <c r="I130">
+        <v>0.54078473029928698</v>
+      </c>
+      <c r="J130">
+        <v>4.7384261449277699E-3</v>
+      </c>
+      <c r="K130">
+        <v>1.18783311815706E-3</v>
+      </c>
+      <c r="L130">
+        <v>1.7611025308575699E-2</v>
+      </c>
+      <c r="M130">
+        <v>3.1187542722641102E-4</v>
+      </c>
+      <c r="N130">
+        <v>7.0580675008617604E-3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A131" s="200">
+        <v>1</v>
+      </c>
+      <c r="B131" t="s">
+        <v>400</v>
+      </c>
+      <c r="C131">
+        <v>3.07660386157338E-2</v>
+      </c>
+      <c r="D131">
+        <v>0.56772075502057695</v>
+      </c>
+      <c r="E131">
+        <v>1.74721528744418</v>
+      </c>
+      <c r="F131">
+        <v>1.3397120081413001</v>
+      </c>
+      <c r="G131">
+        <v>0.77401744809311701</v>
+      </c>
+      <c r="H131">
+        <v>9.9773941982873496E-2</v>
+      </c>
+      <c r="I131">
+        <v>4.1610101635774097E-2</v>
+      </c>
+      <c r="J131">
+        <v>9.1141232775618505E-4</v>
+      </c>
+      <c r="K131">
+        <v>2.20390171932858E-4</v>
+      </c>
+      <c r="L131">
+        <v>6.8805816860270305E-5</v>
+      </c>
+      <c r="M131">
+        <v>3.2902302813796598E-5</v>
+      </c>
+      <c r="N131">
+        <v>8.1969828570453197E-4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A132" s="200">
+        <v>1</v>
+      </c>
+      <c r="B132" t="s">
+        <v>401</v>
+      </c>
+      <c r="C132">
+        <v>8.2371266568431294E-3</v>
+      </c>
+      <c r="D132">
+        <v>5.8854373593070303E-2</v>
+      </c>
+      <c r="E132">
+        <v>0.21817760668332001</v>
+      </c>
+      <c r="F132">
+        <v>0.59161760855533496</v>
+      </c>
+      <c r="G132">
+        <v>0.186925293835939</v>
+      </c>
+      <c r="H132">
+        <v>0.15303922755316601</v>
+      </c>
+      <c r="I132">
+        <v>6.5356269088393398E-2</v>
+      </c>
+      <c r="J132">
+        <v>1.5345166990320799E-3</v>
+      </c>
+      <c r="K132">
+        <v>4.2983396530909103E-3</v>
+      </c>
+      <c r="L132">
+        <v>2.75500569573032E-4</v>
+      </c>
+      <c r="M132">
+        <v>3.9966212437860797E-5</v>
+      </c>
+      <c r="N132">
+        <v>1.7466107375704599E-4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A133" s="200">
+        <v>1</v>
+      </c>
+      <c r="B133" t="s">
+        <v>402</v>
+      </c>
+      <c r="C133">
+        <v>1.16993725612691E-2</v>
+      </c>
+      <c r="D133">
+        <v>0.14975991937754099</v>
+      </c>
+      <c r="E133">
+        <v>3.5763446999885602</v>
+      </c>
+      <c r="F133">
+        <v>19.469476655338401</v>
+      </c>
+      <c r="G133">
+        <v>3.98529020934911</v>
+      </c>
+      <c r="H133">
+        <v>1.28593328462867</v>
+      </c>
+      <c r="I133">
+        <v>0.613529563223986</v>
+      </c>
+      <c r="J133">
+        <v>3.7051779336380201E-2</v>
+      </c>
+      <c r="K133">
+        <v>1.6337011155377599E-3</v>
+      </c>
+      <c r="L133">
+        <v>5.7760880175440196E-3</v>
+      </c>
+      <c r="M133">
+        <v>8.1834652989590494E-3</v>
+      </c>
+      <c r="N133">
+        <v>3.0840070208833701E-2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A134" s="200">
+        <v>1</v>
+      </c>
+      <c r="B134" t="s">
+        <v>403</v>
+      </c>
+      <c r="C134">
+        <v>0.306794440466511</v>
+      </c>
+      <c r="D134">
+        <v>10.195703949727299</v>
+      </c>
+      <c r="E134">
+        <v>50.799797976431996</v>
+      </c>
+      <c r="F134">
+        <v>30.663830416712798</v>
+      </c>
+      <c r="G134">
+        <v>25.507200418572602</v>
+      </c>
+      <c r="H134">
+        <v>6.5080531490901601</v>
+      </c>
+      <c r="I134">
+        <v>2.67944377528605E-2</v>
+      </c>
+      <c r="J134">
+        <v>1.26213496888495E-2</v>
+      </c>
+      <c r="K134">
+        <v>1.10938850317777E-2</v>
+      </c>
+      <c r="L134">
+        <v>1.66311283750545E-3</v>
+      </c>
+      <c r="M134">
+        <v>4.7533955848277902E-2</v>
+      </c>
+      <c r="N134">
+        <v>0.12540296521674299</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A135" s="200">
+        <v>1</v>
+      </c>
+      <c r="B135" t="s">
+        <v>404</v>
+      </c>
+      <c r="C135">
+        <v>0.39398218332896501</v>
+      </c>
+      <c r="D135">
+        <v>2.3111598799489999</v>
+      </c>
+      <c r="E135">
+        <v>10.7517135421873</v>
+      </c>
+      <c r="F135">
+        <v>30.690438697939101</v>
+      </c>
+      <c r="G135">
+        <v>13.495832624511699</v>
+      </c>
+      <c r="H135">
+        <v>6.7344272935368403</v>
+      </c>
+      <c r="I135">
+        <v>0.63474593534082602</v>
+      </c>
+      <c r="J135">
+        <v>2.1639531074273102E-2</v>
+      </c>
+      <c r="K135">
+        <v>3.0287375065916399E-2</v>
+      </c>
+      <c r="L135">
+        <v>4.3741296267398998E-2</v>
+      </c>
+      <c r="M135">
+        <v>2.2183493868441301E-4</v>
+      </c>
+      <c r="N135">
+        <v>5.6365130481672897E-3</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A136" s="200">
+        <v>1</v>
+      </c>
+      <c r="B136" t="s">
+        <v>405</v>
+      </c>
+      <c r="C136">
+        <v>2.9472393179452001E-2</v>
+      </c>
+      <c r="D136">
+        <v>0.41351140178370999</v>
+      </c>
+      <c r="E136">
+        <v>0.47177202034757598</v>
+      </c>
+      <c r="F136">
+        <v>1.2267992707189901</v>
+      </c>
+      <c r="G136">
+        <v>1.1326721547092</v>
+      </c>
+      <c r="H136">
+        <v>0.26804854046696902</v>
+      </c>
+      <c r="I136">
+        <v>4.1205187056275001E-3</v>
+      </c>
+      <c r="J136">
+        <v>3.0106676603295799E-3</v>
+      </c>
+      <c r="K136">
+        <v>2.5706081846691301E-3</v>
+      </c>
+      <c r="L136">
+        <v>4.3369743679771402E-4</v>
+      </c>
+      <c r="M136">
+        <v>1.03073710205967E-4</v>
+      </c>
+      <c r="N136">
+        <v>3.4522504308775403E-5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A137" s="200">
+        <v>1</v>
+      </c>
+      <c r="B137" t="s">
+        <v>406</v>
+      </c>
+      <c r="C137">
+        <v>2.33764062970265E-3</v>
+      </c>
+      <c r="D137">
+        <v>0.13200572118895099</v>
+      </c>
+      <c r="E137">
+        <v>0.80615519384476397</v>
+      </c>
+      <c r="F137">
+        <v>4.4800685033314203</v>
+      </c>
+      <c r="G137">
+        <v>4.6927780095475704</v>
+      </c>
+      <c r="H137">
+        <v>2.1539096472459098</v>
+      </c>
+      <c r="I137">
+        <v>0.60830895273861696</v>
+      </c>
+      <c r="J137">
+        <v>1.7375548719343398E-2</v>
+      </c>
+      <c r="K137">
+        <v>3.6914704608422201E-2</v>
+      </c>
+      <c r="L137">
+        <v>1.6349611360266601E-2</v>
+      </c>
+      <c r="M137">
+        <v>9.8127968832718892E-4</v>
+      </c>
+      <c r="N137">
+        <v>8.2796046307846496E-3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A138" s="200">
+        <v>1</v>
+      </c>
+      <c r="B138" t="s">
+        <v>407</v>
+      </c>
+      <c r="C138">
+        <v>4.64618917555054E-2</v>
+      </c>
+      <c r="D138">
+        <v>4.6759594781248803E-2</v>
+      </c>
+      <c r="E138">
+        <v>3.1254543043644798</v>
+      </c>
+      <c r="F138">
+        <v>11.3959495447381</v>
+      </c>
+      <c r="G138">
+        <v>4.4068184704674804</v>
+      </c>
+      <c r="H138">
+        <v>0.77854006017278199</v>
+      </c>
+      <c r="I138">
+        <v>0.242616469218009</v>
+      </c>
+      <c r="J138">
+        <v>4.3668480459706699E-2</v>
+      </c>
+      <c r="K138">
+        <v>2.7911030634309602E-3</v>
+      </c>
+      <c r="L138">
+        <v>1.6352933062345799E-3</v>
+      </c>
+      <c r="M138">
+        <v>2.3383685836123099E-3</v>
+      </c>
+      <c r="N138">
+        <v>5.6030200934058198E-3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A139" s="200">
+        <v>1</v>
+      </c>
+      <c r="B139" t="s">
+        <v>408</v>
+      </c>
+      <c r="C139">
+        <v>2.7082567270754799E-2</v>
+      </c>
+      <c r="D139">
+        <v>0.61066819806051698</v>
+      </c>
+      <c r="E139">
+        <v>6.1670156343211602</v>
+      </c>
+      <c r="F139">
+        <v>9.6077863171410591</v>
+      </c>
+      <c r="G139">
+        <v>6.6442137066586104</v>
+      </c>
+      <c r="H139">
+        <v>1.70956351435095</v>
+      </c>
+      <c r="I139">
+        <v>1.1012033431624899</v>
+      </c>
+      <c r="J139">
+        <v>2.3230536619582E-2</v>
+      </c>
+      <c r="K139">
+        <v>5.7951501128966403E-2</v>
+      </c>
+      <c r="L139">
+        <v>7.5693901520686502E-2</v>
+      </c>
+      <c r="M139">
+        <v>1.0284818350964601E-2</v>
+      </c>
+      <c r="N139">
+        <v>4.4187641454756501E-3</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A140" s="200">
+        <v>1</v>
+      </c>
+      <c r="B140" t="s">
+        <v>409</v>
+      </c>
+      <c r="C140">
+        <v>0.15716447651204399</v>
+      </c>
+      <c r="D140">
+        <v>0.80106929304975805</v>
+      </c>
+      <c r="E140">
+        <v>5.2267219416377797</v>
+      </c>
+      <c r="F140">
+        <v>34.302678263647699</v>
+      </c>
+      <c r="G140">
+        <v>11.7698960325261</v>
+      </c>
+      <c r="H140">
+        <v>5.4221110052556503</v>
+      </c>
+      <c r="I140">
+        <v>0.58876337742137197</v>
+      </c>
+      <c r="J140">
+        <v>8.9799893544684303E-2</v>
+      </c>
+      <c r="K140">
+        <v>2.9410342779643699E-2</v>
+      </c>
+      <c r="L140">
+        <v>3.5556829668952697E-2</v>
+      </c>
+      <c r="M140">
+        <v>6.3119615265689699E-4</v>
+      </c>
+      <c r="N140">
+        <v>1.43360504186856E-2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A141" s="200">
+        <v>1</v>
+      </c>
+      <c r="B141" t="s">
+        <v>410</v>
+      </c>
+      <c r="C141">
+        <v>5.1478568980485298E-3</v>
+      </c>
+      <c r="D141">
+        <v>7.0342420346098E-2</v>
+      </c>
+      <c r="E141">
+        <v>0.71463065899297595</v>
+      </c>
+      <c r="F141">
+        <v>1.79142704565286</v>
+      </c>
+      <c r="G141">
+        <v>0.72387301080822697</v>
+      </c>
+      <c r="H141">
+        <v>0.39991370987171099</v>
+      </c>
+      <c r="I141">
+        <v>7.1007525568695995E-2</v>
+      </c>
+      <c r="J141">
+        <v>3.6270791527674298E-3</v>
+      </c>
+      <c r="K141">
+        <v>1.82704759515549E-3</v>
+      </c>
+      <c r="L141">
+        <v>3.6632913140811699E-3</v>
+      </c>
+      <c r="M141">
+        <v>1.21834850464413E-3</v>
+      </c>
+      <c r="N141">
+        <v>4.8379247733641202E-4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A142" s="200">
+        <v>1</v>
+      </c>
+      <c r="B142" t="s">
+        <v>411</v>
+      </c>
+      <c r="C142">
+        <v>4.4083265441284703E-3</v>
+      </c>
+      <c r="D142">
+        <v>4.2178429174772797E-2</v>
+      </c>
+      <c r="E142">
+        <v>0.31428955139897802</v>
+      </c>
+      <c r="F142">
+        <v>0.69407559384613804</v>
+      </c>
+      <c r="G142">
+        <v>0.261347590389849</v>
+      </c>
+      <c r="H142">
+        <v>1.5246809289441599E-2</v>
+      </c>
+      <c r="I142">
+        <v>6.9049560737043901E-3</v>
+      </c>
+      <c r="J142">
+        <v>2.5946639619064699E-3</v>
+      </c>
+      <c r="K142">
+        <v>1.49833819599378E-5</v>
+      </c>
+      <c r="L142">
+        <v>1.15346359061226E-3</v>
+      </c>
+      <c r="M142">
+        <v>9.3385100860831098E-4</v>
+      </c>
+      <c r="N142">
+        <v>6.3444811628132099E-3</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A143" s="200">
+        <v>1</v>
+      </c>
+      <c r="B143" t="s">
+        <v>412</v>
+      </c>
+      <c r="C143">
+        <v>1.47468492063621E-2</v>
+      </c>
+      <c r="D143">
+        <v>2.0038044385182901E-2</v>
+      </c>
+      <c r="E143">
+        <v>0.47522600915020802</v>
+      </c>
+      <c r="F143">
+        <v>1.2134141828214</v>
+      </c>
+      <c r="G143">
+        <v>1.4891530108176301</v>
+      </c>
+      <c r="H143">
+        <v>0.60004558651965301</v>
+      </c>
+      <c r="I143">
+        <v>0.16971379465640099</v>
+      </c>
+      <c r="J143">
+        <v>1.29766519549885E-2</v>
+      </c>
+      <c r="K143">
+        <v>6.5741926898956297E-3</v>
+      </c>
+      <c r="L143">
+        <v>1.1911948987696301E-4</v>
+      </c>
+      <c r="M143">
+        <v>8.6262877802533808E-3</v>
+      </c>
+      <c r="N143">
+        <v>1.6567630311438E-2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A144" s="200">
+        <v>1</v>
+      </c>
+      <c r="B144" t="s">
+        <v>413</v>
+      </c>
+      <c r="C144">
+        <v>3.2973695159479101E-2</v>
+      </c>
+      <c r="D144">
+        <v>5.18309800366972E-2</v>
+      </c>
+      <c r="E144">
+        <v>1.1850660794253201</v>
+      </c>
+      <c r="F144">
+        <v>3.1320832364968099</v>
+      </c>
+      <c r="G144">
+        <v>4.6022488161666599</v>
+      </c>
+      <c r="H144">
+        <v>0.355823339132744</v>
+      </c>
+      <c r="I144">
+        <v>0.12978772231100999</v>
+      </c>
+      <c r="J144">
+        <v>2.7606943899440201E-2</v>
+      </c>
+      <c r="K144">
+        <v>5.8560679864413402E-4</v>
+      </c>
+      <c r="L144">
+        <v>7.3200270660749196E-4</v>
+      </c>
+      <c r="M144">
+        <v>4.6434808466172497E-5</v>
+      </c>
+      <c r="N144">
+        <v>6.3204592997060202E-2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A145" s="200">
+        <v>1</v>
+      </c>
+      <c r="B145" t="s">
+        <v>414</v>
+      </c>
+      <c r="C145">
+        <v>0.279236692423666</v>
+      </c>
+      <c r="D145">
+        <v>4.34730131791361</v>
+      </c>
+      <c r="E145">
+        <v>9.4704293010678295</v>
+      </c>
+      <c r="F145">
+        <v>10.522726184735699</v>
+      </c>
+      <c r="G145">
+        <v>9.5980113913633307</v>
+      </c>
+      <c r="H145">
+        <v>2.8819985041123202</v>
+      </c>
+      <c r="I145">
+        <v>0.75364112380691295</v>
+      </c>
+      <c r="J145">
+        <v>1.1767649298150299E-2</v>
+      </c>
+      <c r="K145">
+        <v>1.8427677529879499E-3</v>
+      </c>
+      <c r="L145">
+        <v>3.0031111067187699E-2</v>
+      </c>
+      <c r="M145">
+        <v>3.7082298776453201E-3</v>
+      </c>
+      <c r="N145">
+        <v>8.8154813918704892E-3</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A146" s="200">
+        <v>1</v>
+      </c>
+      <c r="B146" t="s">
+        <v>415</v>
+      </c>
+      <c r="C146">
+        <v>0.24023443299441399</v>
+      </c>
+      <c r="D146">
+        <v>0.84914187109660899</v>
+      </c>
+      <c r="E146">
+        <v>4.4199725063056201</v>
+      </c>
+      <c r="F146">
+        <v>9.4224662002337904</v>
+      </c>
+      <c r="G146">
+        <v>2.0395509553843101</v>
+      </c>
+      <c r="H146">
+        <v>2.0657808495189101</v>
+      </c>
+      <c r="I146">
+        <v>5.8178966195091497E-2</v>
+      </c>
+      <c r="J146">
+        <v>1.9739696417576699E-3</v>
+      </c>
+      <c r="K146">
+        <v>6.1260325601851301E-4</v>
+      </c>
+      <c r="L146">
+        <v>2.5979176140093802E-3</v>
+      </c>
+      <c r="M146">
+        <v>2.2033823022352701E-3</v>
+      </c>
+      <c r="N146">
+        <v>2.1905625985271699E-2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A147" s="200">
+        <v>1</v>
+      </c>
+      <c r="B147" t="s">
+        <v>416</v>
+      </c>
+      <c r="C147">
+        <v>1.1455634519672299E-2</v>
+      </c>
+      <c r="D147">
+        <v>0.11006758152829201</v>
+      </c>
+      <c r="E147">
+        <v>0.745146415588267</v>
+      </c>
+      <c r="F147">
+        <v>2.7396985613570002</v>
+      </c>
+      <c r="G147">
+        <v>2.3517061596937299</v>
+      </c>
+      <c r="H147">
+        <v>0.31410695455794002</v>
+      </c>
+      <c r="I147">
+        <v>0.13392944791820399</v>
+      </c>
+      <c r="J147">
+        <v>2.47554427932955E-3</v>
+      </c>
+      <c r="K147">
+        <v>9.79462567750755E-4</v>
+      </c>
+      <c r="L147">
+        <v>5.7843625591757803E-4</v>
+      </c>
+      <c r="M147">
+        <v>4.3250658582349999E-2</v>
+      </c>
+      <c r="N147">
+        <v>1.5869310711971899E-2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A148" s="200">
+        <v>1</v>
+      </c>
+      <c r="B148" t="s">
+        <v>417</v>
+      </c>
+      <c r="C148">
+        <v>5.4600898094965697E-2</v>
+      </c>
+      <c r="D148">
+        <v>0.16567974000999799</v>
+      </c>
+      <c r="E148">
+        <v>1.7408974125310901</v>
+      </c>
+      <c r="F148">
+        <v>3.9054770928212399</v>
+      </c>
+      <c r="G148">
+        <v>3.4668374344785602</v>
+      </c>
+      <c r="H148">
+        <v>1.0355051628793099</v>
+      </c>
+      <c r="I148">
+        <v>0.30186280926874098</v>
+      </c>
+      <c r="J148">
+        <v>2.7382656906691099E-2</v>
+      </c>
+      <c r="K148">
+        <v>1.07605103181307E-2</v>
+      </c>
+      <c r="L148">
+        <v>1.3957537603999599E-2</v>
+      </c>
+      <c r="M148">
+        <v>2.2942357541703E-4</v>
+      </c>
+      <c r="N148">
+        <v>8.5199683563239505E-3</v>
+      </c>
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A149" s="200">
+        <v>1</v>
+      </c>
+      <c r="B149" t="s">
+        <v>418</v>
+      </c>
+      <c r="C149">
+        <v>3.1768370843020099E-3</v>
+      </c>
+      <c r="D149">
+        <v>0.117291730845729</v>
+      </c>
+      <c r="E149">
+        <v>1.0542099827484199</v>
+      </c>
+      <c r="F149">
+        <v>4.26675169323725</v>
+      </c>
+      <c r="G149">
+        <v>4.1986826416761103</v>
+      </c>
+      <c r="H149">
+        <v>0.85532690840419001</v>
+      </c>
+      <c r="I149">
+        <v>0.14788442618588099</v>
+      </c>
+      <c r="J149">
+        <v>0.104613661969593</v>
+      </c>
+      <c r="K149">
+        <v>6.1900590459128303E-3</v>
+      </c>
+      <c r="L149">
+        <v>1.8320128515456201E-3</v>
+      </c>
+      <c r="M149">
+        <v>4.0110030714988899E-2</v>
+      </c>
+      <c r="N149">
+        <v>2.22299707344692E-3</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A150" s="200">
+        <v>1</v>
+      </c>
+      <c r="B150" t="s">
+        <v>419</v>
+      </c>
+      <c r="C150">
+        <v>4.8894348589937103E-2</v>
+      </c>
+      <c r="D150">
+        <v>0.105887580252264</v>
+      </c>
+      <c r="E150">
+        <v>1.1532750377232801</v>
+      </c>
+      <c r="F150">
+        <v>6.56404985609477</v>
+      </c>
+      <c r="G150">
+        <v>6.3368682441819297</v>
+      </c>
+      <c r="H150">
+        <v>0.40336504355522701</v>
+      </c>
+      <c r="I150">
+        <v>0.17988221385359601</v>
+      </c>
+      <c r="J150">
+        <v>2.1377668906735099E-3</v>
+      </c>
+      <c r="K150">
+        <v>7.5868282911986196E-4</v>
+      </c>
+      <c r="L150">
+        <v>1.01143511638726E-2</v>
+      </c>
+      <c r="M150">
+        <v>7.8678206283973795E-4</v>
+      </c>
+      <c r="N150">
+        <v>1.6046347753969901E-3</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A151" s="200">
+        <v>1</v>
+      </c>
+      <c r="B151" t="s">
+        <v>420</v>
+      </c>
+      <c r="C151">
+        <v>7.6654583148611597E-3</v>
+      </c>
+      <c r="D151">
+        <v>3.5727940447709602E-3</v>
+      </c>
+      <c r="E151">
+        <v>2.28040323464044E-2</v>
+      </c>
+      <c r="F151">
+        <v>0.15296911635629001</v>
+      </c>
+      <c r="G151">
+        <v>0.42325129539071699</v>
+      </c>
+      <c r="H151">
+        <v>0.36839684415943202</v>
+      </c>
+      <c r="I151">
+        <v>2.35118194504268E-2</v>
+      </c>
+      <c r="J151">
+        <v>2.6430146187045301E-5</v>
+      </c>
+      <c r="K151">
+        <v>3.8006204549789199E-4</v>
+      </c>
+      <c r="L151">
+        <v>2.2835952289615601E-4</v>
+      </c>
+      <c r="M151">
+        <v>8.1945532387514596E-5</v>
+      </c>
+      <c r="N151">
+        <v>1.12072182101721E-2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A152" s="200">
+        <v>1</v>
+      </c>
+      <c r="B152" t="s">
+        <v>421</v>
+      </c>
+      <c r="C152">
+        <v>1.3499274631949901E-2</v>
+      </c>
+      <c r="D152">
+        <v>3.1642027913407901E-2</v>
+      </c>
+      <c r="E152">
+        <v>0.32402367260719001</v>
+      </c>
+      <c r="F152">
+        <v>1.4256296074469199</v>
+      </c>
+      <c r="G152">
+        <v>2.18177169661978</v>
+      </c>
+      <c r="H152">
+        <v>0.48538394763788301</v>
+      </c>
+      <c r="I152">
+        <v>1.87765835057976E-3</v>
+      </c>
+      <c r="J152">
+        <v>6.7729041112410003E-4</v>
+      </c>
+      <c r="K152">
+        <v>3.5055823701195498E-4</v>
+      </c>
+      <c r="L152">
+        <v>8.8099293546841102E-5</v>
+      </c>
+      <c r="M152">
+        <v>3.2955703706652401E-3</v>
+      </c>
+      <c r="N152">
+        <v>5.2057166307088497E-3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A153" s="200">
+        <v>1</v>
+      </c>
+      <c r="B153" t="s">
+        <v>422</v>
+      </c>
+      <c r="C153">
+        <v>1.7712380512965901E-3</v>
+      </c>
+      <c r="D153">
+        <v>1.01150102153601E-2</v>
+      </c>
+      <c r="E153">
+        <v>6.5334459010999907E-2</v>
+      </c>
+      <c r="F153">
+        <v>0.344583401890731</v>
+      </c>
+      <c r="G153">
+        <v>0.134842736934597</v>
+      </c>
+      <c r="H153">
+        <v>5.4029481225032899E-2</v>
+      </c>
+      <c r="I153">
+        <v>6.59655364621866E-3</v>
+      </c>
+      <c r="J153">
+        <v>7.63438583522246E-4</v>
+      </c>
+      <c r="K153">
+        <v>1.05927392441679E-4</v>
+      </c>
+      <c r="L153">
+        <v>3.5693026336361598E-5</v>
+      </c>
+      <c r="M153">
+        <v>4.2440948825135797E-5</v>
+      </c>
+      <c r="N153">
+        <v>7.0490875468314499E-5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A154" s="200">
+        <v>1</v>
+      </c>
+      <c r="B154" t="s">
+        <v>423</v>
+      </c>
+      <c r="C154">
+        <v>1.96750063432231E-4</v>
+      </c>
+      <c r="D154">
+        <v>4.4430192041343998E-3</v>
+      </c>
+      <c r="E154">
+        <v>3.9176427025209702E-2</v>
+      </c>
+      <c r="F154">
+        <v>8.7403517328468697E-2</v>
+      </c>
+      <c r="G154">
+        <v>0.14335145499156399</v>
+      </c>
+      <c r="H154">
+        <v>3.7532109366147502E-2</v>
+      </c>
+      <c r="I154">
+        <v>6.9114240725623704E-4</v>
+      </c>
+      <c r="J154">
+        <v>2.65345540115324E-4</v>
+      </c>
+      <c r="K154">
+        <v>3.4478317396981003E-5</v>
+      </c>
+      <c r="L154">
+        <v>1.11552915989178E-5</v>
+      </c>
+      <c r="M154">
+        <v>4.1620513070136299E-4</v>
+      </c>
+      <c r="N154">
+        <v>1.4455027031230299E-4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A155" s="200">
+        <v>1</v>
+      </c>
+      <c r="B155" t="s">
+        <v>424</v>
+      </c>
+      <c r="C155">
+        <v>5.7830065008176298E-3</v>
+      </c>
+      <c r="D155">
+        <v>3.8555480633197997E-2</v>
+      </c>
+      <c r="E155">
+        <v>0.17119897335482401</v>
+      </c>
+      <c r="F155">
+        <v>2.3470625408614798</v>
+      </c>
+      <c r="G155">
+        <v>2.7527659509519702</v>
+      </c>
+      <c r="H155">
+        <v>0.18203373911977999</v>
+      </c>
+      <c r="I155">
+        <v>1.20879032855857E-2</v>
+      </c>
+      <c r="J155">
+        <v>2.3321853621965101E-2</v>
+      </c>
+      <c r="K155">
+        <v>2.33459336217441E-4</v>
+      </c>
+      <c r="L155">
+        <v>1.2851313820071201E-3</v>
+      </c>
+      <c r="M155">
+        <v>8.24851606970945E-4</v>
+      </c>
+      <c r="N155">
+        <v>2.0805417123298101E-3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A156" s="200">
+        <v>1</v>
+      </c>
+      <c r="B156" t="s">
+        <v>425</v>
+      </c>
+      <c r="C156">
+        <v>1.5165146628153599E-3</v>
+      </c>
+      <c r="D156">
+        <v>7.9012996276599204E-2</v>
+      </c>
+      <c r="E156">
+        <v>1.19149378484219</v>
+      </c>
+      <c r="F156">
+        <v>2.98978587654788</v>
+      </c>
+      <c r="G156">
+        <v>1.6385905639200899</v>
+      </c>
+      <c r="H156">
+        <v>0.60194761955713505</v>
+      </c>
+      <c r="I156">
+        <v>0.11107741165726399</v>
+      </c>
+      <c r="J156">
+        <v>1.5253489670280399E-2</v>
+      </c>
+      <c r="K156">
+        <v>3.4185922357821602E-4</v>
+      </c>
+      <c r="L156">
+        <v>6.5297634322970799E-4</v>
+      </c>
+      <c r="M156">
+        <v>1.8275637087313201E-3</v>
+      </c>
+      <c r="N156">
+        <v>4.9029381803826697E-3</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A157" s="200">
+        <v>1</v>
+      </c>
+      <c r="B157" t="s">
+        <v>426</v>
+      </c>
+      <c r="C157">
+        <v>4.0140847968168497E-2</v>
+      </c>
+      <c r="D157">
+        <v>1.2916517417537699E-2</v>
+      </c>
+      <c r="E157">
+        <v>0.41271912925000798</v>
+      </c>
+      <c r="F157">
+        <v>4.6112968041303999</v>
+      </c>
+      <c r="G157">
+        <v>3.5447211463721899</v>
+      </c>
+      <c r="H157">
+        <v>0.505033962742374</v>
+      </c>
+      <c r="I157">
+        <v>0.20939005368786501</v>
+      </c>
+      <c r="J157">
+        <v>1.2548966755536999E-2</v>
+      </c>
+      <c r="K157">
+        <v>3.94652116439772E-4</v>
+      </c>
+      <c r="L157">
+        <v>5.7903761505940902E-4</v>
+      </c>
+      <c r="M157">
+        <v>1.0834733216015801E-4</v>
+      </c>
+      <c r="N157">
+        <v>7.8999247031909996E-4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A158" s="200">
+        <v>1</v>
+      </c>
+      <c r="B158" t="s">
+        <v>427</v>
+      </c>
+      <c r="C158">
+        <v>4.8154850379727504E-3</v>
+      </c>
+      <c r="D158">
+        <v>3.5706369811411101E-3</v>
+      </c>
+      <c r="E158">
+        <v>7.2364289926108404E-3</v>
+      </c>
+      <c r="F158">
+        <v>6.6769354523431301E-3</v>
+      </c>
+      <c r="G158">
+        <v>1.16853925467618E-2</v>
+      </c>
+      <c r="H158">
+        <v>1.62839918500542E-3</v>
+      </c>
+      <c r="I158">
+        <v>2.2167672636537001E-3</v>
+      </c>
+      <c r="J158">
+        <v>1.4048686911916599E-5</v>
+      </c>
+      <c r="K158">
+        <v>2.05148611207859E-6</v>
+      </c>
+      <c r="L158">
+        <v>1.5391234119681001E-7</v>
+      </c>
+      <c r="M158">
+        <v>3.0868864215101501E-7</v>
+      </c>
+      <c r="N158">
+        <v>5.4689382071454801E-5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A159" s="200">
+        <v>1</v>
+      </c>
+      <c r="B159" t="s">
+        <v>428</v>
+      </c>
+      <c r="C159">
+        <v>8.0219908562562602E-4</v>
+      </c>
+      <c r="D159">
+        <v>2.2004190287312798E-2</v>
+      </c>
+      <c r="E159">
+        <v>0.52192793996759801</v>
+      </c>
+      <c r="F159">
+        <v>1.0480003096594701</v>
+      </c>
+      <c r="G159">
+        <v>1.71216464122025</v>
+      </c>
+      <c r="H159">
+        <v>0.45828489186549798</v>
+      </c>
+      <c r="I159">
+        <v>6.8314018556080797E-2</v>
+      </c>
+      <c r="J159">
+        <v>6.7463236446226399E-2</v>
+      </c>
+      <c r="K159">
+        <v>4.0721707477941701E-4</v>
+      </c>
+      <c r="L159">
+        <v>6.4669160443122899E-5</v>
+      </c>
+      <c r="M159">
+        <v>3.6641708189556201E-4</v>
+      </c>
+      <c r="N159">
+        <v>9.2401021627407803E-5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A160" s="200">
+        <v>1</v>
+      </c>
+      <c r="B160" t="s">
+        <v>429</v>
+      </c>
+      <c r="C160">
+        <v>5.4414959268281305E-4</v>
+      </c>
+      <c r="D160">
+        <v>1.02382889980069E-3</v>
+      </c>
+      <c r="E160">
+        <v>0.207162752923782</v>
+      </c>
+      <c r="F160">
+        <v>1.44940871170867</v>
+      </c>
+      <c r="G160">
+        <v>0.44454246935882402</v>
+      </c>
+      <c r="H160">
+        <v>0.16983262447397701</v>
+      </c>
+      <c r="I160">
+        <v>6.5053271197880597E-2</v>
+      </c>
+      <c r="J160">
+        <v>6.3964615869874198E-4</v>
+      </c>
+      <c r="K160">
+        <v>4.9949773723761702E-5</v>
+      </c>
+      <c r="L160">
+        <v>1.7573202606237001E-4</v>
+      </c>
+      <c r="M160">
+        <v>8.6773950697046204E-6</v>
+      </c>
+      <c r="N160">
+        <v>7.8639104982957005E-4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A161" s="200">
+        <v>1</v>
+      </c>
+      <c r="B161" t="s">
+        <v>430</v>
+      </c>
+      <c r="C161">
+        <v>1.6238342028801301E-2</v>
+      </c>
+      <c r="D161">
+        <v>0.50155182874815896</v>
+      </c>
+      <c r="E161">
+        <v>4.8377594368130703</v>
+      </c>
+      <c r="F161">
+        <v>10.571722528060601</v>
+      </c>
+      <c r="G161">
+        <v>7.60970085395304</v>
+      </c>
+      <c r="H161">
+        <v>0.94706352585883402</v>
+      </c>
+      <c r="I161">
+        <v>0.54478371740431697</v>
+      </c>
+      <c r="J161">
+        <v>3.0976860557523698E-3</v>
+      </c>
+      <c r="K161">
+        <v>1.0033690960071901E-3</v>
+      </c>
+      <c r="L161">
+        <v>6.0810762607769499E-4</v>
+      </c>
+      <c r="M161">
+        <v>4.0335450911978E-4</v>
+      </c>
+      <c r="N161">
+        <v>2.3216929004253998E-3</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A162" s="200">
+        <v>1</v>
+      </c>
+      <c r="B162" t="s">
+        <v>431</v>
+      </c>
+      <c r="C162">
+        <v>8.5787629595280301E-2</v>
+      </c>
+      <c r="D162">
+        <v>0.41384280173592303</v>
+      </c>
+      <c r="E162">
+        <v>7.3025056187950801</v>
+      </c>
+      <c r="F162">
+        <v>13.959943630156101</v>
+      </c>
+      <c r="G162">
+        <v>5.0079246697807003</v>
+      </c>
+      <c r="H162">
+        <v>0.66773680067374597</v>
+      </c>
+      <c r="I162">
+        <v>0.155747744159414</v>
+      </c>
+      <c r="J162">
+        <v>8.6715294504231804E-3</v>
+      </c>
+      <c r="K162">
+        <v>4.9965906433434796E-3</v>
+      </c>
+      <c r="L162">
+        <v>8.0501130818772101E-4</v>
+      </c>
+      <c r="M162">
+        <v>3.2970883702349899E-3</v>
+      </c>
+      <c r="N162">
+        <v>1.75504070953105E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A163" s="200">
+        <v>1</v>
+      </c>
+      <c r="B163" t="s">
+        <v>432</v>
+      </c>
+      <c r="C163">
+        <v>0.11448233378631199</v>
+      </c>
+      <c r="D163">
+        <v>0.55747064795010703</v>
+      </c>
+      <c r="E163">
+        <v>6.8682791527165197</v>
+      </c>
+      <c r="F163">
+        <v>19.718208286911999</v>
+      </c>
+      <c r="G163">
+        <v>5.7490156864596198</v>
+      </c>
+      <c r="H163">
+        <v>0.47427815450430899</v>
+      </c>
+      <c r="I163">
+        <v>0.175579336272537</v>
+      </c>
+      <c r="J163">
+        <v>2.5058193471183099E-2</v>
+      </c>
+      <c r="K163">
+        <v>1.1203473627081799E-3</v>
+      </c>
+      <c r="L163">
+        <v>1.18318745356298E-3</v>
+      </c>
+      <c r="M163">
+        <v>1.4565750414473199E-2</v>
+      </c>
+      <c r="N163">
+        <v>0.12812194264766899</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A164" s="200">
+        <v>1</v>
+      </c>
+      <c r="B164" t="s">
+        <v>433</v>
+      </c>
+      <c r="C164">
+        <v>0.73952506773986904</v>
+      </c>
+      <c r="D164">
+        <v>6.3279515718069996</v>
+      </c>
+      <c r="E164">
+        <v>15.245815180591499</v>
+      </c>
+      <c r="F164">
+        <v>34.872638288582401</v>
+      </c>
+      <c r="G164">
+        <v>24.498139669241901</v>
+      </c>
+      <c r="H164">
+        <v>5.3624695871606596</v>
+      </c>
+      <c r="I164">
+        <v>3.0212792675824902</v>
+      </c>
+      <c r="J164">
+        <v>0.130733808671367</v>
+      </c>
+      <c r="K164">
+        <v>9.23656680716156E-2</v>
+      </c>
+      <c r="L164">
+        <v>1.39040933357745E-2</v>
+      </c>
+      <c r="M164">
+        <v>1.49815418253956E-2</v>
+      </c>
+      <c r="N164">
+        <v>2.4858491666375901E-3</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A165" s="200">
+        <v>1</v>
+      </c>
+      <c r="B165" t="s">
+        <v>434</v>
+      </c>
+      <c r="C165">
+        <v>0.11192042398674</v>
+      </c>
+      <c r="D165">
+        <v>0.108740327666804</v>
+      </c>
+      <c r="E165">
+        <v>1.4702967848634301</v>
+      </c>
+      <c r="F165">
+        <v>35.047832498818799</v>
+      </c>
+      <c r="G165">
+        <v>22.3706951164034</v>
+      </c>
+      <c r="H165">
+        <v>11.783731217149599</v>
+      </c>
+      <c r="I165">
+        <v>1.3319469613703101</v>
+      </c>
+      <c r="J165">
+        <v>7.5171800003093703E-2</v>
+      </c>
+      <c r="K165">
+        <v>0.123994649510068</v>
+      </c>
+      <c r="L165">
+        <v>0.472876591181628</v>
+      </c>
+      <c r="M165">
+        <v>8.9149572471594798E-3</v>
+      </c>
+      <c r="N165">
+        <v>1.4208693600110499E-2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A166" s="200">
+        <v>1</v>
+      </c>
+      <c r="B166" t="s">
+        <v>435</v>
+      </c>
+      <c r="C166">
+        <v>9.8348683883894908E-3</v>
+      </c>
+      <c r="D166">
+        <v>0.17766177211769599</v>
+      </c>
+      <c r="E166">
+        <v>0.46563819421865998</v>
+      </c>
+      <c r="F166">
+        <v>2.0881654892028298</v>
+      </c>
+      <c r="G166">
+        <v>2.3743071748442102</v>
+      </c>
+      <c r="H166">
+        <v>1.12664950576909</v>
+      </c>
+      <c r="I166">
+        <v>0.38994924262467201</v>
+      </c>
+      <c r="J166">
+        <v>1.03873179036493E-2</v>
+      </c>
+      <c r="K166">
+        <v>6.9903809873302098E-3</v>
+      </c>
+      <c r="L166">
+        <v>2.42019364658757E-4</v>
+      </c>
+      <c r="M166">
+        <v>1.65468353784124E-3</v>
+      </c>
+      <c r="N166">
+        <v>1.28626857342965E-3</v>
+      </c>
+    </row>
+    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A167" s="200">
+        <v>1</v>
+      </c>
+      <c r="B167" t="s">
+        <v>436</v>
+      </c>
+      <c r="C167">
+        <v>1.7155761671219499E-2</v>
+      </c>
+      <c r="D167">
+        <v>0.54535042259939304</v>
+      </c>
+      <c r="E167">
+        <v>5.1317363635929301</v>
+      </c>
+      <c r="F167">
+        <v>19.299589406876699</v>
+      </c>
+      <c r="G167">
+        <v>45.516514349663296</v>
+      </c>
+      <c r="H167">
+        <v>3.4528636566431601</v>
+      </c>
+      <c r="I167">
+        <v>0.328438838359154</v>
+      </c>
+      <c r="J167">
+        <v>4.80289782224744E-2</v>
+      </c>
+      <c r="K167">
+        <v>3.4462465516525098E-2</v>
+      </c>
+      <c r="L167">
+        <v>1.3813005601336701E-2</v>
+      </c>
+      <c r="M167">
+        <v>4.3417634027590499E-4</v>
+      </c>
+      <c r="N167">
+        <v>7.6429515509119805E-2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A168" s="200">
+        <v>1</v>
+      </c>
+      <c r="B168" t="s">
+        <v>437</v>
+      </c>
+      <c r="C168">
+        <v>0.15537421876128801</v>
+      </c>
+      <c r="D168">
+        <v>0.22231841580960601</v>
+      </c>
+      <c r="E168">
+        <v>4.1929346928252897</v>
+      </c>
+      <c r="F168">
+        <v>16.207809135995099</v>
+      </c>
+      <c r="G168">
+        <v>33.436980448719801</v>
+      </c>
+      <c r="H168">
+        <v>0.70137766256094902</v>
+      </c>
+      <c r="I168">
+        <v>0.852324688965309</v>
+      </c>
+      <c r="J168">
+        <v>9.3054178204158094E-2</v>
+      </c>
+      <c r="K168">
+        <v>1.1684273156889999E-2</v>
+      </c>
+      <c r="L168">
+        <v>1.07012864764545E-2</v>
+      </c>
+      <c r="M168">
+        <v>4.1362991168586202E-2</v>
+      </c>
+      <c r="N168">
+        <v>3.2586810320800103E-2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A169" s="200">
+        <v>1</v>
+      </c>
+      <c r="B169" t="s">
+        <v>438</v>
+      </c>
+      <c r="C169">
+        <v>0.18177276017771299</v>
+      </c>
+      <c r="D169">
+        <v>0.25493012899523199</v>
+      </c>
+      <c r="E169">
+        <v>2.2869293415958101</v>
+      </c>
+      <c r="F169">
+        <v>9.9459622541447796</v>
+      </c>
+      <c r="G169">
+        <v>7.5913152089409897</v>
+      </c>
+      <c r="H169">
+        <v>2.3084717942262998</v>
+      </c>
+      <c r="I169">
+        <v>2.1326817338549899</v>
+      </c>
+      <c r="J169">
+        <v>0.21557025119411599</v>
+      </c>
+      <c r="K169">
+        <v>4.5996231112555496E-3</v>
+      </c>
+      <c r="L169">
+        <v>3.07655182760358E-2</v>
+      </c>
+      <c r="M169">
+        <v>1.9690457462673101E-3</v>
+      </c>
+      <c r="N169">
+        <v>4.62445920601762E-4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A170" s="200">
+        <v>1</v>
+      </c>
+      <c r="B170" t="s">
+        <v>439</v>
+      </c>
+      <c r="C170">
+        <v>9.2117921565284103E-2</v>
+      </c>
+      <c r="D170">
+        <v>4.41696113542452E-2</v>
+      </c>
+      <c r="E170">
+        <v>0.78619863080555896</v>
+      </c>
+      <c r="F170">
+        <v>2.1439868733421701</v>
+      </c>
+      <c r="G170">
+        <v>0.20803547198846101</v>
+      </c>
+      <c r="H170">
+        <v>0.36164381826644898</v>
+      </c>
+      <c r="I170">
+        <v>6.8195876528517801E-2</v>
+      </c>
+      <c r="J170">
+        <v>2.6963973874714799E-3</v>
+      </c>
+      <c r="K170">
+        <v>7.6317052513378604E-4</v>
+      </c>
+      <c r="L170">
+        <v>1.5123533496675E-4</v>
+      </c>
+      <c r="M170">
+        <v>1.1909283209644E-2</v>
+      </c>
+      <c r="N170">
+        <v>4.8939843096662702E-4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A171" s="200">
+        <v>1</v>
+      </c>
+      <c r="B171" t="s">
+        <v>440</v>
+      </c>
+      <c r="C171">
+        <v>3.5359959945421002E-2</v>
+      </c>
+      <c r="D171">
+        <v>0.24102870694668599</v>
+      </c>
+      <c r="E171">
+        <v>2.0191637810800902</v>
+      </c>
+      <c r="F171">
+        <v>10.170434008205101</v>
+      </c>
+      <c r="G171">
+        <v>10.248658277215201</v>
+      </c>
+      <c r="H171">
+        <v>5.4760171260580099</v>
+      </c>
+      <c r="I171">
+        <v>3.1978123646356602</v>
+      </c>
+      <c r="J171">
+        <v>0.229876054022399</v>
+      </c>
+      <c r="K171">
+        <v>1.50104387815145E-2</v>
+      </c>
+      <c r="L171">
+        <v>3.7154473757170403E-2</v>
+      </c>
+      <c r="M171">
+        <v>6.4343087733759099E-3</v>
+      </c>
+      <c r="N171">
+        <v>5.5207038714366703E-3</v>
+      </c>
+    </row>
+    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A172" s="200">
+        <v>1</v>
+      </c>
+      <c r="B172" t="s">
+        <v>441</v>
+      </c>
+      <c r="C172">
+        <v>4.2948700104632698E-2</v>
+      </c>
+      <c r="D172">
+        <v>8.7212053263934095E-2</v>
+      </c>
+      <c r="E172">
+        <v>0.59928267183572204</v>
+      </c>
+      <c r="F172">
+        <v>2.0438680463654801</v>
+      </c>
+      <c r="G172">
+        <v>3.68164062757754</v>
+      </c>
+      <c r="H172">
+        <v>1.5344823113027899</v>
+      </c>
+      <c r="I172">
+        <v>0.70309851647353505</v>
+      </c>
+      <c r="J172">
+        <v>0.129516618990063</v>
+      </c>
+      <c r="K172">
+        <v>4.1062083817125696E-3</v>
+      </c>
+      <c r="L172">
+        <v>2.77969071869372E-3</v>
+      </c>
+      <c r="M172">
+        <v>7.3087216614545799E-5</v>
+      </c>
+      <c r="N172">
+        <v>2.1546984306091001E-2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A173" s="200">
+        <v>1</v>
+      </c>
+      <c r="B173" t="s">
+        <v>442</v>
+      </c>
+      <c r="C173">
+        <v>0.464465154540879</v>
+      </c>
+      <c r="D173">
+        <v>1.5019170663221899</v>
+      </c>
+      <c r="E173">
+        <v>9.0806439461165294</v>
+      </c>
+      <c r="F173">
+        <v>31.7260502232295</v>
+      </c>
+      <c r="G173">
+        <v>14.1877674689937</v>
+      </c>
+      <c r="H173">
+        <v>7.3793563652046803</v>
+      </c>
+      <c r="I173">
+        <v>8.0801153316865193</v>
+      </c>
+      <c r="J173">
+        <v>0.95576133664503704</v>
+      </c>
+      <c r="K173">
+        <v>0.15127568228938401</v>
+      </c>
+      <c r="L173">
+        <v>0.219666142340702</v>
+      </c>
+      <c r="M173">
+        <v>1.4199920179579601E-2</v>
+      </c>
+      <c r="N173">
+        <v>0.184909255509594</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A174" s="200">
+        <v>1</v>
+      </c>
+      <c r="B174" t="s">
+        <v>443</v>
+      </c>
+      <c r="C174">
+        <v>1.5189069799269901</v>
+      </c>
+      <c r="D174">
+        <v>4.81525474023932</v>
+      </c>
+      <c r="E174">
+        <v>23.574535308298799</v>
+      </c>
+      <c r="F174">
+        <v>81.466661024121905</v>
+      </c>
+      <c r="G174">
+        <v>45.984272618957903</v>
+      </c>
+      <c r="H174">
+        <v>8.4791605800984495</v>
+      </c>
+      <c r="I174">
+        <v>0.32349010834338199</v>
+      </c>
+      <c r="J174">
+        <v>6.8151462597555801E-3</v>
+      </c>
+      <c r="K174">
+        <v>0.107374965208561</v>
+      </c>
+      <c r="L174">
+        <v>2.7573124242283201E-2</v>
+      </c>
+      <c r="M174">
+        <v>1.6376231981284999E-2</v>
+      </c>
+      <c r="N174">
+        <v>5.9051354666397202E-2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A175" s="200">
+        <v>1</v>
+      </c>
+      <c r="B175" t="s">
+        <v>444</v>
+      </c>
+      <c r="C175">
+        <v>9.1825630511236794E-2</v>
+      </c>
+      <c r="D175">
+        <v>1.1844397864200999</v>
+      </c>
+      <c r="E175">
+        <v>6.9425576681421397</v>
+      </c>
+      <c r="F175">
+        <v>12.541654909134399</v>
+      </c>
+      <c r="G175">
+        <v>21.385892500583498</v>
+      </c>
+      <c r="H175">
+        <v>4.2731780934653898</v>
+      </c>
+      <c r="I175">
+        <v>3.1185570843862598</v>
+      </c>
+      <c r="J175">
+        <v>9.1989464344925304E-2</v>
+      </c>
+      <c r="K175">
+        <v>0.20537696831816901</v>
+      </c>
+      <c r="L175">
+        <v>1.45048075594429E-2</v>
+      </c>
+      <c r="M175">
+        <v>2.1406749536899499E-3</v>
+      </c>
+      <c r="N175">
+        <v>0.163823991430841</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A176" s="200">
+        <v>1</v>
+      </c>
+      <c r="B176" t="s">
+        <v>445</v>
+      </c>
+      <c r="C176">
+        <v>0.16102585800333299</v>
+      </c>
+      <c r="D176">
+        <v>1.7864539457902</v>
+      </c>
+      <c r="E176">
+        <v>7.8954962334563996</v>
+      </c>
+      <c r="F176">
+        <v>11.091781008111999</v>
+      </c>
+      <c r="G176">
+        <v>3.9391233224414601</v>
+      </c>
+      <c r="H176">
+        <v>0.94989243279475899</v>
+      </c>
+      <c r="I176">
+        <v>0.19415085973754201</v>
+      </c>
+      <c r="J176">
+        <v>7.5473043270910103E-2</v>
+      </c>
+      <c r="K176">
+        <v>2.1131636004004502E-3</v>
+      </c>
+      <c r="L176">
+        <v>1.5056889410012399E-2</v>
+      </c>
+      <c r="M176">
+        <v>1.2015259829228299E-2</v>
+      </c>
+      <c r="N176">
+        <v>1.1055158785769699E-3</v>
+      </c>
+    </row>
+    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A177" s="200">
+        <v>1</v>
+      </c>
+      <c r="B177" t="s">
+        <v>446</v>
+      </c>
+      <c r="C177">
+        <v>0.104300393743949</v>
+      </c>
+      <c r="D177">
+        <v>0.61676548027285105</v>
+      </c>
+      <c r="E177">
+        <v>1.6348530657064599</v>
+      </c>
+      <c r="F177">
+        <v>4.6909632776304404</v>
+      </c>
+      <c r="G177">
+        <v>4.3749944819155404</v>
+      </c>
+      <c r="H177">
+        <v>2.6833818511421401</v>
+      </c>
+      <c r="I177">
+        <v>1.1613424343518099</v>
+      </c>
+      <c r="J177">
+        <v>7.3174099143211904E-3</v>
+      </c>
+      <c r="K177">
+        <v>8.3838250198934802E-4</v>
+      </c>
+      <c r="L177">
+        <v>5.3427184334844501E-4</v>
+      </c>
+      <c r="M177">
+        <v>4.0381988669455299E-4</v>
+      </c>
+      <c r="N177">
+        <v>5.5390361193377903E-3</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A178" s="200">
+        <v>1</v>
+      </c>
+      <c r="B178" t="s">
+        <v>447</v>
+      </c>
+      <c r="C178">
+        <v>6.0455181967421397E-2</v>
+      </c>
+      <c r="D178">
+        <v>0.32919978370094199</v>
+      </c>
+      <c r="E178">
+        <v>1.30479206827945</v>
+      </c>
+      <c r="F178">
+        <v>3.9875027867391899</v>
+      </c>
+      <c r="G178">
+        <v>4.1043473086549698</v>
+      </c>
+      <c r="H178">
+        <v>0.17612239005327299</v>
+      </c>
+      <c r="I178">
+        <v>0.92784356521450095</v>
+      </c>
+      <c r="J178">
+        <v>3.6153387854267902E-2</v>
+      </c>
+      <c r="K178">
+        <v>4.9677607246584703E-3</v>
+      </c>
+      <c r="L178">
+        <v>1.03303788413736E-3</v>
+      </c>
+      <c r="M178">
+        <v>1.45617735071095E-2</v>
+      </c>
+      <c r="N178">
+        <v>7.4316100379419898E-3</v>
+      </c>
+    </row>
+    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A179" s="200">
+        <v>1</v>
+      </c>
+      <c r="B179" t="s">
+        <v>448</v>
+      </c>
+      <c r="C179">
+        <v>3.1385042010266498E-2</v>
+      </c>
+      <c r="D179">
+        <v>8.1931434932581898E-2</v>
+      </c>
+      <c r="E179">
+        <v>1.1992340421818499</v>
+      </c>
+      <c r="F179">
+        <v>2.3426641820087801</v>
+      </c>
+      <c r="G179">
+        <v>2.4974418645158298</v>
+      </c>
+      <c r="H179">
+        <v>0.556385766713825</v>
+      </c>
+      <c r="I179">
+        <v>3.2056562810643903E-2</v>
+      </c>
+      <c r="J179">
+        <v>4.1678411724274597E-2</v>
+      </c>
+      <c r="K179">
+        <v>1.34762618284072E-2</v>
+      </c>
+      <c r="L179">
+        <v>1.69970699437573E-3</v>
+      </c>
+      <c r="M179">
+        <v>3.7700058057697698E-3</v>
+      </c>
+      <c r="N179">
+        <v>3.9367504903068803E-3</v>
+      </c>
+    </row>
+    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A180" s="200">
+        <v>1</v>
+      </c>
+      <c r="B180" t="s">
+        <v>449</v>
+      </c>
+      <c r="C180">
+        <v>2.2222033140490899E-2</v>
+      </c>
+      <c r="D180">
+        <v>1.0430423115288101</v>
+      </c>
+      <c r="E180">
+        <v>3.3606953728223301</v>
+      </c>
+      <c r="F180">
+        <v>4.2260766632340703</v>
+      </c>
+      <c r="G180">
+        <v>0.87339511148760196</v>
+      </c>
+      <c r="H180">
+        <v>0.33048122829111798</v>
+      </c>
+      <c r="I180">
+        <v>2.7697737026311401E-2</v>
+      </c>
+      <c r="J180">
+        <v>1.02153558835644E-3</v>
+      </c>
+      <c r="K180">
+        <v>3.0150621387382702E-3</v>
+      </c>
+      <c r="L180">
+        <v>8.6644128243487499E-4</v>
+      </c>
+      <c r="M180">
+        <v>2.8712297501315102E-3</v>
+      </c>
+      <c r="N180">
+        <v>3.3039246436962601E-3</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A181" s="200">
+        <v>1</v>
+      </c>
+      <c r="B181" t="s">
+        <v>450</v>
+      </c>
+      <c r="C181">
+        <v>2.26851662574157E-2</v>
+      </c>
+      <c r="D181">
+        <v>4.7790021165720897E-2</v>
+      </c>
+      <c r="E181">
+        <v>3.0166522650367602</v>
+      </c>
+      <c r="F181">
+        <v>2.3957067673815402</v>
+      </c>
+      <c r="G181">
+        <v>2.8473437478653199</v>
+      </c>
+      <c r="H181">
+        <v>0.10308672834719</v>
+      </c>
+      <c r="I181">
+        <v>2.16349461263497E-2</v>
+      </c>
+      <c r="J181">
+        <v>7.5300757900279805E-2</v>
+      </c>
+      <c r="K181">
+        <v>5.0653891248195902E-5</v>
+      </c>
+      <c r="L181">
+        <v>1.4633398912394499E-5</v>
+      </c>
+      <c r="M181">
+        <v>9.6496783878523903E-4</v>
+      </c>
+      <c r="N181">
+        <v>1.2935728076598599E-2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A182" s="200">
+        <v>1</v>
+      </c>
+      <c r="B182" t="s">
+        <v>451</v>
+      </c>
+      <c r="C182">
+        <v>8.1822453988877594E-2</v>
+      </c>
+      <c r="D182">
+        <v>0.88925400682575095</v>
+      </c>
+      <c r="E182">
+        <v>5.5910707202118202</v>
+      </c>
+      <c r="F182">
+        <v>11.5046646845775</v>
+      </c>
+      <c r="G182">
+        <v>3.52385538553433</v>
+      </c>
+      <c r="H182">
+        <v>0.91734111361610804</v>
+      </c>
+      <c r="I182">
+        <v>6.5774892517266606E-2</v>
+      </c>
+      <c r="J182">
+        <v>3.3539219188691599E-2</v>
+      </c>
+      <c r="K182">
+        <v>1.2932137745437901E-3</v>
+      </c>
+      <c r="L182">
+        <v>5.1169538027310297E-3</v>
+      </c>
+      <c r="M182">
+        <v>5.3067555285037302E-3</v>
+      </c>
+      <c r="N182">
+        <v>2.1522704731762299E-3</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A183" s="200">
+        <v>1</v>
+      </c>
+      <c r="B183" t="s">
+        <v>452</v>
+      </c>
+      <c r="C183">
+        <v>2.4937657221920399E-3</v>
+      </c>
+      <c r="D183">
+        <v>3.4377350276259398E-2</v>
+      </c>
+      <c r="E183">
+        <v>0.20464379486585199</v>
+      </c>
+      <c r="F183">
+        <v>0.23251498345614099</v>
+      </c>
+      <c r="G183">
+        <v>4.50447714703123E-2</v>
+      </c>
+      <c r="H183">
+        <v>3.0397216662828502E-2</v>
+      </c>
+      <c r="I183">
+        <v>1.26102090493175E-3</v>
+      </c>
+      <c r="J183">
+        <v>8.1778371227220095E-5</v>
+      </c>
+      <c r="K183">
+        <v>7.3125594101540304E-6</v>
+      </c>
+      <c r="L183">
+        <v>1.1587295632837E-5</v>
+      </c>
+      <c r="M183">
+        <v>9.53570310439087E-7</v>
+      </c>
+      <c r="N183">
+        <v>2.6242074989798499E-4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A184" s="200">
+        <v>1</v>
+      </c>
+      <c r="B184" t="s">
+        <v>453</v>
+      </c>
+      <c r="C184">
+        <v>9.3105792519062695E-3</v>
+      </c>
+      <c r="D184">
+        <v>0.106615042774308</v>
+      </c>
+      <c r="E184">
+        <v>2.0487520720813102</v>
+      </c>
+      <c r="F184">
+        <v>22.937803633383702</v>
+      </c>
+      <c r="G184">
+        <v>19.2150180314806</v>
+      </c>
+      <c r="H184">
+        <v>5.5803627997901399</v>
+      </c>
+      <c r="I184">
+        <v>0.875507819184284</v>
+      </c>
+      <c r="J184">
+        <v>6.7658777278800694E-2</v>
+      </c>
+      <c r="K184">
+        <v>0.114717788055561</v>
+      </c>
+      <c r="L184">
+        <v>2.08625090540424E-2</v>
+      </c>
+      <c r="M184">
+        <v>4.9685464762626802E-3</v>
+      </c>
+      <c r="N184">
+        <v>8.5339585362232701E-3</v>
+      </c>
+    </row>
+    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A185" s="200">
+        <v>1</v>
+      </c>
+      <c r="B185" t="s">
+        <v>454</v>
+      </c>
+      <c r="C185">
+        <v>1.21650497851463</v>
+      </c>
+      <c r="D185">
+        <v>13.3049362819664</v>
+      </c>
+      <c r="E185">
+        <v>41.196511236543898</v>
+      </c>
+      <c r="F185">
+        <v>74.811586551947997</v>
+      </c>
+      <c r="G185">
+        <v>23.3966224832328</v>
+      </c>
+      <c r="H185">
+        <v>7.0878010644943004</v>
+      </c>
+      <c r="I185">
+        <v>1.6774313052651</v>
+      </c>
+      <c r="J185">
+        <v>0.29380723776642997</v>
+      </c>
+      <c r="K185">
+        <v>8.3195376444304595E-2</v>
+      </c>
+      <c r="L185">
+        <v>1.2803344086554001E-4</v>
+      </c>
+      <c r="M185">
+        <v>9.8925890579258501E-3</v>
+      </c>
+      <c r="N185">
+        <v>0.370431495857937</v>
+      </c>
+    </row>
+    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A186" s="200">
+        <v>1</v>
+      </c>
+      <c r="B186" t="s">
+        <v>455</v>
+      </c>
+      <c r="C186">
+        <v>1.06236200815728</v>
+      </c>
+      <c r="D186">
+        <v>6.0448084150599204</v>
+      </c>
+      <c r="E186">
+        <v>42.180236839958503</v>
+      </c>
+      <c r="F186">
+        <v>65.526253385467299</v>
+      </c>
+      <c r="G186">
+        <v>13.9549396330902</v>
+      </c>
+      <c r="H186">
+        <v>5.29950389297497</v>
+      </c>
+      <c r="I186">
+        <v>0.55712622749402096</v>
+      </c>
+      <c r="J186">
+        <v>4.6557922937806098E-2</v>
+      </c>
+      <c r="K186">
+        <v>5.9325512887574497E-3</v>
+      </c>
+      <c r="L186">
+        <v>1.8271941005372098E-2</v>
+      </c>
+      <c r="M186">
+        <v>7.2201548743915898E-3</v>
+      </c>
+      <c r="N186">
+        <v>4.5488962120073103E-3</v>
+      </c>
+    </row>
+    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A187" s="200">
+        <v>1</v>
+      </c>
+      <c r="B187" t="s">
+        <v>456</v>
+      </c>
+      <c r="C187">
+        <v>5.8727879904238001E-2</v>
+      </c>
+      <c r="D187">
+        <v>0.13961772218604901</v>
+      </c>
+      <c r="E187">
+        <v>6.4251731371684997</v>
+      </c>
+      <c r="F187">
+        <v>4.67154721122587</v>
+      </c>
+      <c r="G187">
+        <v>1.86169442200312</v>
+      </c>
+      <c r="H187">
+        <v>0.77361517874010999</v>
+      </c>
+      <c r="I187">
+        <v>2.6390151984383201E-2</v>
+      </c>
+      <c r="J187">
+        <v>9.3551125278338698E-4</v>
+      </c>
+      <c r="K187">
+        <v>3.5057473006733702E-4</v>
+      </c>
+      <c r="L187">
+        <v>9.2854460962112803E-5</v>
+      </c>
+      <c r="M187">
+        <v>8.1491334843485604E-5</v>
+      </c>
+      <c r="N187">
+        <v>4.8676227885885502E-4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A188" s="200">
+        <v>1</v>
+      </c>
+      <c r="B188" t="s">
+        <v>457</v>
+      </c>
+      <c r="C188">
+        <v>0.15882506406174199</v>
+      </c>
+      <c r="D188">
+        <v>0.98823384275555803</v>
+      </c>
+      <c r="E188">
+        <v>8.4412433102734905</v>
+      </c>
+      <c r="F188">
+        <v>43.693693700132599</v>
+      </c>
+      <c r="G188">
+        <v>25.214989232235499</v>
+      </c>
+      <c r="H188">
+        <v>9.1103273006241903</v>
+      </c>
+      <c r="I188">
+        <v>0.663675137615795</v>
+      </c>
+      <c r="J188">
+        <v>3.7965189378070998E-3</v>
+      </c>
+      <c r="K188">
+        <v>2.4913290896486301E-3</v>
+      </c>
+      <c r="L188">
+        <v>2.5148229365536301E-3</v>
+      </c>
+      <c r="M188">
+        <v>1.1985952040131701E-3</v>
+      </c>
+      <c r="N188">
+        <v>0.130483576730233</v>
+      </c>
+    </row>
+    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A189" s="200">
+        <v>1</v>
+      </c>
+      <c r="B189" t="s">
+        <v>458</v>
+      </c>
+      <c r="C189">
+        <v>0.55514888443364596</v>
+      </c>
+      <c r="D189">
+        <v>0.69138075680514099</v>
+      </c>
+      <c r="E189">
+        <v>11.5850833439609</v>
+      </c>
+      <c r="F189">
+        <v>34.552218372524301</v>
+      </c>
+      <c r="G189">
+        <v>26.3866543239725</v>
+      </c>
+      <c r="H189">
+        <v>4.10715763967338</v>
+      </c>
+      <c r="I189">
+        <v>3.3403208241192401</v>
+      </c>
+      <c r="J189">
+        <v>4.92607757546712E-2</v>
+      </c>
+      <c r="K189">
+        <v>8.6632018833913294E-3</v>
+      </c>
+      <c r="L189">
+        <v>1.9948072761553802E-3</v>
+      </c>
+      <c r="M189">
+        <v>1.40301005057237E-3</v>
+      </c>
+      <c r="N189">
+        <v>0.61798589787401703</v>
+      </c>
+    </row>
+    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A190" s="200">
+        <v>1</v>
+      </c>
+      <c r="B190" t="s">
+        <v>459</v>
+      </c>
+      <c r="C190">
+        <v>9.3964237399195794E-2</v>
+      </c>
+      <c r="D190">
+        <v>1.25888990627734</v>
+      </c>
+      <c r="E190">
+        <v>2.1414513202464298</v>
+      </c>
+      <c r="F190">
+        <v>5.5333708148072001</v>
+      </c>
+      <c r="G190">
+        <v>6.6141526106402004</v>
+      </c>
+      <c r="H190">
+        <v>0.35042768278110697</v>
+      </c>
+      <c r="I190">
+        <v>0.42115056139149598</v>
+      </c>
+      <c r="J190">
+        <v>8.5832480417043708E-3</v>
+      </c>
+      <c r="K190">
+        <v>3.8367081997663301E-3</v>
+      </c>
+      <c r="L190">
+        <v>4.0623123443264301E-4</v>
+      </c>
+      <c r="M190">
+        <v>3.1408032758731899E-3</v>
+      </c>
+      <c r="N190">
+        <v>4.1692787259878499E-3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A191" s="200">
+        <v>1</v>
+      </c>
+      <c r="B191" t="s">
+        <v>460</v>
+      </c>
+      <c r="C191">
+        <v>0.12754585099003901</v>
+      </c>
+      <c r="D191">
+        <v>0.67073718260553505</v>
+      </c>
+      <c r="E191">
+        <v>4.9143014401017897</v>
+      </c>
+      <c r="F191">
+        <v>8.3591957758512603</v>
+      </c>
+      <c r="G191">
+        <v>5.3285134571600503</v>
+      </c>
+      <c r="H191">
+        <v>0.161811764806914</v>
+      </c>
+      <c r="I191">
+        <v>1.34151823051113E-2</v>
+      </c>
+      <c r="J191">
+        <v>9.6723208135917303E-4</v>
+      </c>
+      <c r="K191">
+        <v>6.7739183584893201E-5</v>
+      </c>
+      <c r="L191">
+        <v>8.0249879871617795E-4</v>
+      </c>
+      <c r="M191">
+        <v>1.57006727988612E-4</v>
+      </c>
+      <c r="N191">
+        <v>6.52193821191334E-5</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A192" s="200">
+        <v>1</v>
+      </c>
+      <c r="B192" t="s">
+        <v>461</v>
+      </c>
+      <c r="C192">
+        <v>0.11354186433852199</v>
+      </c>
+      <c r="D192">
+        <v>0.333052011129292</v>
+      </c>
+      <c r="E192">
+        <v>2.3258606732494602</v>
+      </c>
+      <c r="F192">
+        <v>2.1699980191441099</v>
+      </c>
+      <c r="G192">
+        <v>0.33347668102779798</v>
+      </c>
+      <c r="H192">
+        <v>0.32789581685805602</v>
+      </c>
+      <c r="I192">
+        <v>5.3326830556020201E-2</v>
+      </c>
+      <c r="J192">
+        <v>4.2086283060273198E-4</v>
+      </c>
+      <c r="K192">
+        <v>2.40251941139494E-4</v>
+      </c>
+      <c r="L192">
+        <v>6.6284405718196402E-5</v>
+      </c>
+      <c r="M192">
+        <v>3.1144191842378801E-5</v>
+      </c>
+      <c r="N192">
+        <v>3.7025222787895498E-5</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A193" s="200">
+        <v>1</v>
+      </c>
+      <c r="B193" t="s">
+        <v>462</v>
+      </c>
+      <c r="C193">
+        <v>2.2383136875063002E-3</v>
+      </c>
+      <c r="D193">
+        <v>3.0802836129313001E-2</v>
+      </c>
+      <c r="E193">
+        <v>0.107130022629115</v>
+      </c>
+      <c r="F193">
+        <v>0.45852637734880303</v>
+      </c>
+      <c r="G193">
+        <v>0.12586909259736001</v>
+      </c>
+      <c r="H193">
+        <v>1.26655391368988E-2</v>
+      </c>
+      <c r="I193">
+        <v>1.3714383656657199E-2</v>
+      </c>
+      <c r="J193">
+        <v>2.9668583349177103E-4</v>
+      </c>
+      <c r="K193">
+        <v>6.4200245524816897E-5</v>
+      </c>
+      <c r="L193">
+        <v>4.3915028091422799E-5</v>
+      </c>
+      <c r="M193">
+        <v>1.66081969071766E-5</v>
+      </c>
+      <c r="N193">
+        <v>1.30865048030488E-3</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A194" s="200">
+        <v>1</v>
+      </c>
+      <c r="B194" t="s">
+        <v>463</v>
+      </c>
+      <c r="C194">
+        <v>0.12923391091063599</v>
+      </c>
+      <c r="D194">
+        <v>0.85677069217823798</v>
+      </c>
+      <c r="E194">
+        <v>7.4322556137334601</v>
+      </c>
+      <c r="F194">
+        <v>25.282547946353102</v>
+      </c>
+      <c r="G194">
+        <v>13.753991596396499</v>
+      </c>
+      <c r="H194">
+        <v>14.3696108993406</v>
+      </c>
+      <c r="I194">
+        <v>2.24404072463483</v>
+      </c>
+      <c r="J194">
+        <v>5.8862385114402099E-3</v>
+      </c>
+      <c r="K194">
+        <v>8.0783341918280096E-3</v>
+      </c>
+      <c r="L194">
+        <v>5.0295416951352497E-4</v>
+      </c>
+      <c r="M194">
+        <v>4.4066443049948101E-4</v>
+      </c>
+      <c r="N194">
+        <v>0.22191100678911099</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A195" s="200">
+        <v>1</v>
+      </c>
+      <c r="B195" t="s">
+        <v>464</v>
+      </c>
+      <c r="C195">
+        <v>0.67816729973474099</v>
+      </c>
+      <c r="D195">
+        <v>4.3740290536084503</v>
+      </c>
+      <c r="E195">
+        <v>14.693360486716401</v>
+      </c>
+      <c r="F195">
+        <v>40.713039115591201</v>
+      </c>
+      <c r="G195">
+        <v>28.359163792136201</v>
+      </c>
+      <c r="H195">
+        <v>4.4117532297879203</v>
+      </c>
+      <c r="I195">
+        <v>0.93326073529717801</v>
+      </c>
+      <c r="J195">
+        <v>1.3375220470203499E-3</v>
+      </c>
+      <c r="K195">
+        <v>2.05979748711103E-4</v>
+      </c>
+      <c r="L195">
+        <v>4.9126079225600902E-3</v>
+      </c>
+      <c r="M195">
+        <v>2.9852257270006699E-3</v>
+      </c>
+      <c r="N195">
+        <v>1.85261277013749E-3</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A196" s="200">
+        <v>1</v>
+      </c>
+      <c r="B196" t="s">
+        <v>465</v>
+      </c>
+      <c r="C196">
+        <v>0.24860115757239401</v>
+      </c>
+      <c r="D196">
+        <v>0.86482082517285797</v>
+      </c>
+      <c r="E196">
+        <v>10.528502776593401</v>
+      </c>
+      <c r="F196">
+        <v>42.176720373019997</v>
+      </c>
+      <c r="G196">
+        <v>7.8158839568936997</v>
+      </c>
+      <c r="H196">
+        <v>0.197430427546848</v>
+      </c>
+      <c r="I196">
+        <v>0.25163765557895401</v>
+      </c>
+      <c r="J196">
+        <v>9.1236110082406494E-2</v>
+      </c>
+      <c r="K196">
+        <v>3.2977173816069101E-3</v>
+      </c>
+      <c r="L196">
+        <v>1.39903189346462E-3</v>
+      </c>
+      <c r="M196">
+        <v>7.4353389032572895E-2</v>
+      </c>
+      <c r="N196">
+        <v>5.2015226704830802E-4</v>
+      </c>
+    </row>
+    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A197" s="200">
+        <v>1</v>
+      </c>
+      <c r="B197" t="s">
+        <v>466</v>
+      </c>
+      <c r="C197">
+        <v>7.1702713185456998E-2</v>
+      </c>
+      <c r="D197">
+        <v>3.6141908945264901E-2</v>
+      </c>
+      <c r="E197">
+        <v>0.48000488032940097</v>
+      </c>
+      <c r="F197">
+        <v>2.6011108563751102</v>
+      </c>
+      <c r="G197">
+        <v>2.0208648666231799</v>
+      </c>
+      <c r="H197">
+        <v>8.4984805063780706E-3</v>
+      </c>
+      <c r="I197">
+        <v>4.0117088996428803E-3</v>
+      </c>
+      <c r="J197">
+        <v>1.1845041653612699E-2</v>
+      </c>
+      <c r="K197">
+        <v>5.9615126876426097E-5</v>
+      </c>
+      <c r="L197">
+        <v>9.3214381561590801E-5</v>
+      </c>
+      <c r="M197">
+        <v>4.2245308205571898E-4</v>
+      </c>
+      <c r="N197">
+        <v>8.0541726331008305E-3</v>
+      </c>
+    </row>
+    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A198" s="200">
+        <v>1</v>
+      </c>
+      <c r="B198" t="s">
+        <v>467</v>
+      </c>
+      <c r="C198">
+        <v>0.125622423218822</v>
+      </c>
+      <c r="D198">
+        <v>0.102540205998341</v>
+      </c>
+      <c r="E198">
+        <v>0.53474508383405195</v>
+      </c>
+      <c r="F198">
+        <v>0.71739474936682701</v>
+      </c>
+      <c r="G198">
+        <v>0.30585101157271799</v>
+      </c>
+      <c r="H198">
+        <v>3.1029721124243698E-2</v>
+      </c>
+      <c r="I198">
+        <v>1.37572081039969E-3</v>
+      </c>
+      <c r="J198">
+        <v>9.0094221192887501E-4</v>
+      </c>
+      <c r="K198">
+        <v>4.2157875779310898E-5</v>
+      </c>
+      <c r="L198">
+        <v>1.7269952471200201E-5</v>
+      </c>
+      <c r="M198">
+        <v>1.8931704805793001E-5</v>
+      </c>
+      <c r="N198">
+        <v>2.7477635575232401E-3</v>
+      </c>
+    </row>
+    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A199" s="200">
+        <v>1</v>
+      </c>
+      <c r="B199" t="s">
+        <v>468</v>
+      </c>
+      <c r="C199">
+        <v>2.6554801522584898E-2</v>
+      </c>
+      <c r="D199">
+        <v>0.16899971585271001</v>
+      </c>
+      <c r="E199">
+        <v>2.97925597055518</v>
+      </c>
+      <c r="F199">
+        <v>4.93494256777538</v>
+      </c>
+      <c r="G199">
+        <v>9.1090497407888797</v>
+      </c>
+      <c r="H199">
+        <v>1.4472127786719999</v>
+      </c>
+      <c r="I199">
+        <v>4.56438422187362E-2</v>
+      </c>
+      <c r="J199">
+        <v>1.0417067651200601E-3</v>
+      </c>
+      <c r="K199">
+        <v>1.3595917017870901E-3</v>
+      </c>
+      <c r="L199">
+        <v>4.20919610323554E-3</v>
+      </c>
+      <c r="M199">
+        <v>1.8072950954359401E-2</v>
+      </c>
+      <c r="N199">
+        <v>5.85816041466138E-2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A200" s="200">
+        <v>1</v>
+      </c>
+      <c r="B200" t="s">
+        <v>469</v>
+      </c>
+      <c r="C200">
+        <v>0.345269993461988</v>
+      </c>
+      <c r="D200">
+        <v>2.8574899295837199</v>
+      </c>
+      <c r="E200">
+        <v>9.1608709910490997</v>
+      </c>
+      <c r="F200">
+        <v>21.511031534223999</v>
+      </c>
+      <c r="G200">
+        <v>3.2344058133768998</v>
+      </c>
+      <c r="H200">
+        <v>1.7714825678999599</v>
+      </c>
+      <c r="I200">
+        <v>2.9140491906357302</v>
+      </c>
+      <c r="J200">
+        <v>0.58446719993326302</v>
+      </c>
+      <c r="K200">
+        <v>3.48367794944816E-2</v>
+      </c>
+      <c r="L200">
+        <v>9.3327661634521001E-3</v>
+      </c>
+      <c r="M200">
+        <v>2.7388325784552599E-3</v>
+      </c>
+      <c r="N200">
+        <v>2.11970687782982E-2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A201" s="200">
+        <v>1</v>
+      </c>
+      <c r="B201" t="s">
+        <v>470</v>
+      </c>
+      <c r="C201">
+        <v>3.7731071726016002E-2</v>
+      </c>
+      <c r="D201">
+        <v>0.25259776619681001</v>
+      </c>
+      <c r="E201">
+        <v>0.92625755651992003</v>
+      </c>
+      <c r="F201">
+        <v>9.9564911685604596</v>
+      </c>
+      <c r="G201">
+        <v>2.9889689194248601</v>
+      </c>
+      <c r="H201">
+        <v>1.28823356331155</v>
+      </c>
+      <c r="I201">
+        <v>6.1926739226632797E-2</v>
+      </c>
+      <c r="J201">
+        <v>2.0454617011705302E-3</v>
+      </c>
+      <c r="K201">
+        <v>3.1976938123037699E-4</v>
+      </c>
+      <c r="L201">
+        <v>1.8233933465240901E-4</v>
+      </c>
+      <c r="M201">
+        <v>2.24792832372718E-4</v>
+      </c>
+      <c r="N201">
+        <v>1.0896084609366299E-3</v>
+      </c>
+    </row>
+    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A202" s="200">
+        <v>1</v>
+      </c>
+      <c r="B202" t="s">
+        <v>471</v>
+      </c>
+      <c r="C202">
+        <v>0.40678676332339397</v>
+      </c>
+      <c r="D202">
+        <v>0.32188523197918301</v>
+      </c>
+      <c r="E202">
+        <v>2.6344859118164501</v>
+      </c>
+      <c r="F202">
+        <v>5.8914617709263002</v>
+      </c>
+      <c r="G202">
+        <v>4.2910892979390303</v>
+      </c>
+      <c r="H202">
+        <v>1.0405601107265099</v>
+      </c>
+      <c r="I202">
+        <v>0.58428309323468197</v>
+      </c>
+      <c r="J202">
+        <v>6.3363506884527596E-4</v>
+      </c>
+      <c r="K202">
+        <v>1.58040360172281E-4</v>
+      </c>
+      <c r="L202">
+        <v>8.8666146947339599E-5</v>
+      </c>
+      <c r="M202">
+        <v>1.1799328198021999E-2</v>
+      </c>
+      <c r="N202">
+        <v>1.33365106269884E-3</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A203" s="200">
+        <v>1</v>
+      </c>
+      <c r="B203" t="s">
+        <v>472</v>
+      </c>
+      <c r="C203">
+        <v>9.4896363014472199E-2</v>
+      </c>
+      <c r="D203">
+        <v>1.45183787180975</v>
+      </c>
+      <c r="E203">
+        <v>14.136567237378401</v>
+      </c>
+      <c r="F203">
+        <v>11.664870145870299</v>
+      </c>
+      <c r="G203">
+        <v>5.2388055254349801</v>
+      </c>
+      <c r="H203">
+        <v>2.0939845914589199</v>
+      </c>
+      <c r="I203">
+        <v>1.0600682698493701E-2</v>
+      </c>
+      <c r="J203">
+        <v>6.5359333910384301E-2</v>
+      </c>
+      <c r="K203">
+        <v>1.3070343196111401E-4</v>
+      </c>
+      <c r="L203">
+        <v>3.44230262485556E-3</v>
+      </c>
+      <c r="M203">
+        <v>1.9363431611407499E-3</v>
+      </c>
+      <c r="N203">
+        <v>6.83332877136045E-3</v>
+      </c>
+    </row>
+    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A204" s="200">
+        <v>1</v>
+      </c>
+      <c r="B204" t="s">
+        <v>473</v>
+      </c>
+      <c r="C204">
+        <v>0.85036005261814396</v>
+      </c>
+      <c r="D204">
+        <v>6.7411009792535799</v>
+      </c>
+      <c r="E204">
+        <v>7.7587956932743802</v>
+      </c>
+      <c r="F204">
+        <v>5.6727325615705801</v>
+      </c>
+      <c r="G204">
+        <v>4.8985064373168798</v>
+      </c>
+      <c r="H204">
+        <v>3.2817949382186198</v>
+      </c>
+      <c r="I204">
+        <v>0.39611368193226898</v>
+      </c>
+      <c r="J204">
+        <v>3.5714467047842798E-3</v>
+      </c>
+      <c r="K204">
+        <v>1.10829561852435E-3</v>
+      </c>
+      <c r="L204">
+        <v>8.6398310761108194E-5</v>
+      </c>
+      <c r="M204">
+        <v>4.1514142062645003E-5</v>
+      </c>
+      <c r="N204">
+        <v>3.0976657301568297E-4</v>
+      </c>
+    </row>
+    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A205" s="200">
+        <v>1</v>
+      </c>
+      <c r="B205" t="s">
+        <v>474</v>
+      </c>
+      <c r="C205">
+        <v>1.52643262910494E-2</v>
+      </c>
+      <c r="D205">
+        <v>7.36436591479879E-2</v>
+      </c>
+      <c r="E205">
+        <v>0.61670280289475599</v>
+      </c>
+      <c r="F205">
+        <v>1.12701657642029</v>
+      </c>
+      <c r="G205">
+        <v>0.77950059354355306</v>
+      </c>
+      <c r="H205">
+        <v>0.26956180670496599</v>
+      </c>
+      <c r="I205">
+        <v>1.8349398774853198E-2</v>
+      </c>
+      <c r="J205">
+        <v>2.6055049443530999E-4</v>
+      </c>
+      <c r="K205">
+        <v>1.29639888868797E-5</v>
+      </c>
+      <c r="L205">
+        <v>4.4876553266598702E-6</v>
+      </c>
+      <c r="M205">
+        <v>2.6050661564318199E-5</v>
+      </c>
+      <c r="N205">
+        <v>8.6560340957235796E-4</v>
+      </c>
+    </row>
+    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A206" s="200">
+        <v>1</v>
+      </c>
+      <c r="B206" t="s">
+        <v>475</v>
+      </c>
+      <c r="C206">
+        <v>4.5174977478460701E-4</v>
+      </c>
+      <c r="D206">
+        <v>2.9104447957084799E-2</v>
+      </c>
+      <c r="E206">
+        <v>0.50718694824348698</v>
+      </c>
+      <c r="F206">
+        <v>4.7022157123181803</v>
+      </c>
+      <c r="G206">
+        <v>5.3643462264830202</v>
+      </c>
+      <c r="H206">
+        <v>2.2515867434705998</v>
+      </c>
+      <c r="I206">
+        <v>0.103851229042121</v>
+      </c>
+      <c r="J206">
+        <v>0.116996727067117</v>
+      </c>
+      <c r="K206">
+        <v>5.6369542811413001E-2</v>
+      </c>
+      <c r="L206">
+        <v>3.2985639288548999E-4</v>
+      </c>
+      <c r="M206">
+        <v>1.9184392573288701E-3</v>
+      </c>
+      <c r="N206">
+        <v>9.18436091053337E-3</v>
+      </c>
+    </row>
+    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A207" s="200">
+        <v>1</v>
+      </c>
+      <c r="B207" t="s">
+        <v>476</v>
+      </c>
+      <c r="C207">
+        <v>5.6641082789723896E-3</v>
+      </c>
+      <c r="D207">
+        <v>0.37846667037327802</v>
+      </c>
+      <c r="E207">
+        <v>1.0943215034310101</v>
+      </c>
+      <c r="F207">
+        <v>3.6410498278574002</v>
+      </c>
+      <c r="G207">
+        <v>1.8119711324407699</v>
+      </c>
+      <c r="H207">
+        <v>0.56381296942917802</v>
+      </c>
+      <c r="I207">
+        <v>1.9633320834821302E-2</v>
+      </c>
+      <c r="J207">
+        <v>3.8633167584208597E-4</v>
+      </c>
+      <c r="K207">
+        <v>5.1222534029433699E-2</v>
+      </c>
+      <c r="L207">
+        <v>5.2359228364109098E-2</v>
+      </c>
+      <c r="M207">
+        <v>4.69328398921071E-2</v>
+      </c>
+      <c r="N207">
+        <v>0.16562159817453601</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A208" s="200">
+        <v>1</v>
+      </c>
+      <c r="B208" t="s">
+        <v>477</v>
+      </c>
+      <c r="C208">
+        <v>0.62584920808966404</v>
+      </c>
+      <c r="D208">
+        <v>1.21409102096108</v>
+      </c>
+      <c r="E208">
+        <v>9.1875205810532599</v>
+      </c>
+      <c r="F208">
+        <v>24.660298715549899</v>
+      </c>
+      <c r="G208">
+        <v>11.039510780028399</v>
+      </c>
+      <c r="H208">
+        <v>1.2417380509862199</v>
+      </c>
+      <c r="I208">
+        <v>0.185988219772527</v>
+      </c>
+      <c r="J208">
+        <v>0.450580740239787</v>
+      </c>
+      <c r="K208">
+        <v>6.17839098469421E-4</v>
+      </c>
+      <c r="L208">
+        <v>2.0663689646257399E-4</v>
+      </c>
+      <c r="M208">
+        <v>7.4235143174888299E-4</v>
+      </c>
+      <c r="N208">
+        <v>9.3430038341381898E-3</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A209" s="200">
+        <v>1</v>
+      </c>
+      <c r="B209" t="s">
+        <v>478</v>
+      </c>
+      <c r="C209">
+        <v>0.263519687193982</v>
+      </c>
+      <c r="D209">
+        <v>0.97757978577942395</v>
+      </c>
+      <c r="E209">
+        <v>5.3645894608695404</v>
+      </c>
+      <c r="F209">
+        <v>22.760574855653299</v>
+      </c>
+      <c r="G209">
+        <v>33.382752527938202</v>
+      </c>
+      <c r="H209">
+        <v>8.3959902652823892</v>
+      </c>
+      <c r="I209">
+        <v>2.7589752577024802</v>
+      </c>
+      <c r="J209">
+        <v>0.34785663902609798</v>
+      </c>
+      <c r="K209">
+        <v>4.8283869719098097E-4</v>
+      </c>
+      <c r="L209">
+        <v>1.8397197717420399E-3</v>
+      </c>
+      <c r="M209">
+        <v>3.6884276764448599E-4</v>
+      </c>
+      <c r="N209">
+        <v>5.5092553555118997E-3</v>
+      </c>
+    </row>
+    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A210" s="200">
+        <v>1</v>
+      </c>
+      <c r="B210" t="s">
+        <v>479</v>
+      </c>
+      <c r="C210">
+        <v>8.8847232192585002E-2</v>
+      </c>
+      <c r="D210">
+        <v>9.2583818048500494E-2</v>
+      </c>
+      <c r="E210">
+        <v>0.12801663607953201</v>
+      </c>
+      <c r="F210">
+        <v>0.72519618775546402</v>
+      </c>
+      <c r="G210">
+        <v>0.52509230083886504</v>
+      </c>
+      <c r="H210">
+        <v>0.14878238019783499</v>
+      </c>
+      <c r="I210">
+        <v>5.97291313572231E-3</v>
+      </c>
+      <c r="J210">
+        <v>2.80927211052341E-5</v>
+      </c>
+      <c r="K210">
+        <v>1.3014297044808601E-6</v>
+      </c>
+      <c r="L210">
+        <v>9.2353141047187906E-3</v>
+      </c>
+      <c r="M210">
+        <v>7.0340039179512005E-5</v>
+      </c>
+      <c r="N210">
+        <v>1.3738490220662499E-2</v>
+      </c>
+    </row>
+    <row r="211" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A211" s="200">
+        <v>1</v>
+      </c>
+      <c r="B211" t="s">
+        <v>480</v>
+      </c>
+      <c r="C211">
+        <v>0.27119862038522302</v>
+      </c>
+      <c r="D211">
+        <v>2.2022716590476299</v>
+      </c>
+      <c r="E211">
+        <v>4.7321816397865399</v>
+      </c>
+      <c r="F211">
+        <v>12.5096778285646</v>
+      </c>
+      <c r="G211">
+        <v>8.4629504430443703</v>
+      </c>
+      <c r="H211">
+        <v>2.63317125379786</v>
+      </c>
+      <c r="I211">
+        <v>1.8393133697998201</v>
+      </c>
+      <c r="J211">
+        <v>5.0626255082497497E-2</v>
+      </c>
+      <c r="K211">
+        <v>2.0678825390702698E-3</v>
+      </c>
+      <c r="L211">
+        <v>7.8578483032680294E-2</v>
+      </c>
+      <c r="M211">
+        <v>3.2627516227543801E-3</v>
+      </c>
+      <c r="N211">
+        <v>2.10755945825912E-4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A212" s="200">
+        <v>1</v>
+      </c>
+      <c r="B212" t="s">
+        <v>481</v>
+      </c>
+      <c r="C212">
+        <v>1.9504509033685499E-2</v>
+      </c>
+      <c r="D212">
+        <v>8.39024911558683E-2</v>
+      </c>
+      <c r="E212">
+        <v>0.11693366585215099</v>
+      </c>
+      <c r="F212">
+        <v>0.21986270047329601</v>
+      </c>
+      <c r="G212">
+        <v>3.7308049214112099E-2</v>
+      </c>
+      <c r="H212">
+        <v>2.3083980900723999E-2</v>
+      </c>
+      <c r="I212">
+        <v>1.0793390991111801E-3</v>
+      </c>
+      <c r="J212">
+        <v>5.8317906164777897E-7</v>
+      </c>
+      <c r="K212">
+        <v>1.1704724185986699E-6</v>
+      </c>
+      <c r="L212">
+        <v>3.67584615929416E-6</v>
+      </c>
+      <c r="M212">
+        <v>6.6407116911545902E-6</v>
+      </c>
+      <c r="N212">
+        <v>1.01617328772194E-5</v>
+      </c>
+    </row>
+    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A213" s="200">
+        <v>1</v>
+      </c>
+      <c r="B213" t="s">
+        <v>482</v>
+      </c>
+      <c r="C213">
+        <v>1.0588264620379E-3</v>
+      </c>
+      <c r="D213">
+        <v>4.5664686802148096E-3</v>
+      </c>
+      <c r="E213">
+        <v>3.5226454412915498E-2</v>
+      </c>
+      <c r="F213">
+        <v>0.229935509960801</v>
+      </c>
+      <c r="G213">
+        <v>0.589381785958497</v>
+      </c>
+      <c r="H213">
+        <v>0.27636794990612701</v>
+      </c>
+      <c r="I213">
+        <v>0.16261160289353299</v>
+      </c>
+      <c r="J213">
+        <v>1.31587444300515E-3</v>
+      </c>
+      <c r="K213">
+        <v>1.5828315581128599E-4</v>
+      </c>
+      <c r="L213">
+        <v>6.9584207548916601E-5</v>
+      </c>
+      <c r="M213">
+        <v>5.5784239682074499E-3</v>
+      </c>
+      <c r="N213">
+        <v>3.6233110000254399E-3</v>
+      </c>
+    </row>
+    <row r="214" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A214" s="200">
+        <v>1</v>
+      </c>
+      <c r="B214" t="s">
+        <v>483</v>
+      </c>
+      <c r="C214">
+        <v>9.6586834543878099E-3</v>
+      </c>
+      <c r="D214">
+        <v>3.96797963012335E-2</v>
+      </c>
+      <c r="E214">
+        <v>0.13961348077541599</v>
+      </c>
+      <c r="F214">
+        <v>0.48252106094484098</v>
+      </c>
+      <c r="G214">
+        <v>0.44160103878223</v>
+      </c>
+      <c r="H214">
+        <v>2.83938152960919E-2</v>
+      </c>
+      <c r="I214">
+        <v>1.7964669371690601E-3</v>
+      </c>
+      <c r="J214">
+        <v>3.7485890560160499E-5</v>
+      </c>
+      <c r="K214">
+        <v>9.2619648118055605E-5</v>
+      </c>
+      <c r="L214">
+        <v>1.4541647242453899E-4</v>
+      </c>
+      <c r="M214">
+        <v>6.1585156370891098E-4</v>
+      </c>
+      <c r="N214">
+        <v>3.0692057756591601E-4</v>
+      </c>
+    </row>
+    <row r="215" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A215" s="200">
+        <v>1</v>
+      </c>
+      <c r="B215" t="s">
+        <v>484</v>
+      </c>
+      <c r="C215">
+        <v>2.3265375280009801E-4</v>
+      </c>
+      <c r="D215">
+        <v>1.9136674560422801E-2</v>
+      </c>
+      <c r="E215">
+        <v>0.23589766126926301</v>
+      </c>
+      <c r="F215">
+        <v>0.69040972541231904</v>
+      </c>
+      <c r="G215">
+        <v>0.19916894714660299</v>
+      </c>
+      <c r="H215">
+        <v>0.18133996830426699</v>
+      </c>
+      <c r="I215">
+        <v>0.12438989891119601</v>
+      </c>
+      <c r="J215">
+        <v>1.97945603311347E-4</v>
+      </c>
+      <c r="K215">
+        <v>5.0155512495805298E-5</v>
+      </c>
+      <c r="L215">
+        <v>6.9101847011154097E-6</v>
+      </c>
+      <c r="M215">
+        <v>1.1304247424257901E-6</v>
+      </c>
+      <c r="N215">
+        <v>7.4021615145886902E-4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A216" s="200">
+        <v>1</v>
+      </c>
+      <c r="B216" t="s">
+        <v>485</v>
+      </c>
+      <c r="C216">
+        <v>6.6350314340162295E-2</v>
+      </c>
+      <c r="D216">
+        <v>0.14810305289837999</v>
+      </c>
+      <c r="E216">
+        <v>0.47162958442885899</v>
+      </c>
+      <c r="F216">
+        <v>1.1323957289530699</v>
+      </c>
+      <c r="G216">
+        <v>0.45778789916401103</v>
+      </c>
+      <c r="H216">
+        <v>0.176373488386316</v>
+      </c>
+      <c r="I216">
+        <v>2.43668412805188E-3</v>
+      </c>
+      <c r="J216">
+        <v>3.14107143959668E-5</v>
+      </c>
+      <c r="K216">
+        <v>2.8341606203674497E-4</v>
+      </c>
+      <c r="L216">
+        <v>1.9828463392014699E-4</v>
+      </c>
+      <c r="M216">
+        <v>3.2120085354478799E-5</v>
+      </c>
+      <c r="N216">
+        <v>1.1401808387987E-3</v>
+      </c>
+    </row>
+    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A217" s="200">
+        <v>1</v>
+      </c>
+      <c r="B217" t="s">
+        <v>486</v>
+      </c>
+      <c r="C217">
+        <v>1.42452707113066E-2</v>
+      </c>
+      <c r="D217">
+        <v>0.28622281327909599</v>
+      </c>
+      <c r="E217">
+        <v>3.4275249005425601</v>
+      </c>
+      <c r="F217">
+        <v>4.0960574159172403</v>
+      </c>
+      <c r="G217">
+        <v>2.1215289146309799</v>
+      </c>
+      <c r="H217">
+        <v>0.339105669680559</v>
+      </c>
+      <c r="I217">
+        <v>0.13791452002305901</v>
+      </c>
+      <c r="J217">
+        <v>6.8684789501965602E-4</v>
+      </c>
+      <c r="K217">
+        <v>7.3319199767141706E-5</v>
+      </c>
+      <c r="L217">
+        <v>3.50109262997782E-4</v>
+      </c>
+      <c r="M217">
+        <v>5.37622066053339E-5</v>
+      </c>
+      <c r="N217">
+        <v>7.2312461991613898E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67945B17-5C0D-496E-B6E2-9CA888443B43}">
   <dimension ref="A1:M109"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -64815,7 +74321,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{082B273E-9771-44C3-BCA8-8817FB13A001}">
   <dimension ref="A1:M109"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
